--- a/SpaceX_Cursor_Pro_Forma_Model.xlsx
+++ b/SpaceX_Cursor_Pro_Forma_Model.xlsx
@@ -9,14 +9,13 @@
   <sheets>
     <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Assumptions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="IS SpaceX" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="IS Cursor" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Deal &amp; PPA" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Schedules" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Income Statement" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Balance Sheet" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Cash Flow" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Checks" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="Segments" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Deal &amp; PPA" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Schedules" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Income Statement" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Balance Sheet" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash Flow" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Checks" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -25,10 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="#,##0;(#,##0)"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="#,##0.0;(#,##0.0)"/>
+    <numFmt numFmtId="167" formatCode="0.0000"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -48,12 +48,12 @@
       <color rgb="000B1F3A"/>
     </font>
     <font>
+      <b val="1"/>
+    </font>
+    <font>
       <i val="1"/>
       <color rgb="00595959"/>
       <sz val="9"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -120,12 +120,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="10" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -138,13 +138,20 @@
     </xf>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="4" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment indent="1"/>
+    </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="4" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -152,6 +159,7 @@
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -517,7 +525,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B24"/>
+  <dimension ref="B2:B25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -544,7 +552,7 @@
     <row r="3">
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Pro-Forma Three-Statement Model</t>
+          <t>Pro-Forma Three-Statement Model — Segmented</t>
         </is>
       </c>
     </row>
@@ -573,100 +581,107 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="3" t="inlineStr"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Segments modelled: Space (launch + Starshield), Starlink, and xAI-Cursor (xAI/Grok + Cursor)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="B10" s="4" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="B11" s="4" t="inlineStr">
         <is>
           <t>Contents:</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   • Assumptions — all input drivers (blue cells are editable inputs)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • IS SpaceX / IS Cursor — standalone operating builds</t>
+          <t xml:space="preserve">   • Assumptions — all input drivers (blue cells are editable inputs)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • Deal &amp; PPA — purchase price allocation, goodwill, intangibles</t>
+          <t xml:space="preserve">   • Segments — Space, Starlink &amp; xAI-Cursor: revenue, EBITDA &amp; EPS contribution</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • Schedules — PP&amp;E, intangibles/DTL, debt &amp; spectrum, tax/NOL</t>
+          <t xml:space="preserve">   • Deal &amp; PPA — purchase price allocation, goodwill, intangibles</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • Income Statement — pro-forma combined P&amp;L</t>
+          <t xml:space="preserve">   • Schedules — PP&amp;E, intangibles/DTL, debt &amp; spectrum, tax/NOL</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • Balance Sheet — purchase-accounting bridge + projections</t>
+          <t xml:space="preserve">   • Income Statement — segment-driven P&amp;L with EPS contribution by segment</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • Cash Flow — integrated cash flow statement</t>
+          <t xml:space="preserve">   • Balance Sheet — purchase-accounting bridge + projections</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">   • Checks — balance-sheet and cash-flow integrity checks</t>
+          <t xml:space="preserve">   • Cash Flow — integrated cash flow statement</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="3" t="inlineStr"/>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   • Checks — balance, cash-flow and segment EPS integrity checks</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>All figures in US$ millions unless stated. The workbook is fully formula-linked:</t>
-        </is>
-      </c>
+      <c r="B20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="B21" s="3" t="inlineStr">
         <is>
+          <t>All figures in US$ millions unless stated. The workbook is fully formula-linked:</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
           <t>change any blue input on the Assumptions tab and all three statements recalculate.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="B22" s="3" t="inlineStr"/>
-    </row>
     <row r="23">
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>DISCLAIMER: Illustrative model for analytical purposes only. Built from public</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="3" t="inlineStr">
+    <row r="25">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>estimates and reasonable assumptions; not investment advice and not company-verified.</t>
         </is>
@@ -677,13 +692,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:L44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -703,7 +718,7 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>MODEL INTEGRITY CHECKS (should all be ~0)</t>
+          <t>ASSUMPTIONS &amp; DRIVERS  (US$ millions unless noted; blue = input)</t>
         </is>
       </c>
     </row>
@@ -741,77 +756,653 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Balance sheet balances (A − L&amp;E)</t>
-        </is>
-      </c>
-      <c r="C3" s="20">
-        <f>'Balance Sheet'!C32</f>
-        <v/>
-      </c>
-      <c r="D3" s="20">
-        <f>'Balance Sheet'!G32</f>
-        <v/>
-      </c>
-      <c r="E3" s="20">
-        <f>'Balance Sheet'!H32</f>
-        <v/>
-      </c>
-      <c r="F3" s="20">
-        <f>'Balance Sheet'!I32</f>
-        <v/>
-      </c>
-      <c r="G3" s="20">
-        <f>'Balance Sheet'!J32</f>
-        <v/>
-      </c>
-      <c r="H3" s="20">
-        <f>'Balance Sheet'!K32</f>
-        <v/>
-      </c>
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>Operating segments — revenue &amp; profitability</t>
+        </is>
+      </c>
+      <c r="B3" s="9" t="n"/>
+      <c r="C3" s="9" t="n"/>
+      <c r="D3" s="9" t="n"/>
+      <c r="E3" s="9" t="n"/>
+      <c r="F3" s="9" t="n"/>
+      <c r="G3" s="9" t="n"/>
+      <c r="H3" s="9" t="n"/>
+      <c r="I3" s="9" t="n"/>
+      <c r="J3" s="9" t="n"/>
+      <c r="K3" s="9" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Cash flow ties to balance sheet cash</t>
-        </is>
-      </c>
-      <c r="C4" s="24" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D4" s="20">
-        <f>'Cash Flow'!D29-'Balance Sheet'!G4</f>
-        <v/>
-      </c>
-      <c r="E4" s="20">
-        <f>'Cash Flow'!E29-'Balance Sheet'!H4</f>
-        <v/>
-      </c>
-      <c r="F4" s="20">
-        <f>'Cash Flow'!F29-'Balance Sheet'!I4</f>
-        <v/>
-      </c>
-      <c r="G4" s="20">
-        <f>'Cash Flow'!G29-'Balance Sheet'!J4</f>
-        <v/>
-      </c>
-      <c r="H4" s="20">
-        <f>'Cash Flow'!H29-'Balance Sheet'!K4</f>
-        <v/>
+          <t xml:space="preserve">  Space (launch services + Starshield)</t>
+        </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>PPA bridge balances (Open: A − L&amp;E)</t>
-        </is>
-      </c>
-      <c r="C5" s="20">
-        <f>'Balance Sheet'!F32</f>
-        <v/>
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Revenue, FY2025 ($M)</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Revenue growth %</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E6" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H6" s="12" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    EBITDA margin %</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="n">
+        <v>-0.08</v>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H7" s="12" t="n">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Starlink (satellite connectivity)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Revenue, FY2025 ($M)</t>
+        </is>
+      </c>
+      <c r="C9" s="11" t="n">
+        <v>11400</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Revenue growth %</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="F10" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H10" s="12" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    EBITDA margin %</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="F11" s="12" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="H11" s="12" t="n">
+        <v>0.57</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  xAI-Cursor (AI: xAI/Grok + Cursor)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Organic revenue, FY2025 ($M) [xAI ~1,300 + Cursor ~450]</t>
+        </is>
+      </c>
+      <c r="C13" s="11" t="n">
+        <v>1750</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Organic revenue growth %</t>
+        </is>
+      </c>
+      <c r="D14" s="12" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="E14" s="12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F14" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H14" s="12" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    EBITDA margin % (pre-synergies)</t>
+        </is>
+      </c>
+      <c r="C15" s="12" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="D15" s="12" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="E15" s="12" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="F15" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H15" s="12" t="n">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Pro-forma deal effects (within xAI-Cursor segment)</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="9" t="n"/>
+      <c r="I16" s="9" t="n"/>
+      <c r="J16" s="9" t="n"/>
+      <c r="K16" s="9" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Revenue synergies ($M) [Grok+Cursor cross-sell]</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" s="11" t="n">
+        <v>50</v>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>200</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>350</v>
+      </c>
+      <c r="G17" s="11" t="n">
+        <v>450</v>
+      </c>
+      <c r="H17" s="11" t="n">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Cost synergies ($M) [in-source inference on xAI/Starlink]</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>350</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>550</v>
+      </c>
+      <c r="G18" s="11" t="n">
+        <v>700</v>
+      </c>
+      <c r="H18" s="11" t="n">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Integration &amp; one-time deal costs ($M)</t>
+        </is>
+      </c>
+      <c r="C19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="11" t="n">
+        <v>500</v>
+      </c>
+      <c r="E19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Capital, financing &amp; other</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="9" t="n"/>
+      <c r="H20" s="9" t="n"/>
+      <c r="I20" s="9" t="n"/>
+      <c r="J20" s="9" t="n"/>
+      <c r="K20" s="9" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Capex % of combined revenue</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>0.165</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Depreciation % of beginning net PP&amp;E</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="n">
+        <v>0.09</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D&amp;A allocation — Space %</t>
+        </is>
+      </c>
+      <c r="C23" s="12" t="n">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D&amp;A allocation — Starlink %</t>
+        </is>
+      </c>
+      <c r="C24" s="12" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D&amp;A allocation — xAI-Cursor %</t>
+        </is>
+      </c>
+      <c r="C25" s="12" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Stock-based comp % of revenue</t>
+        </is>
+      </c>
+      <c r="C26" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D26" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E26" s="12" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="F26" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="H26" s="12" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Net new long-term debt ($M)</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E27" s="11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G27" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H27" s="11" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Spectrum obligation repayment ($M)</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="11" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="E28" s="11" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="G28" s="11" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="H28" s="11" t="n">
+        <v>-2000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Primary equity issuance / IPO proceeds ($M)</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="11" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="13" t="inlineStr">
+        <is>
+          <t>SpaceX June-2026 IPO</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Interest rate on debt &amp; spectrum obligation</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="n">
+        <v>0.065</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Interest income rate on cash</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="n">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Statutory tax rate</t>
+        </is>
+      </c>
+      <c r="C32" s="12" t="n">
+        <v>0.21</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Opening NOL carryforward, FY2025 ($M)</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="n">
+        <v>26000</v>
+      </c>
+      <c r="L33" s="13" t="inlineStr">
+        <is>
+          <t>SpaceX accumulated + Cursor</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NOL usage limit (% of taxable income)</t>
+        </is>
+      </c>
+      <c r="C34" s="12" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SpaceX shares pre-deal (M)</t>
+        </is>
+      </c>
+      <c r="C35" s="14" t="n">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  SpaceX share price, deal pricing ($)</t>
+        </is>
+      </c>
+      <c r="C36" s="15" t="n">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>Working capital ratios (% of revenue)</t>
+        </is>
+      </c>
+      <c r="B37" s="9" t="n"/>
+      <c r="C37" s="9" t="n"/>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="9" t="n"/>
+      <c r="H37" s="9" t="n"/>
+      <c r="I37" s="9" t="n"/>
+      <c r="J37" s="9" t="n"/>
+      <c r="K37" s="9" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Accounts receivable (% of revenue)</t>
+        </is>
+      </c>
+      <c r="C38" s="12" t="n">
+        <v>0.1339</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Inventory (% of revenue)</t>
+        </is>
+      </c>
+      <c r="C39" s="12" t="n">
+        <v>0.1499</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Prepaid &amp; other current assets (% of revenue)</t>
+        </is>
+      </c>
+      <c r="C40" s="12" t="n">
+        <v>0.0803</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Accounts payable (% of revenue)</t>
+        </is>
+      </c>
+      <c r="C41" s="12" t="n">
+        <v>0.1499</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Accrued liabilities (% of revenue)</t>
+        </is>
+      </c>
+      <c r="C42" s="12" t="n">
+        <v>0.091</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Deferred revenue, current (% of revenue)</t>
+        </is>
+      </c>
+      <c r="C43" s="12" t="n">
+        <v>0.1499</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Customer deposits &amp; advances (% of revenue)</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="n">
+        <v>0.1017</v>
       </c>
     </row>
   </sheetData>
@@ -819,13 +1410,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L40"/>
+  <dimension ref="A1:K50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -845,1002 +1436,1354 @@
     <row r="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>ASSUMPTIONS &amp; DRIVERS  (US$ millions unless noted; blue = input)</t>
+          <t>OPERATING SEGMENTS — revenue, EBITDA &amp; EPS contribution (US$M)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="C2" s="7" t="inlineStr">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>xAI-Cursor combines xAI/Grok with the acquired Cursor business and carries all deal synergies, integration costs and acquired-intangible amortization.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="C3" s="7" t="inlineStr">
         <is>
           <t>2025A</t>
         </is>
       </c>
-      <c r="D2" s="7" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>2026E</t>
         </is>
       </c>
-      <c r="E2" s="7" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>2027E</t>
         </is>
       </c>
-      <c r="F2" s="7" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>2028E</t>
         </is>
       </c>
-      <c r="G2" s="7" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>2029E</t>
         </is>
       </c>
-      <c r="H2" s="7" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>2030E</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="8" t="inlineStr">
-        <is>
-          <t>SpaceX standalone (consolidated, incl. Starlink, launch, Starshield, xAI)</t>
-        </is>
-      </c>
-      <c r="B3" s="9" t="n"/>
-      <c r="C3" s="9" t="n"/>
-      <c r="D3" s="9" t="n"/>
-      <c r="E3" s="9" t="n"/>
-      <c r="F3" s="9" t="n"/>
-      <c r="G3" s="9" t="n"/>
-      <c r="H3" s="9" t="n"/>
-      <c r="I3" s="9" t="n"/>
-      <c r="J3" s="9" t="n"/>
-      <c r="K3" s="9" t="n"/>
-    </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Revenue, FY2025 actual ($M)</t>
-        </is>
-      </c>
-      <c r="C4" s="11" t="n">
-        <v>18674</v>
-      </c>
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Revenue by segment</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="9" t="n"/>
+      <c r="G4" s="9" t="n"/>
+      <c r="H4" s="9" t="n"/>
+      <c r="I4" s="9" t="n"/>
+      <c r="J4" s="9" t="n"/>
+      <c r="K4" s="9" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Revenue growth %</t>
-        </is>
-      </c>
-      <c r="D5" s="12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E5" s="12" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="F5" s="12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="G5" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="H5" s="12" t="n">
-        <v>0.22</v>
+          <t xml:space="preserve">  Space</t>
+        </is>
+      </c>
+      <c r="C5" s="16">
+        <f>'Assumptions'!C5</f>
+        <v/>
+      </c>
+      <c r="D5" s="16">
+        <f>'Segments'!C5*(1+'Assumptions'!D6)</f>
+        <v/>
+      </c>
+      <c r="E5" s="16">
+        <f>'Segments'!D5*(1+'Assumptions'!E6)</f>
+        <v/>
+      </c>
+      <c r="F5" s="16">
+        <f>'Segments'!E5*(1+'Assumptions'!F6)</f>
+        <v/>
+      </c>
+      <c r="G5" s="16">
+        <f>'Segments'!F5*(1+'Assumptions'!G6)</f>
+        <v/>
+      </c>
+      <c r="H5" s="16">
+        <f>'Segments'!G5*(1+'Assumptions'!H6)</f>
+        <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  COGS % of revenue (ex-D&amp;A)</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="D6" s="12" t="n">
-        <v>0.535</v>
-      </c>
-      <c r="E6" s="12" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="F6" s="12" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="G6" s="12" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H6" s="12" t="n">
-        <v>0.48</v>
+          <t xml:space="preserve">  Starlink</t>
+        </is>
+      </c>
+      <c r="C6" s="16">
+        <f>'Assumptions'!C9</f>
+        <v/>
+      </c>
+      <c r="D6" s="16">
+        <f>'Segments'!C6*(1+'Assumptions'!D10)</f>
+        <v/>
+      </c>
+      <c r="E6" s="16">
+        <f>'Segments'!D6*(1+'Assumptions'!E10)</f>
+        <v/>
+      </c>
+      <c r="F6" s="16">
+        <f>'Segments'!E6*(1+'Assumptions'!F10)</f>
+        <v/>
+      </c>
+      <c r="G6" s="16">
+        <f>'Segments'!F6*(1+'Assumptions'!G10)</f>
+        <v/>
+      </c>
+      <c r="H6" s="16">
+        <f>'Segments'!G6*(1+'Assumptions'!H10)</f>
+        <v/>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  R&amp;D % of revenue</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E7" s="12" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="F7" s="12" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="G7" s="12" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="H7" s="12" t="n">
-        <v>0.125</v>
+          <t xml:space="preserve">  xAI-Cursor — organic</t>
+        </is>
+      </c>
+      <c r="C7" s="16">
+        <f>'Assumptions'!C13</f>
+        <v/>
+      </c>
+      <c r="D7" s="16">
+        <f>'Segments'!C7*(1+'Assumptions'!D14)</f>
+        <v/>
+      </c>
+      <c r="E7" s="16">
+        <f>'Segments'!D7*(1+'Assumptions'!E14)</f>
+        <v/>
+      </c>
+      <c r="F7" s="16">
+        <f>'Segments'!E7*(1+'Assumptions'!F14)</f>
+        <v/>
+      </c>
+      <c r="G7" s="16">
+        <f>'Segments'!F7*(1+'Assumptions'!G14)</f>
+        <v/>
+      </c>
+      <c r="H7" s="16">
+        <f>'Segments'!G7*(1+'Assumptions'!H14)</f>
+        <v/>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  SG&amp;A % of revenue</t>
-        </is>
-      </c>
-      <c r="C8" s="12" t="n">
-        <v>0.147</v>
-      </c>
-      <c r="D8" s="12" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="E8" s="12" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="F8" s="12" t="n">
-        <v>0.115</v>
-      </c>
-      <c r="G8" s="12" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="H8" s="12" t="n">
-        <v>0.1</v>
+          <t xml:space="preserve">  xAI-Cursor — revenue synergies</t>
+        </is>
+      </c>
+      <c r="C8" s="16">
+        <f>'Assumptions'!C17</f>
+        <v/>
+      </c>
+      <c r="D8" s="16">
+        <f>'Assumptions'!D17</f>
+        <v/>
+      </c>
+      <c r="E8" s="16">
+        <f>'Assumptions'!E17</f>
+        <v/>
+      </c>
+      <c r="F8" s="16">
+        <f>'Assumptions'!F17</f>
+        <v/>
+      </c>
+      <c r="G8" s="16">
+        <f>'Assumptions'!G17</f>
+        <v/>
+      </c>
+      <c r="H8" s="16">
+        <f>'Assumptions'!H17</f>
+        <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>Cursor / Anysphere standalone (AI coding platform)</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="n"/>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
-      <c r="E9" s="9" t="n"/>
-      <c r="F9" s="9" t="n"/>
-      <c r="G9" s="9" t="n"/>
-      <c r="H9" s="9" t="n"/>
-      <c r="I9" s="9" t="n"/>
-      <c r="J9" s="9" t="n"/>
-      <c r="K9" s="9" t="n"/>
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  xAI-Cursor — total</t>
+        </is>
+      </c>
+      <c r="C9" s="16">
+        <f>'Segments'!C7+'Segments'!C8</f>
+        <v/>
+      </c>
+      <c r="D9" s="16">
+        <f>'Segments'!D7+'Segments'!D8</f>
+        <v/>
+      </c>
+      <c r="E9" s="16">
+        <f>'Segments'!E7+'Segments'!E8</f>
+        <v/>
+      </c>
+      <c r="F9" s="16">
+        <f>'Segments'!F7+'Segments'!F8</f>
+        <v/>
+      </c>
+      <c r="G9" s="16">
+        <f>'Segments'!G7+'Segments'!G8</f>
+        <v/>
+      </c>
+      <c r="H9" s="16">
+        <f>'Segments'!H7+'Segments'!H8</f>
+        <v/>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Revenue ($M)</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="n">
-        <v>450</v>
-      </c>
-      <c r="D10" s="11" t="n">
-        <v>3000</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <v>6500</v>
-      </c>
-      <c r="F10" s="11" t="n">
-        <v>10000</v>
-      </c>
-      <c r="G10" s="11" t="n">
-        <v>13500</v>
-      </c>
-      <c r="H10" s="11" t="n">
-        <v>17000</v>
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Total revenue</t>
+        </is>
+      </c>
+      <c r="C10" s="17">
+        <f>'Segments'!C5+'Segments'!C6+'Segments'!C9</f>
+        <v/>
+      </c>
+      <c r="D10" s="17">
+        <f>'Segments'!D5+'Segments'!D6+'Segments'!D9</f>
+        <v/>
+      </c>
+      <c r="E10" s="17">
+        <f>'Segments'!E5+'Segments'!E6+'Segments'!E9</f>
+        <v/>
+      </c>
+      <c r="F10" s="17">
+        <f>'Segments'!F5+'Segments'!F6+'Segments'!F9</f>
+        <v/>
+      </c>
+      <c r="G10" s="17">
+        <f>'Segments'!G5+'Segments'!G6+'Segments'!G9</f>
+        <v/>
+      </c>
+      <c r="H10" s="17">
+        <f>'Segments'!H5+'Segments'!H6+'Segments'!H9</f>
+        <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  COGS % of revenue (inference / cloud, ex-D&amp;A)</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="D11" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E11" s="12" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="F11" s="12" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="G11" s="12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="H11" s="12" t="n">
-        <v>0.38</v>
-      </c>
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>EBITDA by segment</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="n"/>
+      <c r="H11" s="9" t="n"/>
+      <c r="I11" s="9" t="n"/>
+      <c r="J11" s="9" t="n"/>
+      <c r="K11" s="9" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  R&amp;D % of revenue</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="D12" s="12" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E12" s="12" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="F12" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="G12" s="12" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="H12" s="12" t="n">
-        <v>0.22</v>
+          <t xml:space="preserve">  Space</t>
+        </is>
+      </c>
+      <c r="C12" s="16">
+        <f>'Segments'!C5*'Assumptions'!C7</f>
+        <v/>
+      </c>
+      <c r="D12" s="16">
+        <f>'Segments'!D5*'Assumptions'!D7</f>
+        <v/>
+      </c>
+      <c r="E12" s="16">
+        <f>'Segments'!E5*'Assumptions'!E7</f>
+        <v/>
+      </c>
+      <c r="F12" s="16">
+        <f>'Segments'!F5*'Assumptions'!F7</f>
+        <v/>
+      </c>
+      <c r="G12" s="16">
+        <f>'Segments'!G5*'Assumptions'!G7</f>
+        <v/>
+      </c>
+      <c r="H12" s="16">
+        <f>'Segments'!H5*'Assumptions'!H7</f>
+        <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Sales &amp; marketing % of revenue</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E13" s="12" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="F13" s="12" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="G13" s="12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H13" s="12" t="n">
-        <v>0.18</v>
+          <t xml:space="preserve">  Starlink</t>
+        </is>
+      </c>
+      <c r="C13" s="16">
+        <f>'Segments'!C6*'Assumptions'!C11</f>
+        <v/>
+      </c>
+      <c r="D13" s="16">
+        <f>'Segments'!D6*'Assumptions'!D11</f>
+        <v/>
+      </c>
+      <c r="E13" s="16">
+        <f>'Segments'!E6*'Assumptions'!E11</f>
+        <v/>
+      </c>
+      <c r="F13" s="16">
+        <f>'Segments'!F6*'Assumptions'!F11</f>
+        <v/>
+      </c>
+      <c r="G13" s="16">
+        <f>'Segments'!G6*'Assumptions'!G11</f>
+        <v/>
+      </c>
+      <c r="H13" s="16">
+        <f>'Segments'!H6*'Assumptions'!H11</f>
+        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  G&amp;A % of revenue</t>
-        </is>
-      </c>
-      <c r="C14" s="12" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="D14" s="12" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="E14" s="12" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="F14" s="12" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="G14" s="12" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="H14" s="12" t="n">
-        <v>0.08</v>
+          <t xml:space="preserve">  xAI-Cursor (incl. cost synergies less integration)</t>
+        </is>
+      </c>
+      <c r="C14" s="16">
+        <f>'Segments'!C9*'Assumptions'!C15+'Assumptions'!C18-'Assumptions'!C19</f>
+        <v/>
+      </c>
+      <c r="D14" s="16">
+        <f>'Segments'!D9*'Assumptions'!D15+'Assumptions'!D18-'Assumptions'!D19</f>
+        <v/>
+      </c>
+      <c r="E14" s="16">
+        <f>'Segments'!E9*'Assumptions'!E15+'Assumptions'!E18-'Assumptions'!E19</f>
+        <v/>
+      </c>
+      <c r="F14" s="16">
+        <f>'Segments'!F9*'Assumptions'!F15+'Assumptions'!F18-'Assumptions'!F19</f>
+        <v/>
+      </c>
+      <c r="G14" s="16">
+        <f>'Segments'!G9*'Assumptions'!G15+'Assumptions'!G18-'Assumptions'!G19</f>
+        <v/>
+      </c>
+      <c r="H14" s="16">
+        <f>'Segments'!H9*'Assumptions'!H15+'Assumptions'!H18-'Assumptions'!H19</f>
+        <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Pro-forma adjustments (deal effects)</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
-      <c r="G15" s="9" t="n"/>
-      <c r="H15" s="9" t="n"/>
-      <c r="I15" s="9" t="n"/>
-      <c r="J15" s="9" t="n"/>
-      <c r="K15" s="9" t="n"/>
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Total EBITDA</t>
+        </is>
+      </c>
+      <c r="C15" s="17">
+        <f>'Segments'!C12+'Segments'!C13+'Segments'!C14</f>
+        <v/>
+      </c>
+      <c r="D15" s="17">
+        <f>'Segments'!D12+'Segments'!D13+'Segments'!D14</f>
+        <v/>
+      </c>
+      <c r="E15" s="17">
+        <f>'Segments'!E12+'Segments'!E13+'Segments'!E14</f>
+        <v/>
+      </c>
+      <c r="F15" s="17">
+        <f>'Segments'!F12+'Segments'!F13+'Segments'!F14</f>
+        <v/>
+      </c>
+      <c r="G15" s="17">
+        <f>'Segments'!G12+'Segments'!G13+'Segments'!G14</f>
+        <v/>
+      </c>
+      <c r="H15" s="17">
+        <f>'Segments'!H12+'Segments'!H13+'Segments'!H14</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Revenue synergies ($M)</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" s="11" t="n">
-        <v>50</v>
-      </c>
-      <c r="E16" s="11" t="n">
-        <v>200</v>
-      </c>
-      <c r="F16" s="11" t="n">
-        <v>350</v>
-      </c>
-      <c r="G16" s="11" t="n">
-        <v>450</v>
-      </c>
-      <c r="H16" s="11" t="n">
-        <v>550</v>
+          <t xml:space="preserve">  Total EBITDA margin %</t>
+        </is>
+      </c>
+      <c r="C16" s="18">
+        <f>'Segments'!C15/'Segments'!C10</f>
+        <v/>
+      </c>
+      <c r="D16" s="18">
+        <f>'Segments'!D15/'Segments'!D10</f>
+        <v/>
+      </c>
+      <c r="E16" s="18">
+        <f>'Segments'!E15/'Segments'!E10</f>
+        <v/>
+      </c>
+      <c r="F16" s="18">
+        <f>'Segments'!F15/'Segments'!F10</f>
+        <v/>
+      </c>
+      <c r="G16" s="18">
+        <f>'Segments'!G15/'Segments'!G10</f>
+        <v/>
+      </c>
+      <c r="H16" s="18">
+        <f>'Segments'!H15/'Segments'!H10</f>
+        <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Cost synergies ($M) [in-source inference on xAI/Starlink]</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="11" t="n">
-        <v>100</v>
-      </c>
-      <c r="E17" s="11" t="n">
-        <v>350</v>
-      </c>
-      <c r="F17" s="11" t="n">
-        <v>550</v>
-      </c>
-      <c r="G17" s="11" t="n">
-        <v>700</v>
-      </c>
-      <c r="H17" s="11" t="n">
-        <v>850</v>
-      </c>
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Segment contribution to net income &amp; EPS</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9" t="n"/>
+      <c r="H17" s="9" t="n"/>
+      <c r="I17" s="9" t="n"/>
+      <c r="J17" s="9" t="n"/>
+      <c r="K17" s="9" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Integration &amp; one-time deal costs ($M)</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="11" t="n">
-        <v>500</v>
-      </c>
-      <c r="E18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="11" t="n">
-        <v>0</v>
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  D&amp;A by capital-intensity weights; net interest &amp; tax allocated by revenue share.</t>
+        </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>Capital, financing &amp; other</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="9" t="n"/>
-      <c r="E19" s="9" t="n"/>
-      <c r="F19" s="9" t="n"/>
-      <c r="G19" s="9" t="n"/>
-      <c r="H19" s="9" t="n"/>
-      <c r="I19" s="9" t="n"/>
-      <c r="J19" s="9" t="n"/>
-      <c r="K19" s="9" t="n"/>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Space</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Capex % of combined revenue</t>
-        </is>
-      </c>
-      <c r="C20" s="12" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="D20" s="12" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E20" s="12" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="F20" s="12" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="G20" s="12" t="n">
-        <v>0.175</v>
-      </c>
-      <c r="H20" s="12" t="n">
-        <v>0.165</v>
+          <t xml:space="preserve">     EBITDA</t>
+        </is>
+      </c>
+      <c r="C20" s="16">
+        <f>'Segments'!C12</f>
+        <v/>
+      </c>
+      <c r="D20" s="16">
+        <f>'Segments'!D12</f>
+        <v/>
+      </c>
+      <c r="E20" s="16">
+        <f>'Segments'!E12</f>
+        <v/>
+      </c>
+      <c r="F20" s="16">
+        <f>'Segments'!F12</f>
+        <v/>
+      </c>
+      <c r="G20" s="16">
+        <f>'Segments'!G12</f>
+        <v/>
+      </c>
+      <c r="H20" s="16">
+        <f>'Segments'!H12</f>
+        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Depreciation % of beginning net PP&amp;E</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="n">
-        <v>0.09</v>
+          <t xml:space="preserve">     Less: depreciation</t>
+        </is>
+      </c>
+      <c r="C21" s="16">
+        <f>-'Income Statement'!C16*'Assumptions'!C23</f>
+        <v/>
+      </c>
+      <c r="D21" s="16">
+        <f>-'Income Statement'!D16*'Assumptions'!C23</f>
+        <v/>
+      </c>
+      <c r="E21" s="16">
+        <f>-'Income Statement'!E16*'Assumptions'!C23</f>
+        <v/>
+      </c>
+      <c r="F21" s="16">
+        <f>-'Income Statement'!F16*'Assumptions'!C23</f>
+        <v/>
+      </c>
+      <c r="G21" s="16">
+        <f>-'Income Statement'!G16*'Assumptions'!C23</f>
+        <v/>
+      </c>
+      <c r="H21" s="16">
+        <f>-'Income Statement'!H16*'Assumptions'!C23</f>
+        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Stock-based comp % of revenue</t>
-        </is>
-      </c>
-      <c r="C22" s="12" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="D22" s="12" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E22" s="12" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="F22" s="12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G22" s="12" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="H22" s="12" t="n">
-        <v>0.04</v>
+          <t xml:space="preserve">     Less: intangible amortization</t>
+        </is>
+      </c>
+      <c r="C22" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Net new long-term debt ($M)</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" s="11" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E23" s="11" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F23" s="11" t="n">
-        <v>1500</v>
-      </c>
-      <c r="G23" s="11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H23" s="11" t="n">
-        <v>1000</v>
+      <c r="A23" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     EBIT</t>
+        </is>
+      </c>
+      <c r="C23" s="17">
+        <f>'Segments'!C20+'Segments'!C21+'Segments'!C22</f>
+        <v/>
+      </c>
+      <c r="D23" s="17">
+        <f>'Segments'!D20+'Segments'!D21+'Segments'!D22</f>
+        <v/>
+      </c>
+      <c r="E23" s="17">
+        <f>'Segments'!E20+'Segments'!E21+'Segments'!E22</f>
+        <v/>
+      </c>
+      <c r="F23" s="17">
+        <f>'Segments'!F20+'Segments'!F21+'Segments'!F22</f>
+        <v/>
+      </c>
+      <c r="G23" s="17">
+        <f>'Segments'!G20+'Segments'!G21+'Segments'!G22</f>
+        <v/>
+      </c>
+      <c r="H23" s="17">
+        <f>'Segments'!H20+'Segments'!H21+'Segments'!H22</f>
+        <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Spectrum obligation repayment ($M)</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="11" t="n">
-        <v>-2000</v>
-      </c>
-      <c r="E24" s="11" t="n">
-        <v>-2000</v>
-      </c>
-      <c r="F24" s="11" t="n">
-        <v>-2000</v>
-      </c>
-      <c r="G24" s="11" t="n">
-        <v>-2000</v>
-      </c>
-      <c r="H24" s="11" t="n">
-        <v>-2000</v>
+          <t xml:space="preserve">     Net interest (alloc.)</t>
+        </is>
+      </c>
+      <c r="C24" s="16">
+        <f>('Income Statement'!C20+'Income Statement'!C21)*('Segments'!C5/'Segments'!C10)</f>
+        <v/>
+      </c>
+      <c r="D24" s="16">
+        <f>('Income Statement'!D20+'Income Statement'!D21)*('Segments'!D5/'Segments'!D10)</f>
+        <v/>
+      </c>
+      <c r="E24" s="16">
+        <f>('Income Statement'!E20+'Income Statement'!E21)*('Segments'!E5/'Segments'!E10)</f>
+        <v/>
+      </c>
+      <c r="F24" s="16">
+        <f>('Income Statement'!F20+'Income Statement'!F21)*('Segments'!F5/'Segments'!F10)</f>
+        <v/>
+      </c>
+      <c r="G24" s="16">
+        <f>('Income Statement'!G20+'Income Statement'!G21)*('Segments'!G5/'Segments'!G10)</f>
+        <v/>
+      </c>
+      <c r="H24" s="16">
+        <f>('Income Statement'!H20+'Income Statement'!H21)*('Segments'!H5/'Segments'!H10)</f>
+        <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Primary equity issuance / IPO proceeds ($M)</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="11" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H25" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="13" t="inlineStr">
-        <is>
-          <t>SpaceX June-2026 IPO</t>
-        </is>
+          <t xml:space="preserve">     Pre-tax income</t>
+        </is>
+      </c>
+      <c r="C25" s="16">
+        <f>'Segments'!C23+'Segments'!C24</f>
+        <v/>
+      </c>
+      <c r="D25" s="16">
+        <f>'Segments'!D23+'Segments'!D24</f>
+        <v/>
+      </c>
+      <c r="E25" s="16">
+        <f>'Segments'!E23+'Segments'!E24</f>
+        <v/>
+      </c>
+      <c r="F25" s="16">
+        <f>'Segments'!F23+'Segments'!F24</f>
+        <v/>
+      </c>
+      <c r="G25" s="16">
+        <f>'Segments'!G23+'Segments'!G24</f>
+        <v/>
+      </c>
+      <c r="H25" s="16">
+        <f>'Segments'!H23+'Segments'!H24</f>
+        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Interest rate on debt &amp; spectrum obligation</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="n">
-        <v>0.065</v>
+          <t xml:space="preserve">     Income tax (alloc.)</t>
+        </is>
+      </c>
+      <c r="C26" s="16">
+        <f>('Income Statement'!C23+'Income Statement'!C24)*('Segments'!C5/'Segments'!C10)</f>
+        <v/>
+      </c>
+      <c r="D26" s="16">
+        <f>('Income Statement'!D23+'Income Statement'!D24)*('Segments'!D5/'Segments'!D10)</f>
+        <v/>
+      </c>
+      <c r="E26" s="16">
+        <f>('Income Statement'!E23+'Income Statement'!E24)*('Segments'!E5/'Segments'!E10)</f>
+        <v/>
+      </c>
+      <c r="F26" s="16">
+        <f>('Income Statement'!F23+'Income Statement'!F24)*('Segments'!F5/'Segments'!F10)</f>
+        <v/>
+      </c>
+      <c r="G26" s="16">
+        <f>('Income Statement'!G23+'Income Statement'!G24)*('Segments'!G5/'Segments'!G10)</f>
+        <v/>
+      </c>
+      <c r="H26" s="16">
+        <f>('Income Statement'!H23+'Income Statement'!H24)*('Segments'!H5/'Segments'!H10)</f>
+        <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Interest income rate on cash</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="n">
-        <v>0.04</v>
+      <c r="A27" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Net income contribution</t>
+        </is>
+      </c>
+      <c r="C27" s="17">
+        <f>'Segments'!C25+'Segments'!C26</f>
+        <v/>
+      </c>
+      <c r="D27" s="17">
+        <f>'Segments'!D25+'Segments'!D26</f>
+        <v/>
+      </c>
+      <c r="E27" s="17">
+        <f>'Segments'!E25+'Segments'!E26</f>
+        <v/>
+      </c>
+      <c r="F27" s="17">
+        <f>'Segments'!F25+'Segments'!F26</f>
+        <v/>
+      </c>
+      <c r="G27" s="17">
+        <f>'Segments'!G25+'Segments'!G26</f>
+        <v/>
+      </c>
+      <c r="H27" s="17">
+        <f>'Segments'!H25+'Segments'!H26</f>
+        <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Statutory tax rate</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="n">
-        <v>0.21</v>
+          <t xml:space="preserve">     EPS contribution ($)</t>
+        </is>
+      </c>
+      <c r="C28" s="21">
+        <f>'Segments'!C27/'Income Statement'!C27</f>
+        <v/>
+      </c>
+      <c r="D28" s="21">
+        <f>'Segments'!D27/'Income Statement'!D27</f>
+        <v/>
+      </c>
+      <c r="E28" s="21">
+        <f>'Segments'!E27/'Income Statement'!E27</f>
+        <v/>
+      </c>
+      <c r="F28" s="21">
+        <f>'Segments'!F27/'Income Statement'!F27</f>
+        <v/>
+      </c>
+      <c r="G28" s="21">
+        <f>'Segments'!G27/'Income Statement'!G27</f>
+        <v/>
+      </c>
+      <c r="H28" s="21">
+        <f>'Segments'!H27/'Income Statement'!H27</f>
+        <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Opening NOL carryforward, FY2025 ($M)</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="n">
-        <v>26000</v>
-      </c>
-      <c r="L29" s="13" t="inlineStr">
-        <is>
-          <t>SpaceX accumulated + Cursor</t>
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Starlink</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NOL usage limit (% of taxable income)</t>
-        </is>
-      </c>
-      <c r="C30" s="12" t="n">
-        <v>0.8</v>
+          <t xml:space="preserve">     EBITDA</t>
+        </is>
+      </c>
+      <c r="C30" s="16">
+        <f>'Segments'!C13</f>
+        <v/>
+      </c>
+      <c r="D30" s="16">
+        <f>'Segments'!D13</f>
+        <v/>
+      </c>
+      <c r="E30" s="16">
+        <f>'Segments'!E13</f>
+        <v/>
+      </c>
+      <c r="F30" s="16">
+        <f>'Segments'!F13</f>
+        <v/>
+      </c>
+      <c r="G30" s="16">
+        <f>'Segments'!G13</f>
+        <v/>
+      </c>
+      <c r="H30" s="16">
+        <f>'Segments'!H13</f>
+        <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  SpaceX shares pre-deal (M)</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="n">
-        <v>2000</v>
+          <t xml:space="preserve">     Less: depreciation</t>
+        </is>
+      </c>
+      <c r="C31" s="16">
+        <f>-'Income Statement'!C16*'Assumptions'!C24</f>
+        <v/>
+      </c>
+      <c r="D31" s="16">
+        <f>-'Income Statement'!D16*'Assumptions'!C24</f>
+        <v/>
+      </c>
+      <c r="E31" s="16">
+        <f>-'Income Statement'!E16*'Assumptions'!C24</f>
+        <v/>
+      </c>
+      <c r="F31" s="16">
+        <f>-'Income Statement'!F16*'Assumptions'!C24</f>
+        <v/>
+      </c>
+      <c r="G31" s="16">
+        <f>-'Income Statement'!G16*'Assumptions'!C24</f>
+        <v/>
+      </c>
+      <c r="H31" s="16">
+        <f>-'Income Statement'!H16*'Assumptions'!C24</f>
+        <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  SpaceX share price, deal pricing ($)</t>
-        </is>
-      </c>
-      <c r="C32" s="15" t="n">
-        <v>450</v>
+          <t xml:space="preserve">     Less: intangible amortization</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="8" t="inlineStr">
-        <is>
-          <t>Working capital ratios (% of revenue)</t>
-        </is>
-      </c>
-      <c r="B33" s="9" t="n"/>
-      <c r="C33" s="9" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="9" t="n"/>
-      <c r="F33" s="9" t="n"/>
-      <c r="G33" s="9" t="n"/>
-      <c r="H33" s="9" t="n"/>
-      <c r="I33" s="9" t="n"/>
-      <c r="J33" s="9" t="n"/>
-      <c r="K33" s="9" t="n"/>
+      <c r="A33" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     EBIT</t>
+        </is>
+      </c>
+      <c r="C33" s="17">
+        <f>'Segments'!C30+'Segments'!C31+'Segments'!C32</f>
+        <v/>
+      </c>
+      <c r="D33" s="17">
+        <f>'Segments'!D30+'Segments'!D31+'Segments'!D32</f>
+        <v/>
+      </c>
+      <c r="E33" s="17">
+        <f>'Segments'!E30+'Segments'!E31+'Segments'!E32</f>
+        <v/>
+      </c>
+      <c r="F33" s="17">
+        <f>'Segments'!F30+'Segments'!F31+'Segments'!F32</f>
+        <v/>
+      </c>
+      <c r="G33" s="17">
+        <f>'Segments'!G30+'Segments'!G31+'Segments'!G32</f>
+        <v/>
+      </c>
+      <c r="H33" s="17">
+        <f>'Segments'!H30+'Segments'!H31+'Segments'!H32</f>
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Accounts receivable (% of revenue)</t>
-        </is>
-      </c>
-      <c r="C34" s="12" t="n">
-        <v>0.1339</v>
+          <t xml:space="preserve">     Net interest (alloc.)</t>
+        </is>
+      </c>
+      <c r="C34" s="16">
+        <f>('Income Statement'!C20+'Income Statement'!C21)*('Segments'!C6/'Segments'!C10)</f>
+        <v/>
+      </c>
+      <c r="D34" s="16">
+        <f>('Income Statement'!D20+'Income Statement'!D21)*('Segments'!D6/'Segments'!D10)</f>
+        <v/>
+      </c>
+      <c r="E34" s="16">
+        <f>('Income Statement'!E20+'Income Statement'!E21)*('Segments'!E6/'Segments'!E10)</f>
+        <v/>
+      </c>
+      <c r="F34" s="16">
+        <f>('Income Statement'!F20+'Income Statement'!F21)*('Segments'!F6/'Segments'!F10)</f>
+        <v/>
+      </c>
+      <c r="G34" s="16">
+        <f>('Income Statement'!G20+'Income Statement'!G21)*('Segments'!G6/'Segments'!G10)</f>
+        <v/>
+      </c>
+      <c r="H34" s="16">
+        <f>('Income Statement'!H20+'Income Statement'!H21)*('Segments'!H6/'Segments'!H10)</f>
+        <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Inventory (% of revenue)</t>
-        </is>
-      </c>
-      <c r="C35" s="12" t="n">
-        <v>0.1499</v>
+          <t xml:space="preserve">     Pre-tax income</t>
+        </is>
+      </c>
+      <c r="C35" s="16">
+        <f>'Segments'!C33+'Segments'!C34</f>
+        <v/>
+      </c>
+      <c r="D35" s="16">
+        <f>'Segments'!D33+'Segments'!D34</f>
+        <v/>
+      </c>
+      <c r="E35" s="16">
+        <f>'Segments'!E33+'Segments'!E34</f>
+        <v/>
+      </c>
+      <c r="F35" s="16">
+        <f>'Segments'!F33+'Segments'!F34</f>
+        <v/>
+      </c>
+      <c r="G35" s="16">
+        <f>'Segments'!G33+'Segments'!G34</f>
+        <v/>
+      </c>
+      <c r="H35" s="16">
+        <f>'Segments'!H33+'Segments'!H34</f>
+        <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Prepaid &amp; other current assets (% of revenue)</t>
-        </is>
-      </c>
-      <c r="C36" s="12" t="n">
-        <v>0.0803</v>
+          <t xml:space="preserve">     Income tax (alloc.)</t>
+        </is>
+      </c>
+      <c r="C36" s="16">
+        <f>('Income Statement'!C23+'Income Statement'!C24)*('Segments'!C6/'Segments'!C10)</f>
+        <v/>
+      </c>
+      <c r="D36" s="16">
+        <f>('Income Statement'!D23+'Income Statement'!D24)*('Segments'!D6/'Segments'!D10)</f>
+        <v/>
+      </c>
+      <c r="E36" s="16">
+        <f>('Income Statement'!E23+'Income Statement'!E24)*('Segments'!E6/'Segments'!E10)</f>
+        <v/>
+      </c>
+      <c r="F36" s="16">
+        <f>('Income Statement'!F23+'Income Statement'!F24)*('Segments'!F6/'Segments'!F10)</f>
+        <v/>
+      </c>
+      <c r="G36" s="16">
+        <f>('Income Statement'!G23+'Income Statement'!G24)*('Segments'!G6/'Segments'!G10)</f>
+        <v/>
+      </c>
+      <c r="H36" s="16">
+        <f>('Income Statement'!H23+'Income Statement'!H24)*('Segments'!H6/'Segments'!H10)</f>
+        <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Accounts payable (% of revenue)</t>
-        </is>
-      </c>
-      <c r="C37" s="12" t="n">
-        <v>0.1499</v>
+      <c r="A37" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Net income contribution</t>
+        </is>
+      </c>
+      <c r="C37" s="17">
+        <f>'Segments'!C35+'Segments'!C36</f>
+        <v/>
+      </c>
+      <c r="D37" s="17">
+        <f>'Segments'!D35+'Segments'!D36</f>
+        <v/>
+      </c>
+      <c r="E37" s="17">
+        <f>'Segments'!E35+'Segments'!E36</f>
+        <v/>
+      </c>
+      <c r="F37" s="17">
+        <f>'Segments'!F35+'Segments'!F36</f>
+        <v/>
+      </c>
+      <c r="G37" s="17">
+        <f>'Segments'!G35+'Segments'!G36</f>
+        <v/>
+      </c>
+      <c r="H37" s="17">
+        <f>'Segments'!H35+'Segments'!H36</f>
+        <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Accrued liabilities (% of revenue)</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="n">
-        <v>0.091</v>
+          <t xml:space="preserve">     EPS contribution ($)</t>
+        </is>
+      </c>
+      <c r="C38" s="21">
+        <f>'Segments'!C37/'Income Statement'!C27</f>
+        <v/>
+      </c>
+      <c r="D38" s="21">
+        <f>'Segments'!D37/'Income Statement'!D27</f>
+        <v/>
+      </c>
+      <c r="E38" s="21">
+        <f>'Segments'!E37/'Income Statement'!E27</f>
+        <v/>
+      </c>
+      <c r="F38" s="21">
+        <f>'Segments'!F37/'Income Statement'!F27</f>
+        <v/>
+      </c>
+      <c r="G38" s="21">
+        <f>'Segments'!G37/'Income Statement'!G27</f>
+        <v/>
+      </c>
+      <c r="H38" s="21">
+        <f>'Segments'!H37/'Income Statement'!H27</f>
+        <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Deferred revenue, current (% of revenue)</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="n">
-        <v>0.1499</v>
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  xAI-Cursor</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Customer deposits &amp; advances (% of revenue)</t>
-        </is>
-      </c>
-      <c r="C40" s="12" t="n">
-        <v>0.1017</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="2" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>SPACEX STANDALONE — operating build (US$M, ex-D&amp;A cash costs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>2025A</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>2026E</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>2027E</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>2028E</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>2029E</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>2030E</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="C3" s="16">
-        <f>'Assumptions'!C4</f>
-        <v/>
-      </c>
-      <c r="D3" s="16">
-        <f>'IS SpaceX'!C3*(1+'Assumptions'!D5)</f>
-        <v/>
-      </c>
-      <c r="E3" s="16">
-        <f>'IS SpaceX'!D3*(1+'Assumptions'!E5)</f>
-        <v/>
-      </c>
-      <c r="F3" s="16">
-        <f>'IS SpaceX'!E3*(1+'Assumptions'!F5)</f>
-        <v/>
-      </c>
-      <c r="G3" s="16">
-        <f>'IS SpaceX'!F3*(1+'Assumptions'!G5)</f>
-        <v/>
-      </c>
-      <c r="H3" s="16">
-        <f>'IS SpaceX'!G3*(1+'Assumptions'!H5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>Cost of revenue (ex-D&amp;A)</t>
-        </is>
-      </c>
-      <c r="C4" s="16">
-        <f>'IS SpaceX'!C3*'Assumptions'!C6</f>
-        <v/>
-      </c>
-      <c r="D4" s="16">
-        <f>'IS SpaceX'!D3*'Assumptions'!D6</f>
-        <v/>
-      </c>
-      <c r="E4" s="16">
-        <f>'IS SpaceX'!E3*'Assumptions'!E6</f>
-        <v/>
-      </c>
-      <c r="F4" s="16">
-        <f>'IS SpaceX'!F3*'Assumptions'!F6</f>
-        <v/>
-      </c>
-      <c r="G4" s="16">
-        <f>'IS SpaceX'!G3*'Assumptions'!G6</f>
-        <v/>
-      </c>
-      <c r="H4" s="16">
-        <f>'IS SpaceX'!H3*'Assumptions'!H6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Gross profit (cash)</t>
-        </is>
-      </c>
-      <c r="C5" s="17">
-        <f>'IS SpaceX'!C3-'IS SpaceX'!C4</f>
-        <v/>
-      </c>
-      <c r="D5" s="17">
-        <f>'IS SpaceX'!D3-'IS SpaceX'!D4</f>
-        <v/>
-      </c>
-      <c r="E5" s="17">
-        <f>'IS SpaceX'!E3-'IS SpaceX'!E4</f>
-        <v/>
-      </c>
-      <c r="F5" s="17">
-        <f>'IS SpaceX'!F3-'IS SpaceX'!F4</f>
-        <v/>
-      </c>
-      <c r="G5" s="17">
-        <f>'IS SpaceX'!G3-'IS SpaceX'!G4</f>
-        <v/>
-      </c>
-      <c r="H5" s="17">
-        <f>'IS SpaceX'!H3-'IS SpaceX'!H4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>Research &amp; development</t>
-        </is>
-      </c>
-      <c r="C6" s="16">
-        <f>'IS SpaceX'!C3*'Assumptions'!C7</f>
-        <v/>
-      </c>
-      <c r="D6" s="16">
-        <f>'IS SpaceX'!D3*'Assumptions'!D7</f>
-        <v/>
-      </c>
-      <c r="E6" s="16">
-        <f>'IS SpaceX'!E3*'Assumptions'!E7</f>
-        <v/>
-      </c>
-      <c r="F6" s="16">
-        <f>'IS SpaceX'!F3*'Assumptions'!F7</f>
-        <v/>
-      </c>
-      <c r="G6" s="16">
-        <f>'IS SpaceX'!G3*'Assumptions'!G7</f>
-        <v/>
-      </c>
-      <c r="H6" s="16">
-        <f>'IS SpaceX'!H3*'Assumptions'!H7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Selling, general &amp; administrative</t>
-        </is>
-      </c>
-      <c r="C7" s="16">
-        <f>'IS SpaceX'!C3*'Assumptions'!C8</f>
-        <v/>
-      </c>
-      <c r="D7" s="16">
-        <f>'IS SpaceX'!D3*'Assumptions'!D8</f>
-        <v/>
-      </c>
-      <c r="E7" s="16">
-        <f>'IS SpaceX'!E3*'Assumptions'!E8</f>
-        <v/>
-      </c>
-      <c r="F7" s="16">
-        <f>'IS SpaceX'!F3*'Assumptions'!F8</f>
-        <v/>
-      </c>
-      <c r="G7" s="16">
-        <f>'IS SpaceX'!G3*'Assumptions'!G8</f>
-        <v/>
-      </c>
-      <c r="H7" s="16">
-        <f>'IS SpaceX'!H3*'Assumptions'!H8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>EBITDA (cash, ex-synergies)</t>
-        </is>
-      </c>
-      <c r="C8" s="17">
-        <f>'IS SpaceX'!C5-'IS SpaceX'!C6-'IS SpaceX'!C7</f>
-        <v/>
-      </c>
-      <c r="D8" s="17">
-        <f>'IS SpaceX'!D5-'IS SpaceX'!D6-'IS SpaceX'!D7</f>
-        <v/>
-      </c>
-      <c r="E8" s="17">
-        <f>'IS SpaceX'!E5-'IS SpaceX'!E6-'IS SpaceX'!E7</f>
-        <v/>
-      </c>
-      <c r="F8" s="17">
-        <f>'IS SpaceX'!F5-'IS SpaceX'!F6-'IS SpaceX'!F7</f>
-        <v/>
-      </c>
-      <c r="G8" s="17">
-        <f>'IS SpaceX'!G5-'IS SpaceX'!G6-'IS SpaceX'!G7</f>
-        <v/>
-      </c>
-      <c r="H8" s="17">
-        <f>'IS SpaceX'!H5-'IS SpaceX'!H6-'IS SpaceX'!H7</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  EBITDA margin %</t>
-        </is>
-      </c>
-      <c r="C9" s="18">
-        <f>'IS SpaceX'!C8/'IS SpaceX'!C3</f>
-        <v/>
-      </c>
-      <c r="D9" s="18">
-        <f>'IS SpaceX'!D8/'IS SpaceX'!D3</f>
-        <v/>
-      </c>
-      <c r="E9" s="18">
-        <f>'IS SpaceX'!E8/'IS SpaceX'!E3</f>
-        <v/>
-      </c>
-      <c r="F9" s="18">
-        <f>'IS SpaceX'!F8/'IS SpaceX'!F3</f>
-        <v/>
-      </c>
-      <c r="G9" s="18">
-        <f>'IS SpaceX'!G8/'IS SpaceX'!G3</f>
-        <v/>
-      </c>
-      <c r="H9" s="18">
-        <f>'IS SpaceX'!H8/'IS SpaceX'!H3</f>
+          <t xml:space="preserve">     EBITDA</t>
+        </is>
+      </c>
+      <c r="C40" s="16">
+        <f>'Segments'!C14</f>
+        <v/>
+      </c>
+      <c r="D40" s="16">
+        <f>'Segments'!D14</f>
+        <v/>
+      </c>
+      <c r="E40" s="16">
+        <f>'Segments'!E14</f>
+        <v/>
+      </c>
+      <c r="F40" s="16">
+        <f>'Segments'!F14</f>
+        <v/>
+      </c>
+      <c r="G40" s="16">
+        <f>'Segments'!G14</f>
+        <v/>
+      </c>
+      <c r="H40" s="16">
+        <f>'Segments'!H14</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Less: depreciation</t>
+        </is>
+      </c>
+      <c r="C41" s="16">
+        <f>-'Income Statement'!C16*'Assumptions'!C25</f>
+        <v/>
+      </c>
+      <c r="D41" s="16">
+        <f>-'Income Statement'!D16*'Assumptions'!C25</f>
+        <v/>
+      </c>
+      <c r="E41" s="16">
+        <f>-'Income Statement'!E16*'Assumptions'!C25</f>
+        <v/>
+      </c>
+      <c r="F41" s="16">
+        <f>-'Income Statement'!F16*'Assumptions'!C25</f>
+        <v/>
+      </c>
+      <c r="G41" s="16">
+        <f>-'Income Statement'!G16*'Assumptions'!C25</f>
+        <v/>
+      </c>
+      <c r="H41" s="16">
+        <f>-'Income Statement'!H16*'Assumptions'!C25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Less: intangible amortization</t>
+        </is>
+      </c>
+      <c r="C42" s="16">
+        <f>-'Income Statement'!C17</f>
+        <v/>
+      </c>
+      <c r="D42" s="16">
+        <f>-'Income Statement'!D17</f>
+        <v/>
+      </c>
+      <c r="E42" s="16">
+        <f>-'Income Statement'!E17</f>
+        <v/>
+      </c>
+      <c r="F42" s="16">
+        <f>-'Income Statement'!F17</f>
+        <v/>
+      </c>
+      <c r="G42" s="16">
+        <f>-'Income Statement'!G17</f>
+        <v/>
+      </c>
+      <c r="H42" s="16">
+        <f>-'Income Statement'!H17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     EBIT</t>
+        </is>
+      </c>
+      <c r="C43" s="17">
+        <f>'Segments'!C40+'Segments'!C41+'Segments'!C42</f>
+        <v/>
+      </c>
+      <c r="D43" s="17">
+        <f>'Segments'!D40+'Segments'!D41+'Segments'!D42</f>
+        <v/>
+      </c>
+      <c r="E43" s="17">
+        <f>'Segments'!E40+'Segments'!E41+'Segments'!E42</f>
+        <v/>
+      </c>
+      <c r="F43" s="17">
+        <f>'Segments'!F40+'Segments'!F41+'Segments'!F42</f>
+        <v/>
+      </c>
+      <c r="G43" s="17">
+        <f>'Segments'!G40+'Segments'!G41+'Segments'!G42</f>
+        <v/>
+      </c>
+      <c r="H43" s="17">
+        <f>'Segments'!H40+'Segments'!H41+'Segments'!H42</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Net interest (alloc.)</t>
+        </is>
+      </c>
+      <c r="C44" s="16">
+        <f>('Income Statement'!C20+'Income Statement'!C21)*('Segments'!C9/'Segments'!C10)</f>
+        <v/>
+      </c>
+      <c r="D44" s="16">
+        <f>('Income Statement'!D20+'Income Statement'!D21)*('Segments'!D9/'Segments'!D10)</f>
+        <v/>
+      </c>
+      <c r="E44" s="16">
+        <f>('Income Statement'!E20+'Income Statement'!E21)*('Segments'!E9/'Segments'!E10)</f>
+        <v/>
+      </c>
+      <c r="F44" s="16">
+        <f>('Income Statement'!F20+'Income Statement'!F21)*('Segments'!F9/'Segments'!F10)</f>
+        <v/>
+      </c>
+      <c r="G44" s="16">
+        <f>('Income Statement'!G20+'Income Statement'!G21)*('Segments'!G9/'Segments'!G10)</f>
+        <v/>
+      </c>
+      <c r="H44" s="16">
+        <f>('Income Statement'!H20+'Income Statement'!H21)*('Segments'!H9/'Segments'!H10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Pre-tax income</t>
+        </is>
+      </c>
+      <c r="C45" s="16">
+        <f>'Segments'!C43+'Segments'!C44</f>
+        <v/>
+      </c>
+      <c r="D45" s="16">
+        <f>'Segments'!D43+'Segments'!D44</f>
+        <v/>
+      </c>
+      <c r="E45" s="16">
+        <f>'Segments'!E43+'Segments'!E44</f>
+        <v/>
+      </c>
+      <c r="F45" s="16">
+        <f>'Segments'!F43+'Segments'!F44</f>
+        <v/>
+      </c>
+      <c r="G45" s="16">
+        <f>'Segments'!G43+'Segments'!G44</f>
+        <v/>
+      </c>
+      <c r="H45" s="16">
+        <f>'Segments'!H43+'Segments'!H44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Income tax (alloc.)</t>
+        </is>
+      </c>
+      <c r="C46" s="16">
+        <f>('Income Statement'!C23+'Income Statement'!C24)*('Segments'!C9/'Segments'!C10)</f>
+        <v/>
+      </c>
+      <c r="D46" s="16">
+        <f>('Income Statement'!D23+'Income Statement'!D24)*('Segments'!D9/'Segments'!D10)</f>
+        <v/>
+      </c>
+      <c r="E46" s="16">
+        <f>('Income Statement'!E23+'Income Statement'!E24)*('Segments'!E9/'Segments'!E10)</f>
+        <v/>
+      </c>
+      <c r="F46" s="16">
+        <f>('Income Statement'!F23+'Income Statement'!F24)*('Segments'!F9/'Segments'!F10)</f>
+        <v/>
+      </c>
+      <c r="G46" s="16">
+        <f>('Income Statement'!G23+'Income Statement'!G24)*('Segments'!G9/'Segments'!G10)</f>
+        <v/>
+      </c>
+      <c r="H46" s="16">
+        <f>('Income Statement'!H23+'Income Statement'!H24)*('Segments'!H9/'Segments'!H10)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Net income contribution</t>
+        </is>
+      </c>
+      <c r="C47" s="17">
+        <f>'Segments'!C45+'Segments'!C46</f>
+        <v/>
+      </c>
+      <c r="D47" s="17">
+        <f>'Segments'!D45+'Segments'!D46</f>
+        <v/>
+      </c>
+      <c r="E47" s="17">
+        <f>'Segments'!E45+'Segments'!E46</f>
+        <v/>
+      </c>
+      <c r="F47" s="17">
+        <f>'Segments'!F45+'Segments'!F46</f>
+        <v/>
+      </c>
+      <c r="G47" s="17">
+        <f>'Segments'!G45+'Segments'!G46</f>
+        <v/>
+      </c>
+      <c r="H47" s="17">
+        <f>'Segments'!H45+'Segments'!H46</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     EPS contribution ($)</t>
+        </is>
+      </c>
+      <c r="C48" s="21">
+        <f>'Segments'!C47/'Income Statement'!C27</f>
+        <v/>
+      </c>
+      <c r="D48" s="21">
+        <f>'Segments'!D47/'Income Statement'!D27</f>
+        <v/>
+      </c>
+      <c r="E48" s="21">
+        <f>'Segments'!E47/'Income Statement'!E27</f>
+        <v/>
+      </c>
+      <c r="F48" s="21">
+        <f>'Segments'!F47/'Income Statement'!F27</f>
+        <v/>
+      </c>
+      <c r="G48" s="21">
+        <f>'Segments'!G47/'Income Statement'!G27</f>
+        <v/>
+      </c>
+      <c r="H48" s="21">
+        <f>'Segments'!H47/'Income Statement'!H27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Total net income (check vs IS)</t>
+        </is>
+      </c>
+      <c r="C49" s="17">
+        <f>'Segments'!C27+'Segments'!C37+'Segments'!C47</f>
+        <v/>
+      </c>
+      <c r="D49" s="17">
+        <f>'Segments'!D27+'Segments'!D37+'Segments'!D47</f>
+        <v/>
+      </c>
+      <c r="E49" s="17">
+        <f>'Segments'!E27+'Segments'!E37+'Segments'!E47</f>
+        <v/>
+      </c>
+      <c r="F49" s="17">
+        <f>'Segments'!F27+'Segments'!F37+'Segments'!F47</f>
+        <v/>
+      </c>
+      <c r="G49" s="17">
+        <f>'Segments'!G27+'Segments'!G37+'Segments'!G47</f>
+        <v/>
+      </c>
+      <c r="H49" s="17">
+        <f>'Segments'!H27+'Segments'!H37+'Segments'!H47</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Total diluted EPS ($)</t>
+        </is>
+      </c>
+      <c r="C50" s="22">
+        <f>'Segments'!C28+'Segments'!C38+'Segments'!C48</f>
+        <v/>
+      </c>
+      <c r="D50" s="22">
+        <f>'Segments'!D28+'Segments'!D38+'Segments'!D48</f>
+        <v/>
+      </c>
+      <c r="E50" s="22">
+        <f>'Segments'!E28+'Segments'!E38+'Segments'!E48</f>
+        <v/>
+      </c>
+      <c r="F50" s="22">
+        <f>'Segments'!F28+'Segments'!F38+'Segments'!F48</f>
+        <v/>
+      </c>
+      <c r="G50" s="22">
+        <f>'Segments'!G28+'Segments'!G38+'Segments'!G48</f>
+        <v/>
+      </c>
+      <c r="H50" s="22">
+        <f>'Segments'!H28+'Segments'!H38+'Segments'!H48</f>
         <v/>
       </c>
     </row>
@@ -1850,322 +2793,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="2" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="13" customWidth="1" min="11" max="11"/>
-    <col width="22" customWidth="1" min="12" max="12"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t>CURSOR (ANYSPHERE) STANDALONE — operating build (US$M, ex-D&amp;A cash costs)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>2025A</t>
-        </is>
-      </c>
-      <c r="D2" s="7" t="inlineStr">
-        <is>
-          <t>2026E</t>
-        </is>
-      </c>
-      <c r="E2" s="7" t="inlineStr">
-        <is>
-          <t>2027E</t>
-        </is>
-      </c>
-      <c r="F2" s="7" t="inlineStr">
-        <is>
-          <t>2028E</t>
-        </is>
-      </c>
-      <c r="G2" s="7" t="inlineStr">
-        <is>
-          <t>2029E</t>
-        </is>
-      </c>
-      <c r="H2" s="7" t="inlineStr">
-        <is>
-          <t>2030E</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Revenue</t>
-        </is>
-      </c>
-      <c r="C3" s="16">
-        <f>'Assumptions'!C10</f>
-        <v/>
-      </c>
-      <c r="D3" s="16">
-        <f>'Assumptions'!D10</f>
-        <v/>
-      </c>
-      <c r="E3" s="16">
-        <f>'Assumptions'!E10</f>
-        <v/>
-      </c>
-      <c r="F3" s="16">
-        <f>'Assumptions'!F10</f>
-        <v/>
-      </c>
-      <c r="G3" s="16">
-        <f>'Assumptions'!G10</f>
-        <v/>
-      </c>
-      <c r="H3" s="16">
-        <f>'Assumptions'!H10</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>Cost of revenue (inference/cloud, ex-D&amp;A)</t>
-        </is>
-      </c>
-      <c r="C4" s="16">
-        <f>'IS Cursor'!C3*'Assumptions'!C11</f>
-        <v/>
-      </c>
-      <c r="D4" s="16">
-        <f>'IS Cursor'!D3*'Assumptions'!D11</f>
-        <v/>
-      </c>
-      <c r="E4" s="16">
-        <f>'IS Cursor'!E3*'Assumptions'!E11</f>
-        <v/>
-      </c>
-      <c r="F4" s="16">
-        <f>'IS Cursor'!F3*'Assumptions'!F11</f>
-        <v/>
-      </c>
-      <c r="G4" s="16">
-        <f>'IS Cursor'!G3*'Assumptions'!G11</f>
-        <v/>
-      </c>
-      <c r="H4" s="16">
-        <f>'IS Cursor'!H3*'Assumptions'!H11</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Gross profit (cash)</t>
-        </is>
-      </c>
-      <c r="C5" s="17">
-        <f>'IS Cursor'!C3-'IS Cursor'!C4</f>
-        <v/>
-      </c>
-      <c r="D5" s="17">
-        <f>'IS Cursor'!D3-'IS Cursor'!D4</f>
-        <v/>
-      </c>
-      <c r="E5" s="17">
-        <f>'IS Cursor'!E3-'IS Cursor'!E4</f>
-        <v/>
-      </c>
-      <c r="F5" s="17">
-        <f>'IS Cursor'!F3-'IS Cursor'!F4</f>
-        <v/>
-      </c>
-      <c r="G5" s="17">
-        <f>'IS Cursor'!G3-'IS Cursor'!G4</f>
-        <v/>
-      </c>
-      <c r="H5" s="17">
-        <f>'IS Cursor'!H3-'IS Cursor'!H4</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="10" t="inlineStr">
-        <is>
-          <t>Research &amp; development</t>
-        </is>
-      </c>
-      <c r="C6" s="16">
-        <f>'IS Cursor'!C3*'Assumptions'!C12</f>
-        <v/>
-      </c>
-      <c r="D6" s="16">
-        <f>'IS Cursor'!D3*'Assumptions'!D12</f>
-        <v/>
-      </c>
-      <c r="E6" s="16">
-        <f>'IS Cursor'!E3*'Assumptions'!E12</f>
-        <v/>
-      </c>
-      <c r="F6" s="16">
-        <f>'IS Cursor'!F3*'Assumptions'!F12</f>
-        <v/>
-      </c>
-      <c r="G6" s="16">
-        <f>'IS Cursor'!G3*'Assumptions'!G12</f>
-        <v/>
-      </c>
-      <c r="H6" s="16">
-        <f>'IS Cursor'!H3*'Assumptions'!H12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="10" t="inlineStr">
-        <is>
-          <t>Sales &amp; marketing</t>
-        </is>
-      </c>
-      <c r="C7" s="16">
-        <f>'IS Cursor'!C3*'Assumptions'!C13</f>
-        <v/>
-      </c>
-      <c r="D7" s="16">
-        <f>'IS Cursor'!D3*'Assumptions'!D13</f>
-        <v/>
-      </c>
-      <c r="E7" s="16">
-        <f>'IS Cursor'!E3*'Assumptions'!E13</f>
-        <v/>
-      </c>
-      <c r="F7" s="16">
-        <f>'IS Cursor'!F3*'Assumptions'!F13</f>
-        <v/>
-      </c>
-      <c r="G7" s="16">
-        <f>'IS Cursor'!G3*'Assumptions'!G13</f>
-        <v/>
-      </c>
-      <c r="H7" s="16">
-        <f>'IS Cursor'!H3*'Assumptions'!H13</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>General &amp; administrative</t>
-        </is>
-      </c>
-      <c r="C8" s="16">
-        <f>'IS Cursor'!C3*'Assumptions'!C14</f>
-        <v/>
-      </c>
-      <c r="D8" s="16">
-        <f>'IS Cursor'!D3*'Assumptions'!D14</f>
-        <v/>
-      </c>
-      <c r="E8" s="16">
-        <f>'IS Cursor'!E3*'Assumptions'!E14</f>
-        <v/>
-      </c>
-      <c r="F8" s="16">
-        <f>'IS Cursor'!F3*'Assumptions'!F14</f>
-        <v/>
-      </c>
-      <c r="G8" s="16">
-        <f>'IS Cursor'!G3*'Assumptions'!G14</f>
-        <v/>
-      </c>
-      <c r="H8" s="16">
-        <f>'IS Cursor'!H3*'Assumptions'!H14</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>EBITDA (cash)</t>
-        </is>
-      </c>
-      <c r="C9" s="17">
-        <f>'IS Cursor'!C5-'IS Cursor'!C6-'IS Cursor'!C7-'IS Cursor'!C8</f>
-        <v/>
-      </c>
-      <c r="D9" s="17">
-        <f>'IS Cursor'!D5-'IS Cursor'!D6-'IS Cursor'!D7-'IS Cursor'!D8</f>
-        <v/>
-      </c>
-      <c r="E9" s="17">
-        <f>'IS Cursor'!E5-'IS Cursor'!E6-'IS Cursor'!E7-'IS Cursor'!E8</f>
-        <v/>
-      </c>
-      <c r="F9" s="17">
-        <f>'IS Cursor'!F5-'IS Cursor'!F6-'IS Cursor'!F7-'IS Cursor'!F8</f>
-        <v/>
-      </c>
-      <c r="G9" s="17">
-        <f>'IS Cursor'!G5-'IS Cursor'!G6-'IS Cursor'!G7-'IS Cursor'!G8</f>
-        <v/>
-      </c>
-      <c r="H9" s="17">
-        <f>'IS Cursor'!H5-'IS Cursor'!H6-'IS Cursor'!H7-'IS Cursor'!H8</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  EBITDA margin %</t>
-        </is>
-      </c>
-      <c r="C10" s="18">
-        <f>'IS Cursor'!C9/'IS Cursor'!C3</f>
-        <v/>
-      </c>
-      <c r="D10" s="18">
-        <f>'IS Cursor'!D9/'IS Cursor'!D3</f>
-        <v/>
-      </c>
-      <c r="E10" s="18">
-        <f>'IS Cursor'!E9/'IS Cursor'!E3</f>
-        <v/>
-      </c>
-      <c r="F10" s="18">
-        <f>'IS Cursor'!F9/'IS Cursor'!F3</f>
-        <v/>
-      </c>
-      <c r="G10" s="18">
-        <f>'IS Cursor'!G9/'IS Cursor'!G3</f>
-        <v/>
-      </c>
-      <c r="H10" s="18">
-        <f>'IS Cursor'!H9/'IS Cursor'!H3</f>
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2235,8 +2862,8 @@
           <t xml:space="preserve">  SpaceX share price at pricing ($)</t>
         </is>
       </c>
-      <c r="C5" s="19">
-        <f>'Assumptions'!C32</f>
+      <c r="C5" s="21">
+        <f>'Assumptions'!C36</f>
         <v/>
       </c>
     </row>
@@ -2246,7 +2873,7 @@
           <t xml:space="preserve">  New SpaceX shares issued (M)</t>
         </is>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="23">
         <f>'Deal &amp; PPA'!C4/'Deal &amp; PPA'!C5</f>
         <v/>
       </c>
@@ -2362,7 +2989,7 @@
           <t xml:space="preserve">    Useful life (yrs)</t>
         </is>
       </c>
-      <c r="C16" s="21" t="n">
+      <c r="C16" s="24" t="n">
         <v>8</v>
       </c>
     </row>
@@ -2382,7 +3009,7 @@
           <t xml:space="preserve">    Useful life (yrs)</t>
         </is>
       </c>
-      <c r="C18" s="21" t="n">
+      <c r="C18" s="24" t="n">
         <v>10</v>
       </c>
     </row>
@@ -2402,7 +3029,7 @@
           <t xml:space="preserve">    Useful life (yrs)</t>
         </is>
       </c>
-      <c r="C20" s="21" t="n">
+      <c r="C20" s="24" t="n">
         <v>15</v>
       </c>
     </row>
@@ -2452,7 +3079,7 @@
         </is>
       </c>
       <c r="C24" s="16">
-        <f>'Assumptions'!C28*'Deal &amp; PPA'!C21</f>
+        <f>'Assumptions'!C32*'Deal &amp; PPA'!C21</f>
         <v/>
       </c>
     </row>
@@ -2473,7 +3100,7 @@
           <t xml:space="preserve">  Goodwill</t>
         </is>
       </c>
-      <c r="C26" s="22">
+      <c r="C26" s="25">
         <f>'Deal &amp; PPA'!C4-'Deal &amp; PPA'!C25</f>
         <v/>
       </c>
@@ -2483,7 +3110,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2600,27 +3227,27 @@
         </is>
       </c>
       <c r="C5" s="16">
-        <f>'Assumptions'!C20*'Income Statement'!C7</f>
+        <f>'Assumptions'!C21*'Income Statement'!C8</f>
         <v/>
       </c>
       <c r="D5" s="16">
-        <f>'Assumptions'!D20*'Income Statement'!D7</f>
+        <f>'Assumptions'!D21*'Income Statement'!D8</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>'Assumptions'!E20*'Income Statement'!E7</f>
+        <f>'Assumptions'!E21*'Income Statement'!E8</f>
         <v/>
       </c>
       <c r="F5" s="16">
-        <f>'Assumptions'!F20*'Income Statement'!F7</f>
+        <f>'Assumptions'!F21*'Income Statement'!F8</f>
         <v/>
       </c>
       <c r="G5" s="16">
-        <f>'Assumptions'!G20*'Income Statement'!G7</f>
+        <f>'Assumptions'!G21*'Income Statement'!G8</f>
         <v/>
       </c>
       <c r="H5" s="16">
-        <f>'Assumptions'!H20*'Income Statement'!H7</f>
+        <f>'Assumptions'!H21*'Income Statement'!H8</f>
         <v/>
       </c>
     </row>
@@ -2631,27 +3258,27 @@
         </is>
       </c>
       <c r="C6" s="16">
-        <f>'Schedules'!C4*'Assumptions'!C21</f>
+        <f>'Schedules'!C4*'Assumptions'!C22</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>'Schedules'!D4*'Assumptions'!C21</f>
+        <f>'Schedules'!D4*'Assumptions'!C22</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>'Schedules'!E4*'Assumptions'!C21</f>
+        <f>'Schedules'!E4*'Assumptions'!C22</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>'Schedules'!F4*'Assumptions'!C21</f>
+        <f>'Schedules'!F4*'Assumptions'!C22</f>
         <v/>
       </c>
       <c r="G6" s="16">
-        <f>'Schedules'!G4*'Assumptions'!C21</f>
+        <f>'Schedules'!G4*'Assumptions'!C22</f>
         <v/>
       </c>
       <c r="H6" s="16">
-        <f>'Schedules'!H4*'Assumptions'!C21</f>
+        <f>'Schedules'!H4*'Assumptions'!C22</f>
         <v/>
       </c>
     </row>
@@ -2832,23 +3459,23 @@
         <v>0</v>
       </c>
       <c r="D13" s="16">
-        <f>-'Assumptions'!C28*'Schedules'!D10</f>
+        <f>-'Assumptions'!C32*'Schedules'!D10</f>
         <v/>
       </c>
       <c r="E13" s="16">
-        <f>-'Assumptions'!C28*'Schedules'!E10</f>
+        <f>-'Assumptions'!C32*'Schedules'!E10</f>
         <v/>
       </c>
       <c r="F13" s="16">
-        <f>-'Assumptions'!C28*'Schedules'!F10</f>
+        <f>-'Assumptions'!C32*'Schedules'!F10</f>
         <v/>
       </c>
       <c r="G13" s="16">
-        <f>-'Assumptions'!C28*'Schedules'!G10</f>
+        <f>-'Assumptions'!C32*'Schedules'!G10</f>
         <v/>
       </c>
       <c r="H13" s="16">
-        <f>-'Assumptions'!C28*'Schedules'!H10</f>
+        <f>-'Assumptions'!C32*'Schedules'!H10</f>
         <v/>
       </c>
     </row>
@@ -2939,23 +3566,23 @@
         <v>0</v>
       </c>
       <c r="D17" s="16">
-        <f>'Assumptions'!D23</f>
+        <f>'Assumptions'!D27</f>
         <v/>
       </c>
       <c r="E17" s="16">
-        <f>'Assumptions'!E23</f>
+        <f>'Assumptions'!E27</f>
         <v/>
       </c>
       <c r="F17" s="16">
-        <f>'Assumptions'!F23</f>
+        <f>'Assumptions'!F27</f>
         <v/>
       </c>
       <c r="G17" s="16">
-        <f>'Assumptions'!G23</f>
+        <f>'Assumptions'!G27</f>
         <v/>
       </c>
       <c r="H17" s="16">
-        <f>'Assumptions'!H23</f>
+        <f>'Assumptions'!H27</f>
         <v/>
       </c>
     </row>
@@ -3029,23 +3656,23 @@
         <v>0</v>
       </c>
       <c r="D20" s="16">
-        <f>'Assumptions'!D24</f>
+        <f>'Assumptions'!D28</f>
         <v/>
       </c>
       <c r="E20" s="16">
-        <f>'Assumptions'!E24</f>
+        <f>'Assumptions'!E28</f>
         <v/>
       </c>
       <c r="F20" s="16">
-        <f>'Assumptions'!F24</f>
+        <f>'Assumptions'!F28</f>
         <v/>
       </c>
       <c r="G20" s="16">
-        <f>'Assumptions'!G24</f>
+        <f>'Assumptions'!G28</f>
         <v/>
       </c>
       <c r="H20" s="16">
-        <f>'Assumptions'!H24</f>
+        <f>'Assumptions'!H28</f>
         <v/>
       </c>
     </row>
@@ -3086,27 +3713,27 @@
         </is>
       </c>
       <c r="C22" s="17">
-        <f>('Schedules'!C16+'Schedules'!C19)*'Assumptions'!C26</f>
+        <f>('Schedules'!C16+'Schedules'!C19)*'Assumptions'!C30</f>
         <v/>
       </c>
       <c r="D22" s="17">
-        <f>('Schedules'!D16+'Schedules'!D19)*'Assumptions'!C26</f>
+        <f>('Schedules'!D16+'Schedules'!D19)*'Assumptions'!C30</f>
         <v/>
       </c>
       <c r="E22" s="17">
-        <f>('Schedules'!E16+'Schedules'!E19)*'Assumptions'!C26</f>
+        <f>('Schedules'!E16+'Schedules'!E19)*'Assumptions'!C30</f>
         <v/>
       </c>
       <c r="F22" s="17">
-        <f>('Schedules'!F16+'Schedules'!F19)*'Assumptions'!C26</f>
+        <f>('Schedules'!F16+'Schedules'!F19)*'Assumptions'!C30</f>
         <v/>
       </c>
       <c r="G22" s="17">
-        <f>('Schedules'!G16+'Schedules'!G19)*'Assumptions'!C26</f>
+        <f>('Schedules'!G16+'Schedules'!G19)*'Assumptions'!C30</f>
         <v/>
       </c>
       <c r="H22" s="17">
-        <f>('Schedules'!H16+'Schedules'!H19)*'Assumptions'!C26</f>
+        <f>('Schedules'!H16+'Schedules'!H19)*'Assumptions'!C30</f>
         <v/>
       </c>
     </row>
@@ -3196,7 +3823,7 @@
         </is>
       </c>
       <c r="C26" s="16">
-        <f>'Assumptions'!C29</f>
+        <f>'Assumptions'!C33</f>
         <v/>
       </c>
       <c r="D26" s="16">
@@ -3227,27 +3854,27 @@
         </is>
       </c>
       <c r="C27" s="16">
-        <f>MIN('Schedules'!C26,'Assumptions'!C30*MAX(0,'Schedules'!C25))</f>
+        <f>MIN('Schedules'!C26,'Assumptions'!C34*MAX(0,'Schedules'!C25))</f>
         <v/>
       </c>
       <c r="D27" s="16">
-        <f>MIN('Schedules'!D26,'Assumptions'!C30*MAX(0,'Schedules'!D25))</f>
+        <f>MIN('Schedules'!D26,'Assumptions'!C34*MAX(0,'Schedules'!D25))</f>
         <v/>
       </c>
       <c r="E27" s="16">
-        <f>MIN('Schedules'!E26,'Assumptions'!C30*MAX(0,'Schedules'!E25))</f>
+        <f>MIN('Schedules'!E26,'Assumptions'!C34*MAX(0,'Schedules'!E25))</f>
         <v/>
       </c>
       <c r="F27" s="16">
-        <f>MIN('Schedules'!F26,'Assumptions'!C30*MAX(0,'Schedules'!F25))</f>
+        <f>MIN('Schedules'!F26,'Assumptions'!C34*MAX(0,'Schedules'!F25))</f>
         <v/>
       </c>
       <c r="G27" s="16">
-        <f>MIN('Schedules'!G26,'Assumptions'!C30*MAX(0,'Schedules'!G25))</f>
+        <f>MIN('Schedules'!G26,'Assumptions'!C34*MAX(0,'Schedules'!G25))</f>
         <v/>
       </c>
       <c r="H27" s="16">
-        <f>MIN('Schedules'!H26,'Assumptions'!C30*MAX(0,'Schedules'!H25))</f>
+        <f>MIN('Schedules'!H26,'Assumptions'!C34*MAX(0,'Schedules'!H25))</f>
         <v/>
       </c>
     </row>
@@ -3320,27 +3947,27 @@
         </is>
       </c>
       <c r="C30" s="17">
-        <f>'Assumptions'!C28*MAX(0,'Schedules'!C25-'Schedules'!C27)</f>
+        <f>'Assumptions'!C32*MAX(0,'Schedules'!C25-'Schedules'!C27)</f>
         <v/>
       </c>
       <c r="D30" s="17">
-        <f>'Assumptions'!C28*MAX(0,'Schedules'!D25-'Schedules'!D27)</f>
+        <f>'Assumptions'!C32*MAX(0,'Schedules'!D25-'Schedules'!D27)</f>
         <v/>
       </c>
       <c r="E30" s="17">
-        <f>'Assumptions'!C28*MAX(0,'Schedules'!E25-'Schedules'!E27)</f>
+        <f>'Assumptions'!C32*MAX(0,'Schedules'!E25-'Schedules'!E27)</f>
         <v/>
       </c>
       <c r="F30" s="17">
-        <f>'Assumptions'!C28*MAX(0,'Schedules'!F25-'Schedules'!F27)</f>
+        <f>'Assumptions'!C32*MAX(0,'Schedules'!F25-'Schedules'!F27)</f>
         <v/>
       </c>
       <c r="G30" s="17">
-        <f>'Assumptions'!C28*MAX(0,'Schedules'!G25-'Schedules'!G27)</f>
+        <f>'Assumptions'!C32*MAX(0,'Schedules'!G25-'Schedules'!G27)</f>
         <v/>
       </c>
       <c r="H30" s="17">
-        <f>'Assumptions'!C28*MAX(0,'Schedules'!H25-'Schedules'!H27)</f>
+        <f>'Assumptions'!C32*MAX(0,'Schedules'!H25-'Schedules'!H27)</f>
         <v/>
       </c>
     </row>
@@ -3349,13 +3976,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:K33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3420,376 +4047,334 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t>Revenue — SpaceX</t>
-        </is>
-      </c>
-      <c r="C4" s="16">
-        <f>'IS SpaceX'!C3</f>
-        <v/>
-      </c>
-      <c r="D4" s="16">
-        <f>'IS SpaceX'!D3</f>
-        <v/>
-      </c>
-      <c r="E4" s="16">
-        <f>'IS SpaceX'!E3</f>
-        <v/>
-      </c>
-      <c r="F4" s="16">
-        <f>'IS SpaceX'!F3</f>
-        <v/>
-      </c>
-      <c r="G4" s="16">
-        <f>'IS SpaceX'!G3</f>
-        <v/>
-      </c>
-      <c r="H4" s="16">
-        <f>'IS SpaceX'!H3</f>
-        <v/>
-      </c>
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>Revenue by segment</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="9" t="n"/>
+      <c r="G4" s="9" t="n"/>
+      <c r="H4" s="9" t="n"/>
+      <c r="I4" s="9" t="n"/>
+      <c r="J4" s="9" t="n"/>
+      <c r="K4" s="9" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t>Revenue — Cursor</t>
+          <t xml:space="preserve">  Space</t>
         </is>
       </c>
       <c r="C5" s="16">
-        <f>'IS Cursor'!C3</f>
+        <f>'Segments'!C5</f>
         <v/>
       </c>
       <c r="D5" s="16">
-        <f>'IS Cursor'!D3</f>
+        <f>'Segments'!D5</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>'IS Cursor'!E3</f>
+        <f>'Segments'!E5</f>
         <v/>
       </c>
       <c r="F5" s="16">
-        <f>'IS Cursor'!F3</f>
+        <f>'Segments'!F5</f>
         <v/>
       </c>
       <c r="G5" s="16">
-        <f>'IS Cursor'!G3</f>
+        <f>'Segments'!G5</f>
         <v/>
       </c>
       <c r="H5" s="16">
-        <f>'IS Cursor'!H3</f>
+        <f>'Segments'!H5</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t>Revenue synergies</t>
+          <t xml:space="preserve">  Starlink</t>
         </is>
       </c>
       <c r="C6" s="16">
-        <f>'Assumptions'!C16</f>
+        <f>'Segments'!C6</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>'Assumptions'!D16</f>
+        <f>'Segments'!D6</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>'Assumptions'!E16</f>
+        <f>'Segments'!E6</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>'Assumptions'!F16</f>
+        <f>'Segments'!F6</f>
         <v/>
       </c>
       <c r="G6" s="16">
-        <f>'Assumptions'!G16</f>
+        <f>'Segments'!G6</f>
         <v/>
       </c>
       <c r="H6" s="16">
-        <f>'Assumptions'!H16</f>
+        <f>'Segments'!H6</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  xAI-Cursor</t>
+        </is>
+      </c>
+      <c r="C7" s="16">
+        <f>'Segments'!C9</f>
+        <v/>
+      </c>
+      <c r="D7" s="16">
+        <f>'Segments'!D9</f>
+        <v/>
+      </c>
+      <c r="E7" s="16">
+        <f>'Segments'!E9</f>
+        <v/>
+      </c>
+      <c r="F7" s="16">
+        <f>'Segments'!F9</f>
+        <v/>
+      </c>
+      <c r="G7" s="16">
+        <f>'Segments'!G9</f>
+        <v/>
+      </c>
+      <c r="H7" s="16">
+        <f>'Segments'!H9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Total revenue</t>
         </is>
       </c>
-      <c r="C7" s="17">
-        <f>'Income Statement'!C4+'Income Statement'!C5+'Income Statement'!C6</f>
-        <v/>
-      </c>
-      <c r="D7" s="17">
-        <f>'Income Statement'!D4+'Income Statement'!D5+'Income Statement'!D6</f>
-        <v/>
-      </c>
-      <c r="E7" s="17">
-        <f>'Income Statement'!E4+'Income Statement'!E5+'Income Statement'!E6</f>
-        <v/>
-      </c>
-      <c r="F7" s="17">
-        <f>'Income Statement'!F4+'Income Statement'!F5+'Income Statement'!F6</f>
-        <v/>
-      </c>
-      <c r="G7" s="17">
-        <f>'Income Statement'!G4+'Income Statement'!G5+'Income Statement'!G6</f>
-        <v/>
-      </c>
-      <c r="H7" s="17">
-        <f>'Income Statement'!H4+'Income Statement'!H5+'Income Statement'!H6</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="10" t="inlineStr">
-        <is>
-          <t>Cost of revenue (net of cost synergies)</t>
-        </is>
-      </c>
-      <c r="C8" s="16">
-        <f>'IS SpaceX'!C4+'IS Cursor'!C4-'Assumptions'!C17</f>
-        <v/>
-      </c>
-      <c r="D8" s="16">
-        <f>'IS SpaceX'!D4+'IS Cursor'!D4-'Assumptions'!D17</f>
-        <v/>
-      </c>
-      <c r="E8" s="16">
-        <f>'IS SpaceX'!E4+'IS Cursor'!E4-'Assumptions'!E17</f>
-        <v/>
-      </c>
-      <c r="F8" s="16">
-        <f>'IS SpaceX'!F4+'IS Cursor'!F4-'Assumptions'!F17</f>
-        <v/>
-      </c>
-      <c r="G8" s="16">
-        <f>'IS SpaceX'!G4+'IS Cursor'!G4-'Assumptions'!G17</f>
-        <v/>
-      </c>
-      <c r="H8" s="16">
-        <f>'IS SpaceX'!H4+'IS Cursor'!H4-'Assumptions'!H17</f>
+      <c r="C8" s="17">
+        <f>'Segments'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="17">
+        <f>'Segments'!D10</f>
+        <v/>
+      </c>
+      <c r="E8" s="17">
+        <f>'Segments'!E10</f>
+        <v/>
+      </c>
+      <c r="F8" s="17">
+        <f>'Segments'!F10</f>
+        <v/>
+      </c>
+      <c r="G8" s="17">
+        <f>'Segments'!G10</f>
+        <v/>
+      </c>
+      <c r="H8" s="17">
+        <f>'Segments'!H10</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Gross profit</t>
-        </is>
-      </c>
-      <c r="C9" s="17">
-        <f>'Income Statement'!C7-'Income Statement'!C8</f>
-        <v/>
-      </c>
-      <c r="D9" s="17">
-        <f>'Income Statement'!D7-'Income Statement'!D8</f>
-        <v/>
-      </c>
-      <c r="E9" s="17">
-        <f>'Income Statement'!E7-'Income Statement'!E8</f>
-        <v/>
-      </c>
-      <c r="F9" s="17">
-        <f>'Income Statement'!F7-'Income Statement'!F8</f>
-        <v/>
-      </c>
-      <c r="G9" s="17">
-        <f>'Income Statement'!G7-'Income Statement'!G8</f>
-        <v/>
-      </c>
-      <c r="H9" s="17">
-        <f>'Income Statement'!H7-'Income Statement'!H8</f>
-        <v/>
-      </c>
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>EBITDA by segment</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="9" t="n"/>
+      <c r="G9" s="9" t="n"/>
+      <c r="H9" s="9" t="n"/>
+      <c r="I9" s="9" t="n"/>
+      <c r="J9" s="9" t="n"/>
+      <c r="K9" s="9" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Gross margin %</t>
-        </is>
-      </c>
-      <c r="C10" s="18">
-        <f>'Income Statement'!C9/'Income Statement'!C7</f>
-        <v/>
-      </c>
-      <c r="D10" s="18">
-        <f>'Income Statement'!D9/'Income Statement'!D7</f>
-        <v/>
-      </c>
-      <c r="E10" s="18">
-        <f>'Income Statement'!E9/'Income Statement'!E7</f>
-        <v/>
-      </c>
-      <c r="F10" s="18">
-        <f>'Income Statement'!F9/'Income Statement'!F7</f>
-        <v/>
-      </c>
-      <c r="G10" s="18">
-        <f>'Income Statement'!G9/'Income Statement'!G7</f>
-        <v/>
-      </c>
-      <c r="H10" s="18">
-        <f>'Income Statement'!H9/'Income Statement'!H7</f>
+          <t xml:space="preserve">  Space</t>
+        </is>
+      </c>
+      <c r="C10" s="16">
+        <f>'Segments'!C12</f>
+        <v/>
+      </c>
+      <c r="D10" s="16">
+        <f>'Segments'!D12</f>
+        <v/>
+      </c>
+      <c r="E10" s="16">
+        <f>'Segments'!E12</f>
+        <v/>
+      </c>
+      <c r="F10" s="16">
+        <f>'Segments'!F12</f>
+        <v/>
+      </c>
+      <c r="G10" s="16">
+        <f>'Segments'!G12</f>
+        <v/>
+      </c>
+      <c r="H10" s="16">
+        <f>'Segments'!H12</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="10" t="inlineStr">
         <is>
-          <t>Research &amp; development</t>
+          <t xml:space="preserve">  Starlink</t>
         </is>
       </c>
       <c r="C11" s="16">
-        <f>'IS SpaceX'!C6+'IS Cursor'!C6</f>
+        <f>'Segments'!C13</f>
         <v/>
       </c>
       <c r="D11" s="16">
-        <f>'IS SpaceX'!D6+'IS Cursor'!D6</f>
+        <f>'Segments'!D13</f>
         <v/>
       </c>
       <c r="E11" s="16">
-        <f>'IS SpaceX'!E6+'IS Cursor'!E6</f>
+        <f>'Segments'!E13</f>
         <v/>
       </c>
       <c r="F11" s="16">
-        <f>'IS SpaceX'!F6+'IS Cursor'!F6</f>
+        <f>'Segments'!F13</f>
         <v/>
       </c>
       <c r="G11" s="16">
-        <f>'IS SpaceX'!G6+'IS Cursor'!G6</f>
+        <f>'Segments'!G13</f>
         <v/>
       </c>
       <c r="H11" s="16">
-        <f>'IS SpaceX'!H6+'IS Cursor'!H6</f>
+        <f>'Segments'!H13</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Selling, general &amp; administrative</t>
+          <t xml:space="preserve">  xAI-Cursor (incl. synergies, integration)</t>
         </is>
       </c>
       <c r="C12" s="16">
-        <f>'IS SpaceX'!C7+'IS Cursor'!C7+'IS Cursor'!C8</f>
+        <f>'Segments'!C14</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>'IS SpaceX'!D7+'IS Cursor'!D7+'IS Cursor'!D8</f>
+        <f>'Segments'!D14</f>
         <v/>
       </c>
       <c r="E12" s="16">
-        <f>'IS SpaceX'!E7+'IS Cursor'!E7+'IS Cursor'!E8</f>
+        <f>'Segments'!E14</f>
         <v/>
       </c>
       <c r="F12" s="16">
-        <f>'IS SpaceX'!F7+'IS Cursor'!F7+'IS Cursor'!F8</f>
+        <f>'Segments'!F14</f>
         <v/>
       </c>
       <c r="G12" s="16">
-        <f>'IS SpaceX'!G7+'IS Cursor'!G7+'IS Cursor'!G8</f>
+        <f>'Segments'!G14</f>
         <v/>
       </c>
       <c r="H12" s="16">
-        <f>'IS SpaceX'!H7+'IS Cursor'!H7+'IS Cursor'!H8</f>
+        <f>'Segments'!H14</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t>Integration &amp; one-time deal costs</t>
-        </is>
-      </c>
-      <c r="C13" s="16">
-        <f>'Assumptions'!C18</f>
-        <v/>
-      </c>
-      <c r="D13" s="16">
-        <f>'Assumptions'!D18</f>
-        <v/>
-      </c>
-      <c r="E13" s="16">
-        <f>'Assumptions'!E18</f>
-        <v/>
-      </c>
-      <c r="F13" s="16">
-        <f>'Assumptions'!F18</f>
-        <v/>
-      </c>
-      <c r="G13" s="16">
-        <f>'Assumptions'!G18</f>
-        <v/>
-      </c>
-      <c r="H13" s="16">
-        <f>'Assumptions'!H18</f>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>Total EBITDA</t>
+        </is>
+      </c>
+      <c r="C13" s="17">
+        <f>'Segments'!C15</f>
+        <v/>
+      </c>
+      <c r="D13" s="17">
+        <f>'Segments'!D15</f>
+        <v/>
+      </c>
+      <c r="E13" s="17">
+        <f>'Segments'!E15</f>
+        <v/>
+      </c>
+      <c r="F13" s="17">
+        <f>'Segments'!F15</f>
+        <v/>
+      </c>
+      <c r="G13" s="17">
+        <f>'Segments'!G15</f>
+        <v/>
+      </c>
+      <c r="H13" s="17">
+        <f>'Segments'!H15</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>EBITDA</t>
-        </is>
-      </c>
-      <c r="C14" s="17">
-        <f>'Income Statement'!C9-'Income Statement'!C11-'Income Statement'!C12-'Income Statement'!C13</f>
-        <v/>
-      </c>
-      <c r="D14" s="17">
-        <f>'Income Statement'!D9-'Income Statement'!D11-'Income Statement'!D12-'Income Statement'!D13</f>
-        <v/>
-      </c>
-      <c r="E14" s="17">
-        <f>'Income Statement'!E9-'Income Statement'!E11-'Income Statement'!E12-'Income Statement'!E13</f>
-        <v/>
-      </c>
-      <c r="F14" s="17">
-        <f>'Income Statement'!F9-'Income Statement'!F11-'Income Statement'!F12-'Income Statement'!F13</f>
-        <v/>
-      </c>
-      <c r="G14" s="17">
-        <f>'Income Statement'!G9-'Income Statement'!G11-'Income Statement'!G12-'Income Statement'!G13</f>
-        <v/>
-      </c>
-      <c r="H14" s="17">
-        <f>'Income Statement'!H9-'Income Statement'!H11-'Income Statement'!H12-'Income Statement'!H13</f>
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  EBITDA margin %</t>
+        </is>
+      </c>
+      <c r="C14" s="18">
+        <f>'Income Statement'!C13/'Income Statement'!C8</f>
+        <v/>
+      </c>
+      <c r="D14" s="18">
+        <f>'Income Statement'!D13/'Income Statement'!D8</f>
+        <v/>
+      </c>
+      <c r="E14" s="18">
+        <f>'Income Statement'!E13/'Income Statement'!E8</f>
+        <v/>
+      </c>
+      <c r="F14" s="18">
+        <f>'Income Statement'!F13/'Income Statement'!F8</f>
+        <v/>
+      </c>
+      <c r="G14" s="18">
+        <f>'Income Statement'!G13/'Income Statement'!G8</f>
+        <v/>
+      </c>
+      <c r="H14" s="18">
+        <f>'Income Statement'!H13/'Income Statement'!H8</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  EBITDA margin %</t>
-        </is>
-      </c>
-      <c r="C15" s="18">
-        <f>'Income Statement'!C14/'Income Statement'!C7</f>
-        <v/>
-      </c>
-      <c r="D15" s="18">
-        <f>'Income Statement'!D14/'Income Statement'!D7</f>
-        <v/>
-      </c>
-      <c r="E15" s="18">
-        <f>'Income Statement'!E14/'Income Statement'!E7</f>
-        <v/>
-      </c>
-      <c r="F15" s="18">
-        <f>'Income Statement'!F14/'Income Statement'!F7</f>
-        <v/>
-      </c>
-      <c r="G15" s="18">
-        <f>'Income Statement'!G14/'Income Statement'!G7</f>
-        <v/>
-      </c>
-      <c r="H15" s="18">
-        <f>'Income Statement'!H14/'Income Statement'!H7</f>
-        <v/>
-      </c>
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Consolidated P&amp;L</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
+      <c r="H15" s="9" t="n"/>
+      <c r="I15" s="9" t="n"/>
+      <c r="J15" s="9" t="n"/>
+      <c r="K15" s="9" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
@@ -3860,27 +4445,27 @@
         </is>
       </c>
       <c r="C18" s="17">
-        <f>'Income Statement'!C14-'Income Statement'!C16-'Income Statement'!C17</f>
+        <f>'Income Statement'!C13-'Income Statement'!C16-'Income Statement'!C17</f>
         <v/>
       </c>
       <c r="D18" s="17">
-        <f>'Income Statement'!D14-'Income Statement'!D16-'Income Statement'!D17</f>
+        <f>'Income Statement'!D13-'Income Statement'!D16-'Income Statement'!D17</f>
         <v/>
       </c>
       <c r="E18" s="17">
-        <f>'Income Statement'!E14-'Income Statement'!E16-'Income Statement'!E17</f>
+        <f>'Income Statement'!E13-'Income Statement'!E16-'Income Statement'!E17</f>
         <v/>
       </c>
       <c r="F18" s="17">
-        <f>'Income Statement'!F14-'Income Statement'!F16-'Income Statement'!F17</f>
+        <f>'Income Statement'!F13-'Income Statement'!F16-'Income Statement'!F17</f>
         <v/>
       </c>
       <c r="G18" s="17">
-        <f>'Income Statement'!G14-'Income Statement'!G16-'Income Statement'!G17</f>
+        <f>'Income Statement'!G13-'Income Statement'!G16-'Income Statement'!G17</f>
         <v/>
       </c>
       <c r="H18" s="17">
-        <f>'Income Statement'!H14-'Income Statement'!H16-'Income Statement'!H17</f>
+        <f>'Income Statement'!H13-'Income Statement'!H16-'Income Statement'!H17</f>
         <v/>
       </c>
     </row>
@@ -3891,27 +4476,27 @@
         </is>
       </c>
       <c r="C19" s="18">
-        <f>'Income Statement'!C18/'Income Statement'!C7</f>
+        <f>'Income Statement'!C18/'Income Statement'!C8</f>
         <v/>
       </c>
       <c r="D19" s="18">
-        <f>'Income Statement'!D18/'Income Statement'!D7</f>
+        <f>'Income Statement'!D18/'Income Statement'!D8</f>
         <v/>
       </c>
       <c r="E19" s="18">
-        <f>'Income Statement'!E18/'Income Statement'!E7</f>
+        <f>'Income Statement'!E18/'Income Statement'!E8</f>
         <v/>
       </c>
       <c r="F19" s="18">
-        <f>'Income Statement'!F18/'Income Statement'!F7</f>
+        <f>'Income Statement'!F18/'Income Statement'!F8</f>
         <v/>
       </c>
       <c r="G19" s="18">
-        <f>'Income Statement'!G18/'Income Statement'!G7</f>
+        <f>'Income Statement'!G18/'Income Statement'!G8</f>
         <v/>
       </c>
       <c r="H19" s="18">
-        <f>'Income Statement'!H18/'Income Statement'!H7</f>
+        <f>'Income Statement'!H18/'Income Statement'!H8</f>
         <v/>
       </c>
     </row>
@@ -3953,27 +4538,27 @@
         </is>
       </c>
       <c r="C21" s="16">
-        <f>12000*'Assumptions'!C27</f>
+        <f>12000*'Assumptions'!C31</f>
         <v/>
       </c>
       <c r="D21" s="16">
-        <f>'Balance Sheet'!F4*'Assumptions'!C27</f>
+        <f>'Balance Sheet'!F4*'Assumptions'!C31</f>
         <v/>
       </c>
       <c r="E21" s="16">
-        <f>'Balance Sheet'!G4*'Assumptions'!C27</f>
+        <f>'Balance Sheet'!G4*'Assumptions'!C31</f>
         <v/>
       </c>
       <c r="F21" s="16">
-        <f>'Balance Sheet'!H4*'Assumptions'!C27</f>
+        <f>'Balance Sheet'!H4*'Assumptions'!C31</f>
         <v/>
       </c>
       <c r="G21" s="16">
-        <f>'Balance Sheet'!I4*'Assumptions'!C27</f>
+        <f>'Balance Sheet'!I4*'Assumptions'!C31</f>
         <v/>
       </c>
       <c r="H21" s="16">
-        <f>'Balance Sheet'!J4*'Assumptions'!C27</f>
+        <f>'Balance Sheet'!J4*'Assumptions'!C31</f>
         <v/>
       </c>
     </row>
@@ -4108,27 +4693,27 @@
         </is>
       </c>
       <c r="C26" s="18">
-        <f>'Income Statement'!C25/'Income Statement'!C7</f>
+        <f>'Income Statement'!C25/'Income Statement'!C8</f>
         <v/>
       </c>
       <c r="D26" s="18">
-        <f>'Income Statement'!D25/'Income Statement'!D7</f>
+        <f>'Income Statement'!D25/'Income Statement'!D8</f>
         <v/>
       </c>
       <c r="E26" s="18">
-        <f>'Income Statement'!E25/'Income Statement'!E7</f>
+        <f>'Income Statement'!E25/'Income Statement'!E8</f>
         <v/>
       </c>
       <c r="F26" s="18">
-        <f>'Income Statement'!F25/'Income Statement'!F7</f>
+        <f>'Income Statement'!F25/'Income Statement'!F8</f>
         <v/>
       </c>
       <c r="G26" s="18">
-        <f>'Income Statement'!G25/'Income Statement'!G7</f>
+        <f>'Income Statement'!G25/'Income Statement'!G8</f>
         <v/>
       </c>
       <c r="H26" s="18">
-        <f>'Income Statement'!H25/'Income Statement'!H7</f>
+        <f>'Income Statement'!H25/'Income Statement'!H8</f>
         <v/>
       </c>
     </row>
@@ -4138,59 +4723,200 @@
           <t>Diluted shares outstanding (M)</t>
         </is>
       </c>
-      <c r="C27" s="20">
-        <f>'Assumptions'!C31+'Deal &amp; PPA'!C6</f>
-        <v/>
-      </c>
-      <c r="D27" s="20">
-        <f>'Assumptions'!C31+'Deal &amp; PPA'!C6</f>
-        <v/>
-      </c>
-      <c r="E27" s="20">
-        <f>'Assumptions'!C31+'Deal &amp; PPA'!C6</f>
-        <v/>
-      </c>
-      <c r="F27" s="20">
-        <f>'Assumptions'!C31+'Deal &amp; PPA'!C6</f>
-        <v/>
-      </c>
-      <c r="G27" s="20">
-        <f>'Assumptions'!C31+'Deal &amp; PPA'!C6</f>
-        <v/>
-      </c>
-      <c r="H27" s="20">
-        <f>'Assumptions'!C31+'Deal &amp; PPA'!C6</f>
+      <c r="C27" s="23">
+        <f>'Assumptions'!C35+'Deal &amp; PPA'!C6</f>
+        <v/>
+      </c>
+      <c r="D27" s="23">
+        <f>'Assumptions'!C35+'Deal &amp; PPA'!C6</f>
+        <v/>
+      </c>
+      <c r="E27" s="23">
+        <f>'Assumptions'!C35+'Deal &amp; PPA'!C6</f>
+        <v/>
+      </c>
+      <c r="F27" s="23">
+        <f>'Assumptions'!C35+'Deal &amp; PPA'!C6</f>
+        <v/>
+      </c>
+      <c r="G27" s="23">
+        <f>'Assumptions'!C35+'Deal &amp; PPA'!C6</f>
+        <v/>
+      </c>
+      <c r="H27" s="23">
+        <f>'Assumptions'!C35+'Deal &amp; PPA'!C6</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="10" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>Diluted EPS ($)</t>
         </is>
       </c>
-      <c r="C28" s="19">
+      <c r="C28" s="22">
         <f>'Income Statement'!C25/'Income Statement'!C27</f>
         <v/>
       </c>
-      <c r="D28" s="19">
+      <c r="D28" s="22">
         <f>'Income Statement'!D25/'Income Statement'!D27</f>
         <v/>
       </c>
-      <c r="E28" s="19">
+      <c r="E28" s="22">
         <f>'Income Statement'!E25/'Income Statement'!E27</f>
         <v/>
       </c>
-      <c r="F28" s="19">
+      <c r="F28" s="22">
         <f>'Income Statement'!F25/'Income Statement'!F27</f>
         <v/>
       </c>
-      <c r="G28" s="19">
+      <c r="G28" s="22">
         <f>'Income Statement'!G25/'Income Statement'!G27</f>
         <v/>
       </c>
-      <c r="H28" s="19">
+      <c r="H28" s="22">
         <f>'Income Statement'!H25/'Income Statement'!H27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>EPS contribution by segment ($)</t>
+        </is>
+      </c>
+      <c r="B29" s="9" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="9" t="n"/>
+      <c r="G29" s="9" t="n"/>
+      <c r="H29" s="9" t="n"/>
+      <c r="I29" s="9" t="n"/>
+      <c r="J29" s="9" t="n"/>
+      <c r="K29" s="9" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Space</t>
+        </is>
+      </c>
+      <c r="C30" s="21">
+        <f>'Segments'!C28</f>
+        <v/>
+      </c>
+      <c r="D30" s="21">
+        <f>'Segments'!D28</f>
+        <v/>
+      </c>
+      <c r="E30" s="21">
+        <f>'Segments'!E28</f>
+        <v/>
+      </c>
+      <c r="F30" s="21">
+        <f>'Segments'!F28</f>
+        <v/>
+      </c>
+      <c r="G30" s="21">
+        <f>'Segments'!G28</f>
+        <v/>
+      </c>
+      <c r="H30" s="21">
+        <f>'Segments'!H28</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Starlink</t>
+        </is>
+      </c>
+      <c r="C31" s="21">
+        <f>'Segments'!C38</f>
+        <v/>
+      </c>
+      <c r="D31" s="21">
+        <f>'Segments'!D38</f>
+        <v/>
+      </c>
+      <c r="E31" s="21">
+        <f>'Segments'!E38</f>
+        <v/>
+      </c>
+      <c r="F31" s="21">
+        <f>'Segments'!F38</f>
+        <v/>
+      </c>
+      <c r="G31" s="21">
+        <f>'Segments'!G38</f>
+        <v/>
+      </c>
+      <c r="H31" s="21">
+        <f>'Segments'!H38</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  xAI-Cursor</t>
+        </is>
+      </c>
+      <c r="C32" s="21">
+        <f>'Segments'!C48</f>
+        <v/>
+      </c>
+      <c r="D32" s="21">
+        <f>'Segments'!D48</f>
+        <v/>
+      </c>
+      <c r="E32" s="21">
+        <f>'Segments'!E48</f>
+        <v/>
+      </c>
+      <c r="F32" s="21">
+        <f>'Segments'!F48</f>
+        <v/>
+      </c>
+      <c r="G32" s="21">
+        <f>'Segments'!G48</f>
+        <v/>
+      </c>
+      <c r="H32" s="21">
+        <f>'Segments'!H48</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Total (= diluted EPS)</t>
+        </is>
+      </c>
+      <c r="C33" s="22">
+        <f>'Segments'!C50</f>
+        <v/>
+      </c>
+      <c r="D33" s="22">
+        <f>'Segments'!D50</f>
+        <v/>
+      </c>
+      <c r="E33" s="22">
+        <f>'Segments'!E50</f>
+        <v/>
+      </c>
+      <c r="F33" s="22">
+        <f>'Segments'!F50</f>
+        <v/>
+      </c>
+      <c r="G33" s="22">
+        <f>'Segments'!G50</f>
+        <v/>
+      </c>
+      <c r="H33" s="22">
+        <f>'Segments'!H50</f>
         <v/>
       </c>
     </row>
@@ -4199,7 +4925,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4231,47 +4957,47 @@
     </row>
     <row r="2">
       <c r="A2" t="inlineStr"/>
-      <c r="C2" s="23" t="inlineStr">
+      <c r="C2" s="26" t="inlineStr">
         <is>
           <t>SpaceX 2025A</t>
         </is>
       </c>
-      <c r="D2" s="23" t="inlineStr">
+      <c r="D2" s="26" t="inlineStr">
         <is>
           <t>+ Cursor</t>
         </is>
       </c>
-      <c r="E2" s="23" t="inlineStr">
+      <c r="E2" s="26" t="inlineStr">
         <is>
           <t>+ Purch. acctg</t>
         </is>
       </c>
-      <c r="F2" s="23" t="inlineStr">
+      <c r="F2" s="26" t="inlineStr">
         <is>
           <t>PF Open 1/1/26</t>
         </is>
       </c>
-      <c r="G2" s="23" t="inlineStr">
+      <c r="G2" s="26" t="inlineStr">
         <is>
           <t>2026E</t>
         </is>
       </c>
-      <c r="H2" s="23" t="inlineStr">
+      <c r="H2" s="26" t="inlineStr">
         <is>
           <t>2027E</t>
         </is>
       </c>
-      <c r="I2" s="23" t="inlineStr">
+      <c r="I2" s="26" t="inlineStr">
         <is>
           <t>2028E</t>
         </is>
       </c>
-      <c r="J2" s="23" t="inlineStr">
+      <c r="J2" s="26" t="inlineStr">
         <is>
           <t>2029E</t>
         </is>
       </c>
-      <c r="K2" s="23" t="inlineStr">
+      <c r="K2" s="26" t="inlineStr">
         <is>
           <t>2030E</t>
         </is>
@@ -4354,23 +5080,23 @@
         <v/>
       </c>
       <c r="G5" s="16">
-        <f>'Income Statement'!D7*'Assumptions'!C34</f>
+        <f>'Income Statement'!D8*'Assumptions'!C38</f>
         <v/>
       </c>
       <c r="H5" s="16">
-        <f>'Income Statement'!E7*'Assumptions'!C34</f>
+        <f>'Income Statement'!E8*'Assumptions'!C38</f>
         <v/>
       </c>
       <c r="I5" s="16">
-        <f>'Income Statement'!F7*'Assumptions'!C34</f>
+        <f>'Income Statement'!F8*'Assumptions'!C38</f>
         <v/>
       </c>
       <c r="J5" s="16">
-        <f>'Income Statement'!G7*'Assumptions'!C34</f>
+        <f>'Income Statement'!G8*'Assumptions'!C38</f>
         <v/>
       </c>
       <c r="K5" s="16">
-        <f>'Income Statement'!H7*'Assumptions'!C34</f>
+        <f>'Income Statement'!H8*'Assumptions'!C38</f>
         <v/>
       </c>
     </row>
@@ -4394,23 +5120,23 @@
         <v/>
       </c>
       <c r="G6" s="16">
-        <f>'Income Statement'!D7*'Assumptions'!C35</f>
+        <f>'Income Statement'!D8*'Assumptions'!C39</f>
         <v/>
       </c>
       <c r="H6" s="16">
-        <f>'Income Statement'!E7*'Assumptions'!C35</f>
+        <f>'Income Statement'!E8*'Assumptions'!C39</f>
         <v/>
       </c>
       <c r="I6" s="16">
-        <f>'Income Statement'!F7*'Assumptions'!C35</f>
+        <f>'Income Statement'!F8*'Assumptions'!C39</f>
         <v/>
       </c>
       <c r="J6" s="16">
-        <f>'Income Statement'!G7*'Assumptions'!C35</f>
+        <f>'Income Statement'!G8*'Assumptions'!C39</f>
         <v/>
       </c>
       <c r="K6" s="16">
-        <f>'Income Statement'!H7*'Assumptions'!C35</f>
+        <f>'Income Statement'!H8*'Assumptions'!C39</f>
         <v/>
       </c>
     </row>
@@ -4434,23 +5160,23 @@
         <v/>
       </c>
       <c r="G7" s="16">
-        <f>'Income Statement'!D7*'Assumptions'!C36</f>
+        <f>'Income Statement'!D8*'Assumptions'!C40</f>
         <v/>
       </c>
       <c r="H7" s="16">
-        <f>'Income Statement'!E7*'Assumptions'!C36</f>
+        <f>'Income Statement'!E8*'Assumptions'!C40</f>
         <v/>
       </c>
       <c r="I7" s="16">
-        <f>'Income Statement'!F7*'Assumptions'!C36</f>
+        <f>'Income Statement'!F8*'Assumptions'!C40</f>
         <v/>
       </c>
       <c r="J7" s="16">
-        <f>'Income Statement'!G7*'Assumptions'!C36</f>
+        <f>'Income Statement'!G8*'Assumptions'!C40</f>
         <v/>
       </c>
       <c r="K7" s="16">
-        <f>'Income Statement'!H7*'Assumptions'!C36</f>
+        <f>'Income Statement'!H8*'Assumptions'!C40</f>
         <v/>
       </c>
     </row>
@@ -4460,39 +5186,39 @@
           <t>Total current assets</t>
         </is>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="25">
         <f>'Balance Sheet'!C4+'Balance Sheet'!C5+'Balance Sheet'!C6+'Balance Sheet'!C7</f>
         <v/>
       </c>
-      <c r="D8" s="22">
+      <c r="D8" s="25">
         <f>'Balance Sheet'!D4+'Balance Sheet'!D5+'Balance Sheet'!D6+'Balance Sheet'!D7</f>
         <v/>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="25">
         <f>'Balance Sheet'!E4+'Balance Sheet'!E5+'Balance Sheet'!E6+'Balance Sheet'!E7</f>
         <v/>
       </c>
-      <c r="F8" s="22">
+      <c r="F8" s="25">
         <f>'Balance Sheet'!F4+'Balance Sheet'!F5+'Balance Sheet'!F6+'Balance Sheet'!F7</f>
         <v/>
       </c>
-      <c r="G8" s="22">
+      <c r="G8" s="25">
         <f>'Balance Sheet'!G4+'Balance Sheet'!G5+'Balance Sheet'!G6+'Balance Sheet'!G7</f>
         <v/>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="25">
         <f>'Balance Sheet'!H4+'Balance Sheet'!H5+'Balance Sheet'!H6+'Balance Sheet'!H7</f>
         <v/>
       </c>
-      <c r="I8" s="22">
+      <c r="I8" s="25">
         <f>'Balance Sheet'!I4+'Balance Sheet'!I5+'Balance Sheet'!I6+'Balance Sheet'!I7</f>
         <v/>
       </c>
-      <c r="J8" s="22">
+      <c r="J8" s="25">
         <f>'Balance Sheet'!J4+'Balance Sheet'!J5+'Balance Sheet'!J6+'Balance Sheet'!J7</f>
         <v/>
       </c>
-      <c r="K8" s="22">
+      <c r="K8" s="25">
         <f>'Balance Sheet'!K4+'Balance Sheet'!K5+'Balance Sheet'!K6+'Balance Sheet'!K7</f>
         <v/>
       </c>
@@ -4705,39 +5431,39 @@
           <t>TOTAL ASSETS</t>
         </is>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="25">
         <f>'Balance Sheet'!C8+'Balance Sheet'!C9+'Balance Sheet'!C10+'Balance Sheet'!C11+'Balance Sheet'!C12+'Balance Sheet'!C13</f>
         <v/>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="25">
         <f>'Balance Sheet'!D8+'Balance Sheet'!D9+'Balance Sheet'!D10+'Balance Sheet'!D11+'Balance Sheet'!D12+'Balance Sheet'!D13</f>
         <v/>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="25">
         <f>'Balance Sheet'!E8+'Balance Sheet'!E9+'Balance Sheet'!E10+'Balance Sheet'!E11+'Balance Sheet'!E12+'Balance Sheet'!E13</f>
         <v/>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="25">
         <f>'Balance Sheet'!F8+'Balance Sheet'!F9+'Balance Sheet'!F10+'Balance Sheet'!F11+'Balance Sheet'!F12+'Balance Sheet'!F13</f>
         <v/>
       </c>
-      <c r="G14" s="22">
+      <c r="G14" s="25">
         <f>'Balance Sheet'!G8+'Balance Sheet'!G9+'Balance Sheet'!G10+'Balance Sheet'!G11+'Balance Sheet'!G12+'Balance Sheet'!G13</f>
         <v/>
       </c>
-      <c r="H14" s="22">
+      <c r="H14" s="25">
         <f>'Balance Sheet'!H8+'Balance Sheet'!H9+'Balance Sheet'!H10+'Balance Sheet'!H11+'Balance Sheet'!H12+'Balance Sheet'!H13</f>
         <v/>
       </c>
-      <c r="I14" s="22">
+      <c r="I14" s="25">
         <f>'Balance Sheet'!I8+'Balance Sheet'!I9+'Balance Sheet'!I10+'Balance Sheet'!I11+'Balance Sheet'!I12+'Balance Sheet'!I13</f>
         <v/>
       </c>
-      <c r="J14" s="22">
+      <c r="J14" s="25">
         <f>'Balance Sheet'!J8+'Balance Sheet'!J9+'Balance Sheet'!J10+'Balance Sheet'!J11+'Balance Sheet'!J12+'Balance Sheet'!J13</f>
         <v/>
       </c>
-      <c r="K14" s="22">
+      <c r="K14" s="25">
         <f>'Balance Sheet'!K8+'Balance Sheet'!K9+'Balance Sheet'!K10+'Balance Sheet'!K11+'Balance Sheet'!K12+'Balance Sheet'!K13</f>
         <v/>
       </c>
@@ -4779,23 +5505,23 @@
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>'Income Statement'!D7*'Assumptions'!C37</f>
+        <f>'Income Statement'!D8*'Assumptions'!C41</f>
         <v/>
       </c>
       <c r="H16" s="16">
-        <f>'Income Statement'!E7*'Assumptions'!C37</f>
+        <f>'Income Statement'!E8*'Assumptions'!C41</f>
         <v/>
       </c>
       <c r="I16" s="16">
-        <f>'Income Statement'!F7*'Assumptions'!C37</f>
+        <f>'Income Statement'!F8*'Assumptions'!C41</f>
         <v/>
       </c>
       <c r="J16" s="16">
-        <f>'Income Statement'!G7*'Assumptions'!C37</f>
+        <f>'Income Statement'!G8*'Assumptions'!C41</f>
         <v/>
       </c>
       <c r="K16" s="16">
-        <f>'Income Statement'!H7*'Assumptions'!C37</f>
+        <f>'Income Statement'!H8*'Assumptions'!C41</f>
         <v/>
       </c>
     </row>
@@ -4819,23 +5545,23 @@
         <v/>
       </c>
       <c r="G17" s="16">
-        <f>'Income Statement'!D7*'Assumptions'!C38</f>
+        <f>'Income Statement'!D8*'Assumptions'!C42</f>
         <v/>
       </c>
       <c r="H17" s="16">
-        <f>'Income Statement'!E7*'Assumptions'!C38</f>
+        <f>'Income Statement'!E8*'Assumptions'!C42</f>
         <v/>
       </c>
       <c r="I17" s="16">
-        <f>'Income Statement'!F7*'Assumptions'!C38</f>
+        <f>'Income Statement'!F8*'Assumptions'!C42</f>
         <v/>
       </c>
       <c r="J17" s="16">
-        <f>'Income Statement'!G7*'Assumptions'!C38</f>
+        <f>'Income Statement'!G8*'Assumptions'!C42</f>
         <v/>
       </c>
       <c r="K17" s="16">
-        <f>'Income Statement'!H7*'Assumptions'!C38</f>
+        <f>'Income Statement'!H8*'Assumptions'!C42</f>
         <v/>
       </c>
     </row>
@@ -4859,23 +5585,23 @@
         <v/>
       </c>
       <c r="G18" s="16">
-        <f>'Income Statement'!D7*'Assumptions'!C39</f>
+        <f>'Income Statement'!D8*'Assumptions'!C43</f>
         <v/>
       </c>
       <c r="H18" s="16">
-        <f>'Income Statement'!E7*'Assumptions'!C39</f>
+        <f>'Income Statement'!E8*'Assumptions'!C43</f>
         <v/>
       </c>
       <c r="I18" s="16">
-        <f>'Income Statement'!F7*'Assumptions'!C39</f>
+        <f>'Income Statement'!F8*'Assumptions'!C43</f>
         <v/>
       </c>
       <c r="J18" s="16">
-        <f>'Income Statement'!G7*'Assumptions'!C39</f>
+        <f>'Income Statement'!G8*'Assumptions'!C43</f>
         <v/>
       </c>
       <c r="K18" s="16">
-        <f>'Income Statement'!H7*'Assumptions'!C39</f>
+        <f>'Income Statement'!H8*'Assumptions'!C43</f>
         <v/>
       </c>
     </row>
@@ -4899,23 +5625,23 @@
         <v/>
       </c>
       <c r="G19" s="16">
-        <f>'Income Statement'!D7*'Assumptions'!C40</f>
+        <f>'Income Statement'!D8*'Assumptions'!C44</f>
         <v/>
       </c>
       <c r="H19" s="16">
-        <f>'Income Statement'!E7*'Assumptions'!C40</f>
+        <f>'Income Statement'!E8*'Assumptions'!C44</f>
         <v/>
       </c>
       <c r="I19" s="16">
-        <f>'Income Statement'!F7*'Assumptions'!C40</f>
+        <f>'Income Statement'!F8*'Assumptions'!C44</f>
         <v/>
       </c>
       <c r="J19" s="16">
-        <f>'Income Statement'!G7*'Assumptions'!C40</f>
+        <f>'Income Statement'!G8*'Assumptions'!C44</f>
         <v/>
       </c>
       <c r="K19" s="16">
-        <f>'Income Statement'!H7*'Assumptions'!C40</f>
+        <f>'Income Statement'!H8*'Assumptions'!C44</f>
         <v/>
       </c>
     </row>
@@ -4925,39 +5651,39 @@
           <t>Total current liabilities</t>
         </is>
       </c>
-      <c r="C20" s="22">
+      <c r="C20" s="25">
         <f>'Balance Sheet'!C16+'Balance Sheet'!C17+'Balance Sheet'!C18+'Balance Sheet'!C19</f>
         <v/>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="25">
         <f>'Balance Sheet'!D16+'Balance Sheet'!D17+'Balance Sheet'!D18+'Balance Sheet'!D19</f>
         <v/>
       </c>
-      <c r="E20" s="22">
+      <c r="E20" s="25">
         <f>'Balance Sheet'!E16+'Balance Sheet'!E17+'Balance Sheet'!E18+'Balance Sheet'!E19</f>
         <v/>
       </c>
-      <c r="F20" s="22">
+      <c r="F20" s="25">
         <f>'Balance Sheet'!F16+'Balance Sheet'!F17+'Balance Sheet'!F18+'Balance Sheet'!F19</f>
         <v/>
       </c>
-      <c r="G20" s="22">
+      <c r="G20" s="25">
         <f>'Balance Sheet'!G16+'Balance Sheet'!G17+'Balance Sheet'!G18+'Balance Sheet'!G19</f>
         <v/>
       </c>
-      <c r="H20" s="22">
+      <c r="H20" s="25">
         <f>'Balance Sheet'!H16+'Balance Sheet'!H17+'Balance Sheet'!H18+'Balance Sheet'!H19</f>
         <v/>
       </c>
-      <c r="I20" s="22">
+      <c r="I20" s="25">
         <f>'Balance Sheet'!I16+'Balance Sheet'!I17+'Balance Sheet'!I18+'Balance Sheet'!I19</f>
         <v/>
       </c>
-      <c r="J20" s="22">
+      <c r="J20" s="25">
         <f>'Balance Sheet'!J16+'Balance Sheet'!J17+'Balance Sheet'!J18+'Balance Sheet'!J19</f>
         <v/>
       </c>
-      <c r="K20" s="22">
+      <c r="K20" s="25">
         <f>'Balance Sheet'!K16+'Balance Sheet'!K17+'Balance Sheet'!K18+'Balance Sheet'!K19</f>
         <v/>
       </c>
@@ -5169,39 +5895,39 @@
           <t>TOTAL LIABILITIES</t>
         </is>
       </c>
-      <c r="C26" s="22">
+      <c r="C26" s="25">
         <f>'Balance Sheet'!C20+'Balance Sheet'!C21+'Balance Sheet'!C22+'Balance Sheet'!C23+'Balance Sheet'!C24+'Balance Sheet'!C25</f>
         <v/>
       </c>
-      <c r="D26" s="22">
+      <c r="D26" s="25">
         <f>'Balance Sheet'!D20+'Balance Sheet'!D21+'Balance Sheet'!D22+'Balance Sheet'!D23+'Balance Sheet'!D24+'Balance Sheet'!D25</f>
         <v/>
       </c>
-      <c r="E26" s="22">
+      <c r="E26" s="25">
         <f>'Balance Sheet'!E20+'Balance Sheet'!E21+'Balance Sheet'!E22+'Balance Sheet'!E23+'Balance Sheet'!E24+'Balance Sheet'!E25</f>
         <v/>
       </c>
-      <c r="F26" s="22">
+      <c r="F26" s="25">
         <f>'Balance Sheet'!F20+'Balance Sheet'!F21+'Balance Sheet'!F22+'Balance Sheet'!F23+'Balance Sheet'!F24+'Balance Sheet'!F25</f>
         <v/>
       </c>
-      <c r="G26" s="22">
+      <c r="G26" s="25">
         <f>'Balance Sheet'!G20+'Balance Sheet'!G21+'Balance Sheet'!G22+'Balance Sheet'!G23+'Balance Sheet'!G24+'Balance Sheet'!G25</f>
         <v/>
       </c>
-      <c r="H26" s="22">
+      <c r="H26" s="25">
         <f>'Balance Sheet'!H20+'Balance Sheet'!H21+'Balance Sheet'!H22+'Balance Sheet'!H23+'Balance Sheet'!H24+'Balance Sheet'!H25</f>
         <v/>
       </c>
-      <c r="I26" s="22">
+      <c r="I26" s="25">
         <f>'Balance Sheet'!I20+'Balance Sheet'!I21+'Balance Sheet'!I22+'Balance Sheet'!I23+'Balance Sheet'!I24+'Balance Sheet'!I25</f>
         <v/>
       </c>
-      <c r="J26" s="22">
+      <c r="J26" s="25">
         <f>'Balance Sheet'!J20+'Balance Sheet'!J21+'Balance Sheet'!J22+'Balance Sheet'!J23+'Balance Sheet'!J24+'Balance Sheet'!J25</f>
         <v/>
       </c>
-      <c r="K26" s="22">
+      <c r="K26" s="25">
         <f>'Balance Sheet'!K20+'Balance Sheet'!K21+'Balance Sheet'!K22+'Balance Sheet'!K23+'Balance Sheet'!K24+'Balance Sheet'!K25</f>
         <v/>
       </c>
@@ -5244,23 +5970,23 @@
         <v/>
       </c>
       <c r="G28" s="16">
-        <f>'Balance Sheet'!F28+'Cash Flow'!D8+'Assumptions'!D25</f>
+        <f>'Balance Sheet'!F28+'Cash Flow'!D8+'Assumptions'!D29</f>
         <v/>
       </c>
       <c r="H28" s="16">
-        <f>'Balance Sheet'!G28+'Cash Flow'!E8+'Assumptions'!E25</f>
+        <f>'Balance Sheet'!G28+'Cash Flow'!E8+'Assumptions'!E29</f>
         <v/>
       </c>
       <c r="I28" s="16">
-        <f>'Balance Sheet'!H28+'Cash Flow'!F8+'Assumptions'!F25</f>
+        <f>'Balance Sheet'!H28+'Cash Flow'!F8+'Assumptions'!F29</f>
         <v/>
       </c>
       <c r="J28" s="16">
-        <f>'Balance Sheet'!I28+'Cash Flow'!G8+'Assumptions'!G25</f>
+        <f>'Balance Sheet'!I28+'Cash Flow'!G8+'Assumptions'!G29</f>
         <v/>
       </c>
       <c r="K28" s="16">
-        <f>'Balance Sheet'!J28+'Cash Flow'!H8+'Assumptions'!H25</f>
+        <f>'Balance Sheet'!J28+'Cash Flow'!H8+'Assumptions'!H29</f>
         <v/>
       </c>
     </row>
@@ -5310,39 +6036,39 @@
           <t>TOTAL EQUITY</t>
         </is>
       </c>
-      <c r="C30" s="22">
+      <c r="C30" s="25">
         <f>'Balance Sheet'!C28+'Balance Sheet'!C29</f>
         <v/>
       </c>
-      <c r="D30" s="22">
+      <c r="D30" s="25">
         <f>'Balance Sheet'!D28+'Balance Sheet'!D29</f>
         <v/>
       </c>
-      <c r="E30" s="22">
+      <c r="E30" s="25">
         <f>'Balance Sheet'!E28+'Balance Sheet'!E29</f>
         <v/>
       </c>
-      <c r="F30" s="22">
+      <c r="F30" s="25">
         <f>'Balance Sheet'!F28+'Balance Sheet'!F29</f>
         <v/>
       </c>
-      <c r="G30" s="22">
+      <c r="G30" s="25">
         <f>'Balance Sheet'!G28+'Balance Sheet'!G29</f>
         <v/>
       </c>
-      <c r="H30" s="22">
+      <c r="H30" s="25">
         <f>'Balance Sheet'!H28+'Balance Sheet'!H29</f>
         <v/>
       </c>
-      <c r="I30" s="22">
+      <c r="I30" s="25">
         <f>'Balance Sheet'!I28+'Balance Sheet'!I29</f>
         <v/>
       </c>
-      <c r="J30" s="22">
+      <c r="J30" s="25">
         <f>'Balance Sheet'!J28+'Balance Sheet'!J29</f>
         <v/>
       </c>
-      <c r="K30" s="22">
+      <c r="K30" s="25">
         <f>'Balance Sheet'!K28+'Balance Sheet'!K29</f>
         <v/>
       </c>
@@ -5353,39 +6079,39 @@
           <t>TOTAL LIABILITIES &amp; EQUITY</t>
         </is>
       </c>
-      <c r="C31" s="22">
+      <c r="C31" s="25">
         <f>'Balance Sheet'!C26+'Balance Sheet'!C30</f>
         <v/>
       </c>
-      <c r="D31" s="22">
+      <c r="D31" s="25">
         <f>'Balance Sheet'!D26+'Balance Sheet'!D30</f>
         <v/>
       </c>
-      <c r="E31" s="22">
+      <c r="E31" s="25">
         <f>'Balance Sheet'!E26+'Balance Sheet'!E30</f>
         <v/>
       </c>
-      <c r="F31" s="22">
+      <c r="F31" s="25">
         <f>'Balance Sheet'!F26+'Balance Sheet'!F30</f>
         <v/>
       </c>
-      <c r="G31" s="22">
+      <c r="G31" s="25">
         <f>'Balance Sheet'!G26+'Balance Sheet'!G30</f>
         <v/>
       </c>
-      <c r="H31" s="22">
+      <c r="H31" s="25">
         <f>'Balance Sheet'!H26+'Balance Sheet'!H30</f>
         <v/>
       </c>
-      <c r="I31" s="22">
+      <c r="I31" s="25">
         <f>'Balance Sheet'!I26+'Balance Sheet'!I30</f>
         <v/>
       </c>
-      <c r="J31" s="22">
+      <c r="J31" s="25">
         <f>'Balance Sheet'!J26+'Balance Sheet'!J30</f>
         <v/>
       </c>
-      <c r="K31" s="22">
+      <c r="K31" s="25">
         <f>'Balance Sheet'!K26+'Balance Sheet'!K30</f>
         <v/>
       </c>
@@ -5396,39 +6122,39 @@
           <t>Balance check (assets − L&amp;E)</t>
         </is>
       </c>
-      <c r="C32" s="20">
+      <c r="C32" s="23">
         <f>'Balance Sheet'!C14-'Balance Sheet'!C31</f>
         <v/>
       </c>
-      <c r="D32" s="20">
+      <c r="D32" s="23">
         <f>'Balance Sheet'!D14-'Balance Sheet'!D31</f>
         <v/>
       </c>
-      <c r="E32" s="20">
+      <c r="E32" s="23">
         <f>'Balance Sheet'!E14-'Balance Sheet'!E31</f>
         <v/>
       </c>
-      <c r="F32" s="20">
+      <c r="F32" s="23">
         <f>'Balance Sheet'!F14-'Balance Sheet'!F31</f>
         <v/>
       </c>
-      <c r="G32" s="20">
+      <c r="G32" s="23">
         <f>'Balance Sheet'!G14-'Balance Sheet'!G31</f>
         <v/>
       </c>
-      <c r="H32" s="20">
+      <c r="H32" s="23">
         <f>'Balance Sheet'!H14-'Balance Sheet'!H31</f>
         <v/>
       </c>
-      <c r="I32" s="20">
+      <c r="I32" s="23">
         <f>'Balance Sheet'!I14-'Balance Sheet'!I31</f>
         <v/>
       </c>
-      <c r="J32" s="20">
+      <c r="J32" s="23">
         <f>'Balance Sheet'!J14-'Balance Sheet'!J31</f>
         <v/>
       </c>
-      <c r="K32" s="20">
+      <c r="K32" s="23">
         <f>'Balance Sheet'!K14-'Balance Sheet'!K31</f>
         <v/>
       </c>
@@ -5438,7 +6164,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5613,23 +6339,23 @@
         </is>
       </c>
       <c r="D8" s="16">
-        <f>'Assumptions'!D22*'Income Statement'!D7</f>
+        <f>'Assumptions'!D26*'Income Statement'!D8</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>'Assumptions'!E22*'Income Statement'!E7</f>
+        <f>'Assumptions'!E26*'Income Statement'!E8</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>'Assumptions'!F22*'Income Statement'!F7</f>
+        <f>'Assumptions'!F26*'Income Statement'!F8</f>
         <v/>
       </c>
       <c r="G8" s="16">
-        <f>'Assumptions'!G22*'Income Statement'!G7</f>
+        <f>'Assumptions'!G26*'Income Statement'!G8</f>
         <v/>
       </c>
       <c r="H8" s="16">
-        <f>'Assumptions'!H22*'Income Statement'!H7</f>
+        <f>'Assumptions'!H26*'Income Statement'!H8</f>
         <v/>
       </c>
     </row>
@@ -6052,23 +6778,23 @@
         </is>
       </c>
       <c r="D25" s="16">
-        <f>'Assumptions'!D25</f>
+        <f>'Assumptions'!D29</f>
         <v/>
       </c>
       <c r="E25" s="16">
-        <f>'Assumptions'!E25</f>
+        <f>'Assumptions'!E29</f>
         <v/>
       </c>
       <c r="F25" s="16">
-        <f>'Assumptions'!F25</f>
+        <f>'Assumptions'!F29</f>
         <v/>
       </c>
       <c r="G25" s="16">
-        <f>'Assumptions'!G25</f>
+        <f>'Assumptions'!G29</f>
         <v/>
       </c>
       <c r="H25" s="16">
-        <f>'Assumptions'!H25</f>
+        <f>'Assumptions'!H29</f>
         <v/>
       </c>
     </row>
@@ -6159,24 +6885,228 @@
           <t>Cash, end of period</t>
         </is>
       </c>
-      <c r="D29" s="22">
+      <c r="D29" s="25">
         <f>'Cash Flow'!D28+'Cash Flow'!D27</f>
         <v/>
       </c>
-      <c r="E29" s="22">
+      <c r="E29" s="25">
         <f>'Cash Flow'!E28+'Cash Flow'!E27</f>
         <v/>
       </c>
-      <c r="F29" s="22">
+      <c r="F29" s="25">
         <f>'Cash Flow'!F28+'Cash Flow'!F27</f>
         <v/>
       </c>
-      <c r="G29" s="22">
+      <c r="G29" s="25">
         <f>'Cash Flow'!G28+'Cash Flow'!G27</f>
         <v/>
       </c>
-      <c r="H29" s="22">
+      <c r="H29" s="25">
         <f>'Cash Flow'!H28+'Cash Flow'!H27</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="2" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>MODEL INTEGRITY CHECKS (should all be ~0)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="C2" s="7" t="inlineStr">
+        <is>
+          <t>2025A</t>
+        </is>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>2026E</t>
+        </is>
+      </c>
+      <c r="E2" s="7" t="inlineStr">
+        <is>
+          <t>2027E</t>
+        </is>
+      </c>
+      <c r="F2" s="7" t="inlineStr">
+        <is>
+          <t>2028E</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="inlineStr">
+        <is>
+          <t>2029E</t>
+        </is>
+      </c>
+      <c r="H2" s="7" t="inlineStr">
+        <is>
+          <t>2030E</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Balance sheet balances (A − L&amp;E)</t>
+        </is>
+      </c>
+      <c r="C3" s="23">
+        <f>'Balance Sheet'!C32</f>
+        <v/>
+      </c>
+      <c r="D3" s="23">
+        <f>'Balance Sheet'!G32</f>
+        <v/>
+      </c>
+      <c r="E3" s="23">
+        <f>'Balance Sheet'!H32</f>
+        <v/>
+      </c>
+      <c r="F3" s="23">
+        <f>'Balance Sheet'!I32</f>
+        <v/>
+      </c>
+      <c r="G3" s="23">
+        <f>'Balance Sheet'!J32</f>
+        <v/>
+      </c>
+      <c r="H3" s="23">
+        <f>'Balance Sheet'!K32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Cash flow ties to balance sheet cash</t>
+        </is>
+      </c>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D4" s="23">
+        <f>'Cash Flow'!D29-'Balance Sheet'!G4</f>
+        <v/>
+      </c>
+      <c r="E4" s="23">
+        <f>'Cash Flow'!E29-'Balance Sheet'!H4</f>
+        <v/>
+      </c>
+      <c r="F4" s="23">
+        <f>'Cash Flow'!F29-'Balance Sheet'!I4</f>
+        <v/>
+      </c>
+      <c r="G4" s="23">
+        <f>'Cash Flow'!G29-'Balance Sheet'!J4</f>
+        <v/>
+      </c>
+      <c r="H4" s="23">
+        <f>'Cash Flow'!H29-'Balance Sheet'!K4</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>PPA bridge balances (Open: A − L&amp;E)</t>
+        </is>
+      </c>
+      <c r="C5" s="23">
+        <f>'Balance Sheet'!F32</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Segment net income sums to consolidated NI</t>
+        </is>
+      </c>
+      <c r="C6" s="23">
+        <f>'Segments'!C49-'Income Statement'!C25</f>
+        <v/>
+      </c>
+      <c r="D6" s="23">
+        <f>'Segments'!D49-'Income Statement'!D25</f>
+        <v/>
+      </c>
+      <c r="E6" s="23">
+        <f>'Segments'!E49-'Income Statement'!E25</f>
+        <v/>
+      </c>
+      <c r="F6" s="23">
+        <f>'Segments'!F49-'Income Statement'!F25</f>
+        <v/>
+      </c>
+      <c r="G6" s="23">
+        <f>'Segments'!G49-'Income Statement'!G25</f>
+        <v/>
+      </c>
+      <c r="H6" s="23">
+        <f>'Segments'!H49-'Income Statement'!H25</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Segment EPS contributions sum to diluted EPS</t>
+        </is>
+      </c>
+      <c r="C7" s="28">
+        <f>'Segments'!C50-'Income Statement'!C28</f>
+        <v/>
+      </c>
+      <c r="D7" s="28">
+        <f>'Segments'!D50-'Income Statement'!D28</f>
+        <v/>
+      </c>
+      <c r="E7" s="28">
+        <f>'Segments'!E50-'Income Statement'!E28</f>
+        <v/>
+      </c>
+      <c r="F7" s="28">
+        <f>'Segments'!F50-'Income Statement'!F28</f>
+        <v/>
+      </c>
+      <c r="G7" s="28">
+        <f>'Segments'!G50-'Income Statement'!G28</f>
+        <v/>
+      </c>
+      <c r="H7" s="28">
+        <f>'Segments'!H50-'Income Statement'!H28</f>
         <v/>
       </c>
     </row>

--- a/SpaceX_Cursor_Pro_Forma_Model.xlsx
+++ b/SpaceX_Cursor_Pro_Forma_Model.xlsx
@@ -698,7 +698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1076,332 +1076,397 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Capex % of combined revenue</t>
+          <t xml:space="preserve">  Space — capex % of segment revenue</t>
         </is>
       </c>
       <c r="C21" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="D21" s="12" t="n">
         <v>0.26</v>
       </c>
-      <c r="D21" s="12" t="n">
-        <v>0.23</v>
-      </c>
       <c r="E21" s="12" t="n">
-        <v>0.21</v>
+        <v>0.24</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>0.19</v>
+        <v>0.22</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.175</v>
+        <v>0.2</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>0.165</v>
+        <v>0.18</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Depreciation % of beginning net PP&amp;E</t>
+          <t xml:space="preserve">  Starlink — capex % of segment revenue</t>
         </is>
       </c>
       <c r="C22" s="12" t="n">
-        <v>0.09</v>
+        <v>0.36</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>0.22</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  D&amp;A allocation — Space %</t>
+          <t xml:space="preserve">  xAI-Cursor — capex % of segment revenue</t>
         </is>
       </c>
       <c r="C23" s="12" t="n">
-        <v>0.3</v>
+        <v>0.25</v>
+      </c>
+      <c r="D23" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="F23" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H23" s="12" t="n">
+        <v>0.18</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  D&amp;A allocation — Starlink %</t>
+          <t xml:space="preserve">  Space — depreciation % of beginning PP&amp;E</t>
         </is>
       </c>
       <c r="C24" s="12" t="n">
-        <v>0.5</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  D&amp;A allocation — xAI-Cursor %</t>
+          <t xml:space="preserve">  Starlink — depreciation % of beginning PP&amp;E</t>
         </is>
       </c>
       <c r="C25" s="12" t="n">
-        <v>0.2</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Stock-based comp % of revenue</t>
+          <t xml:space="preserve">  xAI-Cursor — depreciation % of beginning PP&amp;E</t>
         </is>
       </c>
       <c r="C26" s="12" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="D26" s="12" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E26" s="12" t="n">
-        <v>0.055</v>
-      </c>
-      <c r="F26" s="12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G26" s="12" t="n">
-        <v>0.045</v>
-      </c>
-      <c r="H26" s="12" t="n">
-        <v>0.04</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Net new long-term debt ($M)</t>
+          <t xml:space="preserve">  Space — opening net PP&amp;E ($M)</t>
         </is>
       </c>
       <c r="C27" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="11" t="n">
-        <v>2000</v>
-      </c>
-      <c r="E27" s="11" t="n">
-        <v>2000</v>
-      </c>
-      <c r="F27" s="11" t="n">
-        <v>1500</v>
-      </c>
-      <c r="G27" s="11" t="n">
-        <v>1000</v>
-      </c>
-      <c r="H27" s="11" t="n">
-        <v>1000</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Spectrum obligation repayment ($M)</t>
+          <t xml:space="preserve">  xAI-Cursor — opening net PP&amp;E ($M)</t>
         </is>
       </c>
       <c r="C28" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="11" t="n">
-        <v>-2000</v>
-      </c>
-      <c r="E28" s="11" t="n">
-        <v>-2000</v>
-      </c>
-      <c r="F28" s="11" t="n">
-        <v>-2000</v>
-      </c>
-      <c r="G28" s="11" t="n">
-        <v>-2000</v>
-      </c>
-      <c r="H28" s="11" t="n">
-        <v>-2000</v>
+        <v>3300</v>
+      </c>
+      <c r="L28" s="13" t="inlineStr">
+        <is>
+          <t>Starlink opening = total − Space − xAI-Cursor</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Primary equity issuance / IPO proceeds ($M)</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="11" t="n">
-        <v>50000</v>
-      </c>
-      <c r="E29" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F29" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="13" t="inlineStr">
-        <is>
-          <t>SpaceX June-2026 IPO</t>
-        </is>
+          <t xml:space="preserve">  Stock-based comp % of revenue</t>
+        </is>
+      </c>
+      <c r="C29" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="D29" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E29" s="12" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="F29" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="H29" s="12" t="n">
+        <v>0.04</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Interest rate on debt &amp; spectrum obligation</t>
-        </is>
-      </c>
-      <c r="C30" s="12" t="n">
-        <v>0.065</v>
+          <t xml:space="preserve">  Net new long-term debt ($M)</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E30" s="11" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>1500</v>
+      </c>
+      <c r="G30" s="11" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H30" s="11" t="n">
+        <v>1000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Interest income rate on cash</t>
-        </is>
-      </c>
-      <c r="C31" s="12" t="n">
-        <v>0.04</v>
+          <t xml:space="preserve">  Spectrum obligation repayment ($M)</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" s="11" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="E31" s="11" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="G31" s="11" t="n">
+        <v>-2000</v>
+      </c>
+      <c r="H31" s="11" t="n">
+        <v>-2000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Statutory tax rate</t>
-        </is>
-      </c>
-      <c r="C32" s="12" t="n">
-        <v>0.21</v>
+          <t xml:space="preserve">  Primary equity issuance / IPO proceeds ($M)</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="11" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="13" t="inlineStr">
+        <is>
+          <t>SpaceX June-2026 IPO</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Opening NOL carryforward, FY2025 ($M)</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="n">
-        <v>26000</v>
-      </c>
-      <c r="L33" s="13" t="inlineStr">
-        <is>
-          <t>SpaceX accumulated + Cursor</t>
-        </is>
+          <t xml:space="preserve">  Interest rate on debt &amp; spectrum obligation</t>
+        </is>
+      </c>
+      <c r="C33" s="12" t="n">
+        <v>0.065</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NOL usage limit (% of taxable income)</t>
+          <t xml:space="preserve">  Interest income rate on cash</t>
         </is>
       </c>
       <c r="C34" s="12" t="n">
-        <v>0.8</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  SpaceX shares pre-deal (M)</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="n">
-        <v>2000</v>
+          <t xml:space="preserve">  Statutory tax rate</t>
+        </is>
+      </c>
+      <c r="C35" s="12" t="n">
+        <v>0.21</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  SpaceX share price, deal pricing ($)</t>
-        </is>
-      </c>
-      <c r="C36" s="15" t="n">
-        <v>450</v>
+          <t xml:space="preserve">  Opening NOL carryforward, FY2025 ($M)</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="n">
+        <v>26000</v>
+      </c>
+      <c r="L36" s="13" t="inlineStr">
+        <is>
+          <t>SpaceX accumulated + Cursor</t>
+        </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="8" t="inlineStr">
-        <is>
-          <t>Working capital ratios (% of revenue)</t>
-        </is>
-      </c>
-      <c r="B37" s="9" t="n"/>
-      <c r="C37" s="9" t="n"/>
-      <c r="D37" s="9" t="n"/>
-      <c r="E37" s="9" t="n"/>
-      <c r="F37" s="9" t="n"/>
-      <c r="G37" s="9" t="n"/>
-      <c r="H37" s="9" t="n"/>
-      <c r="I37" s="9" t="n"/>
-      <c r="J37" s="9" t="n"/>
-      <c r="K37" s="9" t="n"/>
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NOL usage limit (% of taxable income)</t>
+        </is>
+      </c>
+      <c r="C37" s="12" t="n">
+        <v>0.8</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Accounts receivable (% of revenue)</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="n">
-        <v>0.1339</v>
+          <t xml:space="preserve">  SpaceX shares pre-deal (M)</t>
+        </is>
+      </c>
+      <c r="C38" s="14" t="n">
+        <v>2000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Inventory (% of revenue)</t>
-        </is>
-      </c>
-      <c r="C39" s="12" t="n">
-        <v>0.1499</v>
+          <t xml:space="preserve">  SpaceX share price, deal pricing ($)</t>
+        </is>
+      </c>
+      <c r="C39" s="15" t="n">
+        <v>450</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Prepaid &amp; other current assets (% of revenue)</t>
-        </is>
-      </c>
-      <c r="C40" s="12" t="n">
-        <v>0.0803</v>
-      </c>
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>Working capital ratios (% of revenue)</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="n"/>
+      <c r="C40" s="9" t="n"/>
+      <c r="D40" s="9" t="n"/>
+      <c r="E40" s="9" t="n"/>
+      <c r="F40" s="9" t="n"/>
+      <c r="G40" s="9" t="n"/>
+      <c r="H40" s="9" t="n"/>
+      <c r="I40" s="9" t="n"/>
+      <c r="J40" s="9" t="n"/>
+      <c r="K40" s="9" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Accounts payable (% of revenue)</t>
+          <t xml:space="preserve">  Accounts receivable (% of revenue)</t>
         </is>
       </c>
       <c r="C41" s="12" t="n">
-        <v>0.1499</v>
+        <v>0.1339</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Accrued liabilities (% of revenue)</t>
+          <t xml:space="preserve">  Inventory (% of revenue)</t>
         </is>
       </c>
       <c r="C42" s="12" t="n">
-        <v>0.091</v>
+        <v>0.1499</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Deferred revenue, current (% of revenue)</t>
+          <t xml:space="preserve">  Prepaid &amp; other current assets (% of revenue)</t>
         </is>
       </c>
       <c r="C43" s="12" t="n">
-        <v>0.1499</v>
+        <v>0.0803</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="10" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Accounts payable (% of revenue)</t>
+        </is>
+      </c>
+      <c r="C44" s="12" t="n">
+        <v>0.1499</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Accrued liabilities (% of revenue)</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="n">
+        <v>0.091</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Deferred revenue, current (% of revenue)</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="n">
+        <v>0.1499</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Customer deposits &amp; advances (% of revenue)</t>
         </is>
       </c>
-      <c r="C44" s="12" t="n">
+      <c r="C47" s="12" t="n">
         <v>0.1017</v>
       </c>
     </row>
@@ -1875,7 +1940,7 @@
     <row r="18">
       <c r="A18" s="19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  D&amp;A by capital-intensity weights; net interest &amp; tax allocated by revenue share.</t>
+          <t xml:space="preserve">  Segment D&amp;A from the PP&amp;E schedule; net interest &amp; tax allocated by revenue share.</t>
         </is>
       </c>
     </row>
@@ -1924,27 +1989,27 @@
         </is>
       </c>
       <c r="C21" s="16">
-        <f>-'Income Statement'!C16*'Assumptions'!C23</f>
+        <f>-'Schedules'!C7</f>
         <v/>
       </c>
       <c r="D21" s="16">
-        <f>-'Income Statement'!D16*'Assumptions'!C23</f>
+        <f>-'Schedules'!D7</f>
         <v/>
       </c>
       <c r="E21" s="16">
-        <f>-'Income Statement'!E16*'Assumptions'!C23</f>
+        <f>-'Schedules'!E7</f>
         <v/>
       </c>
       <c r="F21" s="16">
-        <f>-'Income Statement'!F16*'Assumptions'!C23</f>
+        <f>-'Schedules'!F7</f>
         <v/>
       </c>
       <c r="G21" s="16">
-        <f>-'Income Statement'!G16*'Assumptions'!C23</f>
+        <f>-'Schedules'!G7</f>
         <v/>
       </c>
       <c r="H21" s="16">
-        <f>-'Income Statement'!H16*'Assumptions'!C23</f>
+        <f>-'Schedules'!H7</f>
         <v/>
       </c>
     </row>
@@ -2204,27 +2269,27 @@
         </is>
       </c>
       <c r="C31" s="16">
-        <f>-'Income Statement'!C16*'Assumptions'!C24</f>
+        <f>-'Schedules'!C12</f>
         <v/>
       </c>
       <c r="D31" s="16">
-        <f>-'Income Statement'!D16*'Assumptions'!C24</f>
+        <f>-'Schedules'!D12</f>
         <v/>
       </c>
       <c r="E31" s="16">
-        <f>-'Income Statement'!E16*'Assumptions'!C24</f>
+        <f>-'Schedules'!E12</f>
         <v/>
       </c>
       <c r="F31" s="16">
-        <f>-'Income Statement'!F16*'Assumptions'!C24</f>
+        <f>-'Schedules'!F12</f>
         <v/>
       </c>
       <c r="G31" s="16">
-        <f>-'Income Statement'!G16*'Assumptions'!C24</f>
+        <f>-'Schedules'!G12</f>
         <v/>
       </c>
       <c r="H31" s="16">
-        <f>-'Income Statement'!H16*'Assumptions'!C24</f>
+        <f>-'Schedules'!H12</f>
         <v/>
       </c>
     </row>
@@ -2484,27 +2549,27 @@
         </is>
       </c>
       <c r="C41" s="16">
-        <f>-'Income Statement'!C16*'Assumptions'!C25</f>
+        <f>-'Schedules'!C17</f>
         <v/>
       </c>
       <c r="D41" s="16">
-        <f>-'Income Statement'!D16*'Assumptions'!C25</f>
+        <f>-'Schedules'!D17</f>
         <v/>
       </c>
       <c r="E41" s="16">
-        <f>-'Income Statement'!E16*'Assumptions'!C25</f>
+        <f>-'Schedules'!E17</f>
         <v/>
       </c>
       <c r="F41" s="16">
-        <f>-'Income Statement'!F16*'Assumptions'!C25</f>
+        <f>-'Schedules'!F17</f>
         <v/>
       </c>
       <c r="G41" s="16">
-        <f>-'Income Statement'!G16*'Assumptions'!C25</f>
+        <f>-'Schedules'!G17</f>
         <v/>
       </c>
       <c r="H41" s="16">
-        <f>-'Income Statement'!H16*'Assumptions'!C25</f>
+        <f>-'Schedules'!H17</f>
         <v/>
       </c>
     </row>
@@ -2863,7 +2928,7 @@
         </is>
       </c>
       <c r="C5" s="21">
-        <f>'Assumptions'!C36</f>
+        <f>'Assumptions'!C39</f>
         <v/>
       </c>
     </row>
@@ -3079,7 +3144,7 @@
         </is>
       </c>
       <c r="C24" s="16">
-        <f>'Assumptions'!C32*'Deal &amp; PPA'!C21</f>
+        <f>'Assumptions'!C35*'Deal &amp; PPA'!C21</f>
         <v/>
       </c>
     </row>
@@ -3116,7 +3181,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K30"/>
+  <dimension ref="A1:K46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -3176,7 +3241,7 @@
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Property, plant &amp; equipment</t>
+          <t>Property, plant &amp; equipment — forecast by segment</t>
         </is>
       </c>
       <c r="B3" s="9" t="n"/>
@@ -3191,783 +3256,1185 @@
       <c r="K3" s="9" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Beginning net PP&amp;E</t>
-        </is>
-      </c>
-      <c r="C4" s="16" t="n">
-        <v>46000</v>
-      </c>
-      <c r="D4" s="16">
-        <f>'Balance Sheet'!F9</f>
-        <v/>
-      </c>
-      <c r="E4" s="16">
-        <f>'Schedules'!D7</f>
-        <v/>
-      </c>
-      <c r="F4" s="16">
-        <f>'Schedules'!E7</f>
-        <v/>
-      </c>
-      <c r="G4" s="16">
-        <f>'Schedules'!F7</f>
-        <v/>
-      </c>
-      <c r="H4" s="16">
-        <f>'Schedules'!G7</f>
-        <v/>
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Space</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Capital expenditures</t>
+          <t xml:space="preserve">     Beginning net PP&amp;E</t>
         </is>
       </c>
       <c r="C5" s="16">
-        <f>'Assumptions'!C21*'Income Statement'!C8</f>
+        <f>'Assumptions'!C27</f>
         <v/>
       </c>
       <c r="D5" s="16">
-        <f>'Assumptions'!D21*'Income Statement'!D8</f>
+        <f>'Assumptions'!C27</f>
         <v/>
       </c>
       <c r="E5" s="16">
-        <f>'Assumptions'!E21*'Income Statement'!E8</f>
+        <f>'Schedules'!D8</f>
         <v/>
       </c>
       <c r="F5" s="16">
-        <f>'Assumptions'!F21*'Income Statement'!F8</f>
+        <f>'Schedules'!E8</f>
         <v/>
       </c>
       <c r="G5" s="16">
-        <f>'Assumptions'!G21*'Income Statement'!G8</f>
+        <f>'Schedules'!F8</f>
         <v/>
       </c>
       <c r="H5" s="16">
-        <f>'Assumptions'!H21*'Income Statement'!H8</f>
+        <f>'Schedules'!G8</f>
         <v/>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Depreciation</t>
+          <t xml:space="preserve">     (+) Capital expenditures</t>
         </is>
       </c>
       <c r="C6" s="16">
-        <f>'Schedules'!C4*'Assumptions'!C22</f>
+        <f>'Assumptions'!C21*'Segments'!C5</f>
         <v/>
       </c>
       <c r="D6" s="16">
-        <f>'Schedules'!D4*'Assumptions'!C22</f>
+        <f>'Assumptions'!D21*'Segments'!D5</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>'Schedules'!E4*'Assumptions'!C22</f>
+        <f>'Assumptions'!E21*'Segments'!E5</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>'Schedules'!F4*'Assumptions'!C22</f>
+        <f>'Assumptions'!F21*'Segments'!F5</f>
         <v/>
       </c>
       <c r="G6" s="16">
-        <f>'Schedules'!G4*'Assumptions'!C22</f>
+        <f>'Assumptions'!G21*'Segments'!G5</f>
         <v/>
       </c>
       <c r="H6" s="16">
-        <f>'Schedules'!H4*'Assumptions'!C22</f>
+        <f>'Assumptions'!H21*'Segments'!H5</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Ending net PP&amp;E</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="n">
-        <v>46000</v>
-      </c>
-      <c r="D7" s="17">
-        <f>'Schedules'!D4+'Schedules'!D5-'Schedules'!D6</f>
-        <v/>
-      </c>
-      <c r="E7" s="17">
-        <f>'Schedules'!E4+'Schedules'!E5-'Schedules'!E6</f>
-        <v/>
-      </c>
-      <c r="F7" s="17">
-        <f>'Schedules'!F4+'Schedules'!F5-'Schedules'!F6</f>
-        <v/>
-      </c>
-      <c r="G7" s="17">
-        <f>'Schedules'!G4+'Schedules'!G5-'Schedules'!G6</f>
-        <v/>
-      </c>
-      <c r="H7" s="17">
-        <f>'Schedules'!H4+'Schedules'!H5-'Schedules'!H6</f>
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     (−) Depreciation</t>
+        </is>
+      </c>
+      <c r="C7" s="16">
+        <f>'Schedules'!C5*'Assumptions'!C24</f>
+        <v/>
+      </c>
+      <c r="D7" s="16">
+        <f>'Schedules'!D5*'Assumptions'!C24</f>
+        <v/>
+      </c>
+      <c r="E7" s="16">
+        <f>'Schedules'!E5*'Assumptions'!C24</f>
+        <v/>
+      </c>
+      <c r="F7" s="16">
+        <f>'Schedules'!F5*'Assumptions'!C24</f>
+        <v/>
+      </c>
+      <c r="G7" s="16">
+        <f>'Schedules'!G5*'Assumptions'!C24</f>
+        <v/>
+      </c>
+      <c r="H7" s="16">
+        <f>'Schedules'!H5*'Assumptions'!C24</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>Acquired intangibles &amp; deferred tax</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="9" t="n"/>
-      <c r="F8" s="9" t="n"/>
-      <c r="G8" s="9" t="n"/>
-      <c r="H8" s="9" t="n"/>
-      <c r="I8" s="9" t="n"/>
-      <c r="J8" s="9" t="n"/>
-      <c r="K8" s="9" t="n"/>
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Ending net PP&amp;E</t>
+        </is>
+      </c>
+      <c r="C8" s="17">
+        <f>'Schedules'!C5</f>
+        <v/>
+      </c>
+      <c r="D8" s="17">
+        <f>'Schedules'!D5+'Schedules'!D6-'Schedules'!D7</f>
+        <v/>
+      </c>
+      <c r="E8" s="17">
+        <f>'Schedules'!E5+'Schedules'!E6-'Schedules'!E7</f>
+        <v/>
+      </c>
+      <c r="F8" s="17">
+        <f>'Schedules'!F5+'Schedules'!F6-'Schedules'!F7</f>
+        <v/>
+      </c>
+      <c r="G8" s="17">
+        <f>'Schedules'!G5+'Schedules'!G6-'Schedules'!G7</f>
+        <v/>
+      </c>
+      <c r="H8" s="17">
+        <f>'Schedules'!H5+'Schedules'!H6-'Schedules'!H7</f>
+        <v/>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Beginning intangibles, net</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" s="16">
-        <f>'Deal &amp; PPA'!C21</f>
-        <v/>
-      </c>
-      <c r="E9" s="16">
-        <f>'Schedules'!D11</f>
-        <v/>
-      </c>
-      <c r="F9" s="16">
-        <f>'Schedules'!E11</f>
-        <v/>
-      </c>
-      <c r="G9" s="16">
-        <f>'Schedules'!F11</f>
-        <v/>
-      </c>
-      <c r="H9" s="16">
-        <f>'Schedules'!G11</f>
-        <v/>
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Starlink</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Amortization</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="n">
-        <v>0</v>
+          <t xml:space="preserve">     Beginning net PP&amp;E</t>
+        </is>
+      </c>
+      <c r="C10" s="16">
+        <f>'Balance Sheet'!F9-'Assumptions'!C27-'Assumptions'!C28</f>
+        <v/>
       </c>
       <c r="D10" s="16">
-        <f>MIN('Schedules'!D9,'Deal &amp; PPA'!C22)</f>
+        <f>'Balance Sheet'!F9-'Assumptions'!C27-'Assumptions'!C28</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>MIN('Schedules'!E9,'Deal &amp; PPA'!C22)</f>
+        <f>'Schedules'!D13</f>
         <v/>
       </c>
       <c r="F10" s="16">
-        <f>MIN('Schedules'!F9,'Deal &amp; PPA'!C22)</f>
+        <f>'Schedules'!E13</f>
         <v/>
       </c>
       <c r="G10" s="16">
-        <f>MIN('Schedules'!G9,'Deal &amp; PPA'!C22)</f>
+        <f>'Schedules'!F13</f>
         <v/>
       </c>
       <c r="H10" s="16">
-        <f>MIN('Schedules'!H9,'Deal &amp; PPA'!C22)</f>
+        <f>'Schedules'!G13</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Ending intangibles, net</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="17">
-        <f>'Schedules'!D9-'Schedules'!D10</f>
-        <v/>
-      </c>
-      <c r="E11" s="17">
-        <f>'Schedules'!E9-'Schedules'!E10</f>
-        <v/>
-      </c>
-      <c r="F11" s="17">
-        <f>'Schedules'!F9-'Schedules'!F10</f>
-        <v/>
-      </c>
-      <c r="G11" s="17">
-        <f>'Schedules'!G9-'Schedules'!G10</f>
-        <v/>
-      </c>
-      <c r="H11" s="17">
-        <f>'Schedules'!H9-'Schedules'!H10</f>
+      <c r="A11" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     (+) Capital expenditures</t>
+        </is>
+      </c>
+      <c r="C11" s="16">
+        <f>'Assumptions'!C22*'Segments'!C6</f>
+        <v/>
+      </c>
+      <c r="D11" s="16">
+        <f>'Assumptions'!D22*'Segments'!D6</f>
+        <v/>
+      </c>
+      <c r="E11" s="16">
+        <f>'Assumptions'!E22*'Segments'!E6</f>
+        <v/>
+      </c>
+      <c r="F11" s="16">
+        <f>'Assumptions'!F22*'Segments'!F6</f>
+        <v/>
+      </c>
+      <c r="G11" s="16">
+        <f>'Assumptions'!G22*'Segments'!G6</f>
+        <v/>
+      </c>
+      <c r="H11" s="16">
+        <f>'Assumptions'!H22*'Segments'!H6</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Beginning deferred tax liability</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="n">
-        <v>0</v>
+          <t xml:space="preserve">     (−) Depreciation</t>
+        </is>
+      </c>
+      <c r="C12" s="16">
+        <f>'Schedules'!C10*'Assumptions'!C25</f>
+        <v/>
       </c>
       <c r="D12" s="16">
-        <f>'Deal &amp; PPA'!C24</f>
+        <f>'Schedules'!D10*'Assumptions'!C25</f>
         <v/>
       </c>
       <c r="E12" s="16">
-        <f>'Schedules'!D14</f>
+        <f>'Schedules'!E10*'Assumptions'!C25</f>
         <v/>
       </c>
       <c r="F12" s="16">
-        <f>'Schedules'!E14</f>
+        <f>'Schedules'!F10*'Assumptions'!C25</f>
         <v/>
       </c>
       <c r="G12" s="16">
-        <f>'Schedules'!F14</f>
+        <f>'Schedules'!G10*'Assumptions'!C25</f>
         <v/>
       </c>
       <c r="H12" s="16">
-        <f>'Schedules'!G14</f>
+        <f>'Schedules'!H10*'Assumptions'!C25</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Change in DTL (deferred tax benefit)</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="16">
-        <f>-'Assumptions'!C32*'Schedules'!D10</f>
-        <v/>
-      </c>
-      <c r="E13" s="16">
-        <f>-'Assumptions'!C32*'Schedules'!E10</f>
-        <v/>
-      </c>
-      <c r="F13" s="16">
-        <f>-'Assumptions'!C32*'Schedules'!F10</f>
-        <v/>
-      </c>
-      <c r="G13" s="16">
-        <f>-'Assumptions'!C32*'Schedules'!G10</f>
-        <v/>
-      </c>
-      <c r="H13" s="16">
-        <f>-'Assumptions'!C32*'Schedules'!H10</f>
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Ending net PP&amp;E</t>
+        </is>
+      </c>
+      <c r="C13" s="17">
+        <f>'Schedules'!C10</f>
+        <v/>
+      </c>
+      <c r="D13" s="17">
+        <f>'Schedules'!D10+'Schedules'!D11-'Schedules'!D12</f>
+        <v/>
+      </c>
+      <c r="E13" s="17">
+        <f>'Schedules'!E10+'Schedules'!E11-'Schedules'!E12</f>
+        <v/>
+      </c>
+      <c r="F13" s="17">
+        <f>'Schedules'!F10+'Schedules'!F11-'Schedules'!F12</f>
+        <v/>
+      </c>
+      <c r="G13" s="17">
+        <f>'Schedules'!G10+'Schedules'!G11-'Schedules'!G12</f>
+        <v/>
+      </c>
+      <c r="H13" s="17">
+        <f>'Schedules'!H10+'Schedules'!H11-'Schedules'!H12</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Ending deferred tax liability</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" s="17">
-        <f>'Schedules'!D12+'Schedules'!D13</f>
-        <v/>
-      </c>
-      <c r="E14" s="17">
-        <f>'Schedules'!E12+'Schedules'!E13</f>
-        <v/>
-      </c>
-      <c r="F14" s="17">
-        <f>'Schedules'!F12+'Schedules'!F13</f>
-        <v/>
-      </c>
-      <c r="G14" s="17">
-        <f>'Schedules'!G12+'Schedules'!G13</f>
-        <v/>
-      </c>
-      <c r="H14" s="17">
-        <f>'Schedules'!H12+'Schedules'!H13</f>
-        <v/>
+          <t xml:space="preserve">  xAI-Cursor</t>
+        </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>Debt &amp; spectrum obligation</t>
-        </is>
-      </c>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
-      <c r="G15" s="9" t="n"/>
-      <c r="H15" s="9" t="n"/>
-      <c r="I15" s="9" t="n"/>
-      <c r="J15" s="9" t="n"/>
-      <c r="K15" s="9" t="n"/>
+      <c r="A15" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Beginning net PP&amp;E</t>
+        </is>
+      </c>
+      <c r="C15" s="16">
+        <f>'Assumptions'!C28</f>
+        <v/>
+      </c>
+      <c r="D15" s="16">
+        <f>'Assumptions'!C28</f>
+        <v/>
+      </c>
+      <c r="E15" s="16">
+        <f>'Schedules'!D18</f>
+        <v/>
+      </c>
+      <c r="F15" s="16">
+        <f>'Schedules'!E18</f>
+        <v/>
+      </c>
+      <c r="G15" s="16">
+        <f>'Schedules'!F18</f>
+        <v/>
+      </c>
+      <c r="H15" s="16">
+        <f>'Schedules'!G18</f>
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Beginning long-term debt</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="n">
-        <v>12000</v>
+          <t xml:space="preserve">     (+) Capital expenditures</t>
+        </is>
+      </c>
+      <c r="C16" s="16">
+        <f>'Assumptions'!C23*'Segments'!C9</f>
+        <v/>
       </c>
       <c r="D16" s="16">
-        <f>'Balance Sheet'!F21</f>
+        <f>'Assumptions'!D23*'Segments'!D9</f>
         <v/>
       </c>
       <c r="E16" s="16">
-        <f>'Schedules'!D18</f>
+        <f>'Assumptions'!E23*'Segments'!E9</f>
         <v/>
       </c>
       <c r="F16" s="16">
-        <f>'Schedules'!E18</f>
+        <f>'Assumptions'!F23*'Segments'!F9</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>'Schedules'!F18</f>
+        <f>'Assumptions'!G23*'Segments'!G9</f>
         <v/>
       </c>
       <c r="H16" s="16">
-        <f>'Schedules'!G18</f>
+        <f>'Assumptions'!H23*'Segments'!H9</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Net draws / (repayments)</t>
-        </is>
-      </c>
-      <c r="C17" s="16" t="n">
-        <v>0</v>
+          <t xml:space="preserve">     (−) Depreciation</t>
+        </is>
+      </c>
+      <c r="C17" s="16">
+        <f>'Schedules'!C15*'Assumptions'!C26</f>
+        <v/>
       </c>
       <c r="D17" s="16">
-        <f>'Assumptions'!D27</f>
+        <f>'Schedules'!D15*'Assumptions'!C26</f>
         <v/>
       </c>
       <c r="E17" s="16">
-        <f>'Assumptions'!E27</f>
+        <f>'Schedules'!E15*'Assumptions'!C26</f>
         <v/>
       </c>
       <c r="F17" s="16">
-        <f>'Assumptions'!F27</f>
+        <f>'Schedules'!F15*'Assumptions'!C26</f>
         <v/>
       </c>
       <c r="G17" s="16">
-        <f>'Assumptions'!G27</f>
+        <f>'Schedules'!G15*'Assumptions'!C26</f>
         <v/>
       </c>
       <c r="H17" s="16">
-        <f>'Assumptions'!H27</f>
+        <f>'Schedules'!H15*'Assumptions'!C26</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Ending long-term debt</t>
-        </is>
-      </c>
-      <c r="C18" s="17" t="n">
-        <v>12000</v>
+          <t xml:space="preserve">     Ending net PP&amp;E</t>
+        </is>
+      </c>
+      <c r="C18" s="17">
+        <f>'Schedules'!C15</f>
+        <v/>
       </c>
       <c r="D18" s="17">
-        <f>'Schedules'!D16+'Schedules'!D17</f>
+        <f>'Schedules'!D15+'Schedules'!D16-'Schedules'!D17</f>
         <v/>
       </c>
       <c r="E18" s="17">
-        <f>'Schedules'!E16+'Schedules'!E17</f>
+        <f>'Schedules'!E15+'Schedules'!E16-'Schedules'!E17</f>
         <v/>
       </c>
       <c r="F18" s="17">
-        <f>'Schedules'!F16+'Schedules'!F17</f>
+        <f>'Schedules'!F15+'Schedules'!F16-'Schedules'!F17</f>
         <v/>
       </c>
       <c r="G18" s="17">
-        <f>'Schedules'!G16+'Schedules'!G17</f>
+        <f>'Schedules'!G15+'Schedules'!G16-'Schedules'!G17</f>
         <v/>
       </c>
       <c r="H18" s="17">
-        <f>'Schedules'!H16+'Schedules'!H17</f>
+        <f>'Schedules'!H15+'Schedules'!H16-'Schedules'!H17</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Beginning spectrum obligation</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="n">
-        <v>19600</v>
-      </c>
-      <c r="D19" s="16">
-        <f>'Balance Sheet'!F22</f>
-        <v/>
-      </c>
-      <c r="E19" s="16">
-        <f>'Schedules'!D21</f>
-        <v/>
-      </c>
-      <c r="F19" s="16">
-        <f>'Schedules'!E21</f>
-        <v/>
-      </c>
-      <c r="G19" s="16">
-        <f>'Schedules'!F21</f>
-        <v/>
-      </c>
-      <c r="H19" s="16">
-        <f>'Schedules'!G21</f>
-        <v/>
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Total — all segments</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Repayments</t>
-        </is>
-      </c>
-      <c r="C20" s="16" t="n">
-        <v>0</v>
+          <t xml:space="preserve">     Total beginning net PP&amp;E</t>
+        </is>
+      </c>
+      <c r="C20" s="16">
+        <f>'Schedules'!C5+'Schedules'!C10+'Schedules'!C15</f>
+        <v/>
       </c>
       <c r="D20" s="16">
-        <f>'Assumptions'!D28</f>
+        <f>'Schedules'!D5+'Schedules'!D10+'Schedules'!D15</f>
         <v/>
       </c>
       <c r="E20" s="16">
-        <f>'Assumptions'!E28</f>
+        <f>'Schedules'!E5+'Schedules'!E10+'Schedules'!E15</f>
         <v/>
       </c>
       <c r="F20" s="16">
-        <f>'Assumptions'!F28</f>
+        <f>'Schedules'!F5+'Schedules'!F10+'Schedules'!F15</f>
         <v/>
       </c>
       <c r="G20" s="16">
-        <f>'Assumptions'!G28</f>
+        <f>'Schedules'!G5+'Schedules'!G10+'Schedules'!G15</f>
         <v/>
       </c>
       <c r="H20" s="16">
-        <f>'Assumptions'!H28</f>
+        <f>'Schedules'!H5+'Schedules'!H10+'Schedules'!H15</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Ending spectrum obligation</t>
-        </is>
-      </c>
-      <c r="C21" s="17" t="n">
-        <v>19600</v>
-      </c>
-      <c r="D21" s="17">
-        <f>'Schedules'!D19+'Schedules'!D20</f>
-        <v/>
-      </c>
-      <c r="E21" s="17">
-        <f>'Schedules'!E19+'Schedules'!E20</f>
-        <v/>
-      </c>
-      <c r="F21" s="17">
-        <f>'Schedules'!F19+'Schedules'!F20</f>
-        <v/>
-      </c>
-      <c r="G21" s="17">
-        <f>'Schedules'!G19+'Schedules'!G20</f>
-        <v/>
-      </c>
-      <c r="H21" s="17">
-        <f>'Schedules'!H19+'Schedules'!H20</f>
+      <c r="A21" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     (+) Total capital expenditures</t>
+        </is>
+      </c>
+      <c r="C21" s="16">
+        <f>'Schedules'!C6+'Schedules'!C11+'Schedules'!C16</f>
+        <v/>
+      </c>
+      <c r="D21" s="16">
+        <f>'Schedules'!D6+'Schedules'!D11+'Schedules'!D16</f>
+        <v/>
+      </c>
+      <c r="E21" s="16">
+        <f>'Schedules'!E6+'Schedules'!E11+'Schedules'!E16</f>
+        <v/>
+      </c>
+      <c r="F21" s="16">
+        <f>'Schedules'!F6+'Schedules'!F11+'Schedules'!F16</f>
+        <v/>
+      </c>
+      <c r="G21" s="16">
+        <f>'Schedules'!G6+'Schedules'!G11+'Schedules'!G16</f>
+        <v/>
+      </c>
+      <c r="H21" s="16">
+        <f>'Schedules'!H6+'Schedules'!H11+'Schedules'!H16</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Interest expense (on beginning balances)</t>
-        </is>
-      </c>
-      <c r="C22" s="17">
-        <f>('Schedules'!C16+'Schedules'!C19)*'Assumptions'!C30</f>
-        <v/>
-      </c>
-      <c r="D22" s="17">
-        <f>('Schedules'!D16+'Schedules'!D19)*'Assumptions'!C30</f>
-        <v/>
-      </c>
-      <c r="E22" s="17">
-        <f>('Schedules'!E16+'Schedules'!E19)*'Assumptions'!C30</f>
-        <v/>
-      </c>
-      <c r="F22" s="17">
-        <f>('Schedules'!F16+'Schedules'!F19)*'Assumptions'!C30</f>
-        <v/>
-      </c>
-      <c r="G22" s="17">
-        <f>('Schedules'!G16+'Schedules'!G19)*'Assumptions'!C30</f>
-        <v/>
-      </c>
-      <c r="H22" s="17">
-        <f>('Schedules'!H16+'Schedules'!H19)*'Assumptions'!C30</f>
+      <c r="A22" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     (−) Total depreciation</t>
+        </is>
+      </c>
+      <c r="C22" s="16">
+        <f>'Schedules'!C7+'Schedules'!C12+'Schedules'!C17</f>
+        <v/>
+      </c>
+      <c r="D22" s="16">
+        <f>'Schedules'!D7+'Schedules'!D12+'Schedules'!D17</f>
+        <v/>
+      </c>
+      <c r="E22" s="16">
+        <f>'Schedules'!E7+'Schedules'!E12+'Schedules'!E17</f>
+        <v/>
+      </c>
+      <c r="F22" s="16">
+        <f>'Schedules'!F7+'Schedules'!F12+'Schedules'!F17</f>
+        <v/>
+      </c>
+      <c r="G22" s="16">
+        <f>'Schedules'!G7+'Schedules'!G12+'Schedules'!G17</f>
+        <v/>
+      </c>
+      <c r="H22" s="16">
+        <f>'Schedules'!H7+'Schedules'!H12+'Schedules'!H17</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>Tax &amp; NOL carryforward</t>
-        </is>
-      </c>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="9" t="n"/>
-      <c r="G23" s="9" t="n"/>
-      <c r="H23" s="9" t="n"/>
-      <c r="I23" s="9" t="n"/>
-      <c r="J23" s="9" t="n"/>
-      <c r="K23" s="9" t="n"/>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">     Total ending net PP&amp;E</t>
+        </is>
+      </c>
+      <c r="C23" s="17">
+        <f>'Schedules'!C8+'Schedules'!C13+'Schedules'!C18</f>
+        <v/>
+      </c>
+      <c r="D23" s="17">
+        <f>'Schedules'!D8+'Schedules'!D13+'Schedules'!D18</f>
+        <v/>
+      </c>
+      <c r="E23" s="17">
+        <f>'Schedules'!E8+'Schedules'!E13+'Schedules'!E18</f>
+        <v/>
+      </c>
+      <c r="F23" s="17">
+        <f>'Schedules'!F8+'Schedules'!F13+'Schedules'!F18</f>
+        <v/>
+      </c>
+      <c r="G23" s="17">
+        <f>'Schedules'!G8+'Schedules'!G13+'Schedules'!G18</f>
+        <v/>
+      </c>
+      <c r="H23" s="17">
+        <f>'Schedules'!H8+'Schedules'!H13+'Schedules'!H18</f>
+        <v/>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Pre-tax income (from IS)</t>
-        </is>
-      </c>
-      <c r="C24" s="16">
-        <f>'Income Statement'!C22</f>
-        <v/>
-      </c>
-      <c r="D24" s="16">
-        <f>'Income Statement'!D22</f>
-        <v/>
-      </c>
-      <c r="E24" s="16">
-        <f>'Income Statement'!E22</f>
-        <v/>
-      </c>
-      <c r="F24" s="16">
-        <f>'Income Statement'!F22</f>
-        <v/>
-      </c>
-      <c r="G24" s="16">
-        <f>'Income Statement'!G22</f>
-        <v/>
-      </c>
-      <c r="H24" s="16">
-        <f>'Income Statement'!H22</f>
-        <v/>
-      </c>
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Acquired intangibles &amp; deferred tax</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n"/>
+      <c r="G24" s="9" t="n"/>
+      <c r="H24" s="9" t="n"/>
+      <c r="I24" s="9" t="n"/>
+      <c r="J24" s="9" t="n"/>
+      <c r="K24" s="9" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Taxable income (add back non-deductible amort)</t>
-        </is>
-      </c>
-      <c r="C25" s="16">
-        <f>'Schedules'!C24+'Schedules'!C10</f>
-        <v/>
+          <t xml:space="preserve">  Beginning intangibles, net</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="D25" s="16">
-        <f>'Schedules'!D24+'Schedules'!D10</f>
+        <f>'Deal &amp; PPA'!C21</f>
         <v/>
       </c>
       <c r="E25" s="16">
-        <f>'Schedules'!E24+'Schedules'!E10</f>
+        <f>'Schedules'!D27</f>
         <v/>
       </c>
       <c r="F25" s="16">
-        <f>'Schedules'!F24+'Schedules'!F10</f>
+        <f>'Schedules'!E27</f>
         <v/>
       </c>
       <c r="G25" s="16">
-        <f>'Schedules'!G24+'Schedules'!G10</f>
+        <f>'Schedules'!F27</f>
         <v/>
       </c>
       <c r="H25" s="16">
-        <f>'Schedules'!H24+'Schedules'!H10</f>
+        <f>'Schedules'!G27</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Beginning NOL balance</t>
-        </is>
-      </c>
-      <c r="C26" s="16">
-        <f>'Assumptions'!C33</f>
-        <v/>
+          <t xml:space="preserve">  Amortization</t>
+        </is>
+      </c>
+      <c r="C26" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="D26" s="16">
-        <f>'Schedules'!C29</f>
+        <f>MIN('Schedules'!D25,'Deal &amp; PPA'!C22)</f>
         <v/>
       </c>
       <c r="E26" s="16">
-        <f>'Schedules'!D29</f>
+        <f>MIN('Schedules'!E25,'Deal &amp; PPA'!C22)</f>
         <v/>
       </c>
       <c r="F26" s="16">
-        <f>'Schedules'!E29</f>
+        <f>MIN('Schedules'!F25,'Deal &amp; PPA'!C22)</f>
         <v/>
       </c>
       <c r="G26" s="16">
-        <f>'Schedules'!F29</f>
+        <f>MIN('Schedules'!G25,'Deal &amp; PPA'!C22)</f>
         <v/>
       </c>
       <c r="H26" s="16">
-        <f>'Schedules'!G29</f>
+        <f>MIN('Schedules'!H25,'Deal &amp; PPA'!C22)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  NOL utilised</t>
-        </is>
-      </c>
-      <c r="C27" s="16">
-        <f>MIN('Schedules'!C26,'Assumptions'!C34*MAX(0,'Schedules'!C25))</f>
-        <v/>
-      </c>
-      <c r="D27" s="16">
-        <f>MIN('Schedules'!D26,'Assumptions'!C34*MAX(0,'Schedules'!D25))</f>
-        <v/>
-      </c>
-      <c r="E27" s="16">
-        <f>MIN('Schedules'!E26,'Assumptions'!C34*MAX(0,'Schedules'!E25))</f>
-        <v/>
-      </c>
-      <c r="F27" s="16">
-        <f>MIN('Schedules'!F26,'Assumptions'!C34*MAX(0,'Schedules'!F25))</f>
-        <v/>
-      </c>
-      <c r="G27" s="16">
-        <f>MIN('Schedules'!G26,'Assumptions'!C34*MAX(0,'Schedules'!G25))</f>
-        <v/>
-      </c>
-      <c r="H27" s="16">
-        <f>MIN('Schedules'!H26,'Assumptions'!C34*MAX(0,'Schedules'!H25))</f>
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ending intangibles, net</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="17">
+        <f>'Schedules'!D25-'Schedules'!D26</f>
+        <v/>
+      </c>
+      <c r="E27" s="17">
+        <f>'Schedules'!E25-'Schedules'!E26</f>
+        <v/>
+      </c>
+      <c r="F27" s="17">
+        <f>'Schedules'!F25-'Schedules'!F26</f>
+        <v/>
+      </c>
+      <c r="G27" s="17">
+        <f>'Schedules'!G25-'Schedules'!G26</f>
+        <v/>
+      </c>
+      <c r="H27" s="17">
+        <f>'Schedules'!H25-'Schedules'!H26</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="10" t="inlineStr">
         <is>
-          <t xml:space="preserve">  NOL generated</t>
-        </is>
-      </c>
-      <c r="C28" s="16">
-        <f>MAX(0,-'Schedules'!C25)</f>
-        <v/>
+          <t xml:space="preserve">  Beginning deferred tax liability</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="D28" s="16">
-        <f>MAX(0,-'Schedules'!D25)</f>
+        <f>'Deal &amp; PPA'!C24</f>
         <v/>
       </c>
       <c r="E28" s="16">
-        <f>MAX(0,-'Schedules'!E25)</f>
+        <f>'Schedules'!D30</f>
         <v/>
       </c>
       <c r="F28" s="16">
-        <f>MAX(0,-'Schedules'!F25)</f>
+        <f>'Schedules'!E30</f>
         <v/>
       </c>
       <c r="G28" s="16">
-        <f>MAX(0,-'Schedules'!G25)</f>
+        <f>'Schedules'!F30</f>
         <v/>
       </c>
       <c r="H28" s="16">
-        <f>MAX(0,-'Schedules'!H25)</f>
+        <f>'Schedules'!G30</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  Ending NOL balance</t>
-        </is>
-      </c>
-      <c r="C29" s="17">
-        <f>'Schedules'!C26-'Schedules'!C27+'Schedules'!C28</f>
-        <v/>
-      </c>
-      <c r="D29" s="17">
-        <f>'Schedules'!D26-'Schedules'!D27+'Schedules'!D28</f>
-        <v/>
-      </c>
-      <c r="E29" s="17">
-        <f>'Schedules'!E26-'Schedules'!E27+'Schedules'!E28</f>
-        <v/>
-      </c>
-      <c r="F29" s="17">
-        <f>'Schedules'!F26-'Schedules'!F27+'Schedules'!F28</f>
-        <v/>
-      </c>
-      <c r="G29" s="17">
-        <f>'Schedules'!G26-'Schedules'!G27+'Schedules'!G28</f>
-        <v/>
-      </c>
-      <c r="H29" s="17">
-        <f>'Schedules'!H26-'Schedules'!H27+'Schedules'!H28</f>
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Change in DTL (deferred tax benefit)</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" s="16">
+        <f>-'Assumptions'!C35*'Schedules'!D26</f>
+        <v/>
+      </c>
+      <c r="E29" s="16">
+        <f>-'Assumptions'!C35*'Schedules'!E26</f>
+        <v/>
+      </c>
+      <c r="F29" s="16">
+        <f>-'Assumptions'!C35*'Schedules'!F26</f>
+        <v/>
+      </c>
+      <c r="G29" s="16">
+        <f>-'Assumptions'!C35*'Schedules'!G26</f>
+        <v/>
+      </c>
+      <c r="H29" s="16">
+        <f>-'Assumptions'!C35*'Schedules'!H26</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
+          <t xml:space="preserve">  Ending deferred tax liability</t>
+        </is>
+      </c>
+      <c r="C30" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="17">
+        <f>'Schedules'!D28+'Schedules'!D29</f>
+        <v/>
+      </c>
+      <c r="E30" s="17">
+        <f>'Schedules'!E28+'Schedules'!E29</f>
+        <v/>
+      </c>
+      <c r="F30" s="17">
+        <f>'Schedules'!F28+'Schedules'!F29</f>
+        <v/>
+      </c>
+      <c r="G30" s="17">
+        <f>'Schedules'!G28+'Schedules'!G29</f>
+        <v/>
+      </c>
+      <c r="H30" s="17">
+        <f>'Schedules'!H28+'Schedules'!H29</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>Debt &amp; spectrum obligation</t>
+        </is>
+      </c>
+      <c r="B31" s="9" t="n"/>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="9" t="n"/>
+      <c r="G31" s="9" t="n"/>
+      <c r="H31" s="9" t="n"/>
+      <c r="I31" s="9" t="n"/>
+      <c r="J31" s="9" t="n"/>
+      <c r="K31" s="9" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Beginning long-term debt</t>
+        </is>
+      </c>
+      <c r="C32" s="16" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D32" s="16">
+        <f>'Balance Sheet'!F21</f>
+        <v/>
+      </c>
+      <c r="E32" s="16">
+        <f>'Schedules'!D34</f>
+        <v/>
+      </c>
+      <c r="F32" s="16">
+        <f>'Schedules'!E34</f>
+        <v/>
+      </c>
+      <c r="G32" s="16">
+        <f>'Schedules'!F34</f>
+        <v/>
+      </c>
+      <c r="H32" s="16">
+        <f>'Schedules'!G34</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Net draws / (repayments)</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="16">
+        <f>'Assumptions'!D30</f>
+        <v/>
+      </c>
+      <c r="E33" s="16">
+        <f>'Assumptions'!E30</f>
+        <v/>
+      </c>
+      <c r="F33" s="16">
+        <f>'Assumptions'!F30</f>
+        <v/>
+      </c>
+      <c r="G33" s="16">
+        <f>'Assumptions'!G30</f>
+        <v/>
+      </c>
+      <c r="H33" s="16">
+        <f>'Assumptions'!H30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ending long-term debt</t>
+        </is>
+      </c>
+      <c r="C34" s="17" t="n">
+        <v>12000</v>
+      </c>
+      <c r="D34" s="17">
+        <f>'Schedules'!D32+'Schedules'!D33</f>
+        <v/>
+      </c>
+      <c r="E34" s="17">
+        <f>'Schedules'!E32+'Schedules'!E33</f>
+        <v/>
+      </c>
+      <c r="F34" s="17">
+        <f>'Schedules'!F32+'Schedules'!F33</f>
+        <v/>
+      </c>
+      <c r="G34" s="17">
+        <f>'Schedules'!G32+'Schedules'!G33</f>
+        <v/>
+      </c>
+      <c r="H34" s="17">
+        <f>'Schedules'!H32+'Schedules'!H33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Beginning spectrum obligation</t>
+        </is>
+      </c>
+      <c r="C35" s="16" t="n">
+        <v>19600</v>
+      </c>
+      <c r="D35" s="16">
+        <f>'Balance Sheet'!F22</f>
+        <v/>
+      </c>
+      <c r="E35" s="16">
+        <f>'Schedules'!D37</f>
+        <v/>
+      </c>
+      <c r="F35" s="16">
+        <f>'Schedules'!E37</f>
+        <v/>
+      </c>
+      <c r="G35" s="16">
+        <f>'Schedules'!F37</f>
+        <v/>
+      </c>
+      <c r="H35" s="16">
+        <f>'Schedules'!G37</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Repayments</t>
+        </is>
+      </c>
+      <c r="C36" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="16">
+        <f>'Assumptions'!D31</f>
+        <v/>
+      </c>
+      <c r="E36" s="16">
+        <f>'Assumptions'!E31</f>
+        <v/>
+      </c>
+      <c r="F36" s="16">
+        <f>'Assumptions'!F31</f>
+        <v/>
+      </c>
+      <c r="G36" s="16">
+        <f>'Assumptions'!G31</f>
+        <v/>
+      </c>
+      <c r="H36" s="16">
+        <f>'Assumptions'!H31</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ending spectrum obligation</t>
+        </is>
+      </c>
+      <c r="C37" s="17" t="n">
+        <v>19600</v>
+      </c>
+      <c r="D37" s="17">
+        <f>'Schedules'!D35+'Schedules'!D36</f>
+        <v/>
+      </c>
+      <c r="E37" s="17">
+        <f>'Schedules'!E35+'Schedules'!E36</f>
+        <v/>
+      </c>
+      <c r="F37" s="17">
+        <f>'Schedules'!F35+'Schedules'!F36</f>
+        <v/>
+      </c>
+      <c r="G37" s="17">
+        <f>'Schedules'!G35+'Schedules'!G36</f>
+        <v/>
+      </c>
+      <c r="H37" s="17">
+        <f>'Schedules'!H35+'Schedules'!H36</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Interest expense (on beginning balances)</t>
+        </is>
+      </c>
+      <c r="C38" s="17">
+        <f>('Schedules'!C32+'Schedules'!C35)*'Assumptions'!C33</f>
+        <v/>
+      </c>
+      <c r="D38" s="17">
+        <f>('Schedules'!D32+'Schedules'!D35)*'Assumptions'!C33</f>
+        <v/>
+      </c>
+      <c r="E38" s="17">
+        <f>('Schedules'!E32+'Schedules'!E35)*'Assumptions'!C33</f>
+        <v/>
+      </c>
+      <c r="F38" s="17">
+        <f>('Schedules'!F32+'Schedules'!F35)*'Assumptions'!C33</f>
+        <v/>
+      </c>
+      <c r="G38" s="17">
+        <f>('Schedules'!G32+'Schedules'!G35)*'Assumptions'!C33</f>
+        <v/>
+      </c>
+      <c r="H38" s="17">
+        <f>('Schedules'!H32+'Schedules'!H35)*'Assumptions'!C33</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>Tax &amp; NOL carryforward</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="n"/>
+      <c r="C39" s="9" t="n"/>
+      <c r="D39" s="9" t="n"/>
+      <c r="E39" s="9" t="n"/>
+      <c r="F39" s="9" t="n"/>
+      <c r="G39" s="9" t="n"/>
+      <c r="H39" s="9" t="n"/>
+      <c r="I39" s="9" t="n"/>
+      <c r="J39" s="9" t="n"/>
+      <c r="K39" s="9" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Pre-tax income (from IS)</t>
+        </is>
+      </c>
+      <c r="C40" s="16">
+        <f>'Income Statement'!C22</f>
+        <v/>
+      </c>
+      <c r="D40" s="16">
+        <f>'Income Statement'!D22</f>
+        <v/>
+      </c>
+      <c r="E40" s="16">
+        <f>'Income Statement'!E22</f>
+        <v/>
+      </c>
+      <c r="F40" s="16">
+        <f>'Income Statement'!F22</f>
+        <v/>
+      </c>
+      <c r="G40" s="16">
+        <f>'Income Statement'!G22</f>
+        <v/>
+      </c>
+      <c r="H40" s="16">
+        <f>'Income Statement'!H22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Taxable income (add back non-deductible amort)</t>
+        </is>
+      </c>
+      <c r="C41" s="16">
+        <f>'Schedules'!C40+'Schedules'!C26</f>
+        <v/>
+      </c>
+      <c r="D41" s="16">
+        <f>'Schedules'!D40+'Schedules'!D26</f>
+        <v/>
+      </c>
+      <c r="E41" s="16">
+        <f>'Schedules'!E40+'Schedules'!E26</f>
+        <v/>
+      </c>
+      <c r="F41" s="16">
+        <f>'Schedules'!F40+'Schedules'!F26</f>
+        <v/>
+      </c>
+      <c r="G41" s="16">
+        <f>'Schedules'!G40+'Schedules'!G26</f>
+        <v/>
+      </c>
+      <c r="H41" s="16">
+        <f>'Schedules'!H40+'Schedules'!H26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Beginning NOL balance</t>
+        </is>
+      </c>
+      <c r="C42" s="16">
+        <f>'Assumptions'!C36</f>
+        <v/>
+      </c>
+      <c r="D42" s="16">
+        <f>'Schedules'!C45</f>
+        <v/>
+      </c>
+      <c r="E42" s="16">
+        <f>'Schedules'!D45</f>
+        <v/>
+      </c>
+      <c r="F42" s="16">
+        <f>'Schedules'!E45</f>
+        <v/>
+      </c>
+      <c r="G42" s="16">
+        <f>'Schedules'!F45</f>
+        <v/>
+      </c>
+      <c r="H42" s="16">
+        <f>'Schedules'!G45</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NOL utilised</t>
+        </is>
+      </c>
+      <c r="C43" s="16">
+        <f>MIN('Schedules'!C42,'Assumptions'!C37*MAX(0,'Schedules'!C41))</f>
+        <v/>
+      </c>
+      <c r="D43" s="16">
+        <f>MIN('Schedules'!D42,'Assumptions'!C37*MAX(0,'Schedules'!D41))</f>
+        <v/>
+      </c>
+      <c r="E43" s="16">
+        <f>MIN('Schedules'!E42,'Assumptions'!C37*MAX(0,'Schedules'!E41))</f>
+        <v/>
+      </c>
+      <c r="F43" s="16">
+        <f>MIN('Schedules'!F42,'Assumptions'!C37*MAX(0,'Schedules'!F41))</f>
+        <v/>
+      </c>
+      <c r="G43" s="16">
+        <f>MIN('Schedules'!G42,'Assumptions'!C37*MAX(0,'Schedules'!G41))</f>
+        <v/>
+      </c>
+      <c r="H43" s="16">
+        <f>MIN('Schedules'!H42,'Assumptions'!C37*MAX(0,'Schedules'!H41))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  NOL generated</t>
+        </is>
+      </c>
+      <c r="C44" s="16">
+        <f>MAX(0,-'Schedules'!C41)</f>
+        <v/>
+      </c>
+      <c r="D44" s="16">
+        <f>MAX(0,-'Schedules'!D41)</f>
+        <v/>
+      </c>
+      <c r="E44" s="16">
+        <f>MAX(0,-'Schedules'!E41)</f>
+        <v/>
+      </c>
+      <c r="F44" s="16">
+        <f>MAX(0,-'Schedules'!F41)</f>
+        <v/>
+      </c>
+      <c r="G44" s="16">
+        <f>MAX(0,-'Schedules'!G41)</f>
+        <v/>
+      </c>
+      <c r="H44" s="16">
+        <f>MAX(0,-'Schedules'!H41)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Ending NOL balance</t>
+        </is>
+      </c>
+      <c r="C45" s="17">
+        <f>'Schedules'!C42-'Schedules'!C43+'Schedules'!C44</f>
+        <v/>
+      </c>
+      <c r="D45" s="17">
+        <f>'Schedules'!D42-'Schedules'!D43+'Schedules'!D44</f>
+        <v/>
+      </c>
+      <c r="E45" s="17">
+        <f>'Schedules'!E42-'Schedules'!E43+'Schedules'!E44</f>
+        <v/>
+      </c>
+      <c r="F45" s="17">
+        <f>'Schedules'!F42-'Schedules'!F43+'Schedules'!F44</f>
+        <v/>
+      </c>
+      <c r="G45" s="17">
+        <f>'Schedules'!G42-'Schedules'!G43+'Schedules'!G44</f>
+        <v/>
+      </c>
+      <c r="H45" s="17">
+        <f>'Schedules'!H42-'Schedules'!H43+'Schedules'!H44</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
           <t xml:space="preserve">  Current income tax</t>
         </is>
       </c>
-      <c r="C30" s="17">
-        <f>'Assumptions'!C32*MAX(0,'Schedules'!C25-'Schedules'!C27)</f>
-        <v/>
-      </c>
-      <c r="D30" s="17">
-        <f>'Assumptions'!C32*MAX(0,'Schedules'!D25-'Schedules'!D27)</f>
-        <v/>
-      </c>
-      <c r="E30" s="17">
-        <f>'Assumptions'!C32*MAX(0,'Schedules'!E25-'Schedules'!E27)</f>
-        <v/>
-      </c>
-      <c r="F30" s="17">
-        <f>'Assumptions'!C32*MAX(0,'Schedules'!F25-'Schedules'!F27)</f>
-        <v/>
-      </c>
-      <c r="G30" s="17">
-        <f>'Assumptions'!C32*MAX(0,'Schedules'!G25-'Schedules'!G27)</f>
-        <v/>
-      </c>
-      <c r="H30" s="17">
-        <f>'Assumptions'!C32*MAX(0,'Schedules'!H25-'Schedules'!H27)</f>
+      <c r="C46" s="17">
+        <f>'Assumptions'!C35*MAX(0,'Schedules'!C41-'Schedules'!C43)</f>
+        <v/>
+      </c>
+      <c r="D46" s="17">
+        <f>'Assumptions'!C35*MAX(0,'Schedules'!D41-'Schedules'!D43)</f>
+        <v/>
+      </c>
+      <c r="E46" s="17">
+        <f>'Assumptions'!C35*MAX(0,'Schedules'!E41-'Schedules'!E43)</f>
+        <v/>
+      </c>
+      <c r="F46" s="17">
+        <f>'Assumptions'!C35*MAX(0,'Schedules'!F41-'Schedules'!F43)</f>
+        <v/>
+      </c>
+      <c r="G46" s="17">
+        <f>'Assumptions'!C35*MAX(0,'Schedules'!G41-'Schedules'!G43)</f>
+        <v/>
+      </c>
+      <c r="H46" s="17">
+        <f>'Assumptions'!C35*MAX(0,'Schedules'!H41-'Schedules'!H43)</f>
         <v/>
       </c>
     </row>
@@ -4383,27 +4850,27 @@
         </is>
       </c>
       <c r="C16" s="16">
-        <f>'Schedules'!C6</f>
+        <f>'Schedules'!C22</f>
         <v/>
       </c>
       <c r="D16" s="16">
-        <f>'Schedules'!D6</f>
+        <f>'Schedules'!D22</f>
         <v/>
       </c>
       <c r="E16" s="16">
-        <f>'Schedules'!E6</f>
+        <f>'Schedules'!E22</f>
         <v/>
       </c>
       <c r="F16" s="16">
-        <f>'Schedules'!F6</f>
+        <f>'Schedules'!F22</f>
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>'Schedules'!G6</f>
+        <f>'Schedules'!G22</f>
         <v/>
       </c>
       <c r="H16" s="16">
-        <f>'Schedules'!H6</f>
+        <f>'Schedules'!H22</f>
         <v/>
       </c>
     </row>
@@ -4414,27 +4881,27 @@
         </is>
       </c>
       <c r="C17" s="16">
-        <f>'Schedules'!C10</f>
+        <f>'Schedules'!C26</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>'Schedules'!D10</f>
+        <f>'Schedules'!D26</f>
         <v/>
       </c>
       <c r="E17" s="16">
-        <f>'Schedules'!E10</f>
+        <f>'Schedules'!E26</f>
         <v/>
       </c>
       <c r="F17" s="16">
-        <f>'Schedules'!F10</f>
+        <f>'Schedules'!F26</f>
         <v/>
       </c>
       <c r="G17" s="16">
-        <f>'Schedules'!G10</f>
+        <f>'Schedules'!G26</f>
         <v/>
       </c>
       <c r="H17" s="16">
-        <f>'Schedules'!H10</f>
+        <f>'Schedules'!H26</f>
         <v/>
       </c>
     </row>
@@ -4507,27 +4974,27 @@
         </is>
       </c>
       <c r="C20" s="16">
-        <f>-'Schedules'!C22</f>
+        <f>-'Schedules'!C38</f>
         <v/>
       </c>
       <c r="D20" s="16">
-        <f>-'Schedules'!D22</f>
+        <f>-'Schedules'!D38</f>
         <v/>
       </c>
       <c r="E20" s="16">
-        <f>-'Schedules'!E22</f>
+        <f>-'Schedules'!E38</f>
         <v/>
       </c>
       <c r="F20" s="16">
-        <f>-'Schedules'!F22</f>
+        <f>-'Schedules'!F38</f>
         <v/>
       </c>
       <c r="G20" s="16">
-        <f>-'Schedules'!G22</f>
+        <f>-'Schedules'!G38</f>
         <v/>
       </c>
       <c r="H20" s="16">
-        <f>-'Schedules'!H22</f>
+        <f>-'Schedules'!H38</f>
         <v/>
       </c>
     </row>
@@ -4538,27 +5005,27 @@
         </is>
       </c>
       <c r="C21" s="16">
-        <f>12000*'Assumptions'!C31</f>
+        <f>12000*'Assumptions'!C34</f>
         <v/>
       </c>
       <c r="D21" s="16">
-        <f>'Balance Sheet'!F4*'Assumptions'!C31</f>
+        <f>'Balance Sheet'!F4*'Assumptions'!C34</f>
         <v/>
       </c>
       <c r="E21" s="16">
-        <f>'Balance Sheet'!G4*'Assumptions'!C31</f>
+        <f>'Balance Sheet'!G4*'Assumptions'!C34</f>
         <v/>
       </c>
       <c r="F21" s="16">
-        <f>'Balance Sheet'!H4*'Assumptions'!C31</f>
+        <f>'Balance Sheet'!H4*'Assumptions'!C34</f>
         <v/>
       </c>
       <c r="G21" s="16">
-        <f>'Balance Sheet'!I4*'Assumptions'!C31</f>
+        <f>'Balance Sheet'!I4*'Assumptions'!C34</f>
         <v/>
       </c>
       <c r="H21" s="16">
-        <f>'Balance Sheet'!J4*'Assumptions'!C31</f>
+        <f>'Balance Sheet'!J4*'Assumptions'!C34</f>
         <v/>
       </c>
     </row>
@@ -4600,27 +5067,27 @@
         </is>
       </c>
       <c r="C23" s="16">
-        <f>-'Schedules'!C30</f>
+        <f>-'Schedules'!C46</f>
         <v/>
       </c>
       <c r="D23" s="16">
-        <f>-'Schedules'!D30</f>
+        <f>-'Schedules'!D46</f>
         <v/>
       </c>
       <c r="E23" s="16">
-        <f>-'Schedules'!E30</f>
+        <f>-'Schedules'!E46</f>
         <v/>
       </c>
       <c r="F23" s="16">
-        <f>-'Schedules'!F30</f>
+        <f>-'Schedules'!F46</f>
         <v/>
       </c>
       <c r="G23" s="16">
-        <f>-'Schedules'!G30</f>
+        <f>-'Schedules'!G46</f>
         <v/>
       </c>
       <c r="H23" s="16">
-        <f>-'Schedules'!H30</f>
+        <f>-'Schedules'!H46</f>
         <v/>
       </c>
     </row>
@@ -4631,27 +5098,27 @@
         </is>
       </c>
       <c r="C24" s="16">
-        <f>-'Schedules'!C13</f>
+        <f>-'Schedules'!C29</f>
         <v/>
       </c>
       <c r="D24" s="16">
-        <f>-'Schedules'!D13</f>
+        <f>-'Schedules'!D29</f>
         <v/>
       </c>
       <c r="E24" s="16">
-        <f>-'Schedules'!E13</f>
+        <f>-'Schedules'!E29</f>
         <v/>
       </c>
       <c r="F24" s="16">
-        <f>-'Schedules'!F13</f>
+        <f>-'Schedules'!F29</f>
         <v/>
       </c>
       <c r="G24" s="16">
-        <f>-'Schedules'!G13</f>
+        <f>-'Schedules'!G29</f>
         <v/>
       </c>
       <c r="H24" s="16">
-        <f>-'Schedules'!H13</f>
+        <f>-'Schedules'!H29</f>
         <v/>
       </c>
     </row>
@@ -4724,27 +5191,27 @@
         </is>
       </c>
       <c r="C27" s="23">
-        <f>'Assumptions'!C35+'Deal &amp; PPA'!C6</f>
+        <f>'Assumptions'!C38+'Deal &amp; PPA'!C6</f>
         <v/>
       </c>
       <c r="D27" s="23">
-        <f>'Assumptions'!C35+'Deal &amp; PPA'!C6</f>
+        <f>'Assumptions'!C38+'Deal &amp; PPA'!C6</f>
         <v/>
       </c>
       <c r="E27" s="23">
-        <f>'Assumptions'!C35+'Deal &amp; PPA'!C6</f>
+        <f>'Assumptions'!C38+'Deal &amp; PPA'!C6</f>
         <v/>
       </c>
       <c r="F27" s="23">
-        <f>'Assumptions'!C35+'Deal &amp; PPA'!C6</f>
+        <f>'Assumptions'!C38+'Deal &amp; PPA'!C6</f>
         <v/>
       </c>
       <c r="G27" s="23">
-        <f>'Assumptions'!C35+'Deal &amp; PPA'!C6</f>
+        <f>'Assumptions'!C38+'Deal &amp; PPA'!C6</f>
         <v/>
       </c>
       <c r="H27" s="23">
-        <f>'Assumptions'!C35+'Deal &amp; PPA'!C6</f>
+        <f>'Assumptions'!C38+'Deal &amp; PPA'!C6</f>
         <v/>
       </c>
     </row>
@@ -5080,23 +5547,23 @@
         <v/>
       </c>
       <c r="G5" s="16">
-        <f>'Income Statement'!D8*'Assumptions'!C38</f>
+        <f>'Income Statement'!D8*'Assumptions'!C41</f>
         <v/>
       </c>
       <c r="H5" s="16">
-        <f>'Income Statement'!E8*'Assumptions'!C38</f>
+        <f>'Income Statement'!E8*'Assumptions'!C41</f>
         <v/>
       </c>
       <c r="I5" s="16">
-        <f>'Income Statement'!F8*'Assumptions'!C38</f>
+        <f>'Income Statement'!F8*'Assumptions'!C41</f>
         <v/>
       </c>
       <c r="J5" s="16">
-        <f>'Income Statement'!G8*'Assumptions'!C38</f>
+        <f>'Income Statement'!G8*'Assumptions'!C41</f>
         <v/>
       </c>
       <c r="K5" s="16">
-        <f>'Income Statement'!H8*'Assumptions'!C38</f>
+        <f>'Income Statement'!H8*'Assumptions'!C41</f>
         <v/>
       </c>
     </row>
@@ -5120,23 +5587,23 @@
         <v/>
       </c>
       <c r="G6" s="16">
-        <f>'Income Statement'!D8*'Assumptions'!C39</f>
+        <f>'Income Statement'!D8*'Assumptions'!C42</f>
         <v/>
       </c>
       <c r="H6" s="16">
-        <f>'Income Statement'!E8*'Assumptions'!C39</f>
+        <f>'Income Statement'!E8*'Assumptions'!C42</f>
         <v/>
       </c>
       <c r="I6" s="16">
-        <f>'Income Statement'!F8*'Assumptions'!C39</f>
+        <f>'Income Statement'!F8*'Assumptions'!C42</f>
         <v/>
       </c>
       <c r="J6" s="16">
-        <f>'Income Statement'!G8*'Assumptions'!C39</f>
+        <f>'Income Statement'!G8*'Assumptions'!C42</f>
         <v/>
       </c>
       <c r="K6" s="16">
-        <f>'Income Statement'!H8*'Assumptions'!C39</f>
+        <f>'Income Statement'!H8*'Assumptions'!C42</f>
         <v/>
       </c>
     </row>
@@ -5160,23 +5627,23 @@
         <v/>
       </c>
       <c r="G7" s="16">
-        <f>'Income Statement'!D8*'Assumptions'!C40</f>
+        <f>'Income Statement'!D8*'Assumptions'!C43</f>
         <v/>
       </c>
       <c r="H7" s="16">
-        <f>'Income Statement'!E8*'Assumptions'!C40</f>
+        <f>'Income Statement'!E8*'Assumptions'!C43</f>
         <v/>
       </c>
       <c r="I7" s="16">
-        <f>'Income Statement'!F8*'Assumptions'!C40</f>
+        <f>'Income Statement'!F8*'Assumptions'!C43</f>
         <v/>
       </c>
       <c r="J7" s="16">
-        <f>'Income Statement'!G8*'Assumptions'!C40</f>
+        <f>'Income Statement'!G8*'Assumptions'!C43</f>
         <v/>
       </c>
       <c r="K7" s="16">
-        <f>'Income Statement'!H8*'Assumptions'!C40</f>
+        <f>'Income Statement'!H8*'Assumptions'!C43</f>
         <v/>
       </c>
     </row>
@@ -5243,23 +5710,23 @@
         <v/>
       </c>
       <c r="G9" s="16">
-        <f>'Schedules'!D7</f>
+        <f>'Schedules'!D23</f>
         <v/>
       </c>
       <c r="H9" s="16">
-        <f>'Schedules'!E7</f>
+        <f>'Schedules'!E23</f>
         <v/>
       </c>
       <c r="I9" s="16">
-        <f>'Schedules'!F7</f>
+        <f>'Schedules'!F23</f>
         <v/>
       </c>
       <c r="J9" s="16">
-        <f>'Schedules'!G7</f>
+        <f>'Schedules'!G23</f>
         <v/>
       </c>
       <c r="K9" s="16">
-        <f>'Schedules'!H7</f>
+        <f>'Schedules'!H23</f>
         <v/>
       </c>
     </row>
@@ -5284,23 +5751,23 @@
         <v/>
       </c>
       <c r="G10" s="16">
-        <f>'Schedules'!D11</f>
+        <f>'Schedules'!D27</f>
         <v/>
       </c>
       <c r="H10" s="16">
-        <f>'Schedules'!E11</f>
+        <f>'Schedules'!E27</f>
         <v/>
       </c>
       <c r="I10" s="16">
-        <f>'Schedules'!F11</f>
+        <f>'Schedules'!F27</f>
         <v/>
       </c>
       <c r="J10" s="16">
-        <f>'Schedules'!G11</f>
+        <f>'Schedules'!G27</f>
         <v/>
       </c>
       <c r="K10" s="16">
-        <f>'Schedules'!H11</f>
+        <f>'Schedules'!H27</f>
         <v/>
       </c>
     </row>
@@ -5505,23 +5972,23 @@
         <v/>
       </c>
       <c r="G16" s="16">
-        <f>'Income Statement'!D8*'Assumptions'!C41</f>
+        <f>'Income Statement'!D8*'Assumptions'!C44</f>
         <v/>
       </c>
       <c r="H16" s="16">
-        <f>'Income Statement'!E8*'Assumptions'!C41</f>
+        <f>'Income Statement'!E8*'Assumptions'!C44</f>
         <v/>
       </c>
       <c r="I16" s="16">
-        <f>'Income Statement'!F8*'Assumptions'!C41</f>
+        <f>'Income Statement'!F8*'Assumptions'!C44</f>
         <v/>
       </c>
       <c r="J16" s="16">
-        <f>'Income Statement'!G8*'Assumptions'!C41</f>
+        <f>'Income Statement'!G8*'Assumptions'!C44</f>
         <v/>
       </c>
       <c r="K16" s="16">
-        <f>'Income Statement'!H8*'Assumptions'!C41</f>
+        <f>'Income Statement'!H8*'Assumptions'!C44</f>
         <v/>
       </c>
     </row>
@@ -5545,23 +6012,23 @@
         <v/>
       </c>
       <c r="G17" s="16">
-        <f>'Income Statement'!D8*'Assumptions'!C42</f>
+        <f>'Income Statement'!D8*'Assumptions'!C45</f>
         <v/>
       </c>
       <c r="H17" s="16">
-        <f>'Income Statement'!E8*'Assumptions'!C42</f>
+        <f>'Income Statement'!E8*'Assumptions'!C45</f>
         <v/>
       </c>
       <c r="I17" s="16">
-        <f>'Income Statement'!F8*'Assumptions'!C42</f>
+        <f>'Income Statement'!F8*'Assumptions'!C45</f>
         <v/>
       </c>
       <c r="J17" s="16">
-        <f>'Income Statement'!G8*'Assumptions'!C42</f>
+        <f>'Income Statement'!G8*'Assumptions'!C45</f>
         <v/>
       </c>
       <c r="K17" s="16">
-        <f>'Income Statement'!H8*'Assumptions'!C42</f>
+        <f>'Income Statement'!H8*'Assumptions'!C45</f>
         <v/>
       </c>
     </row>
@@ -5585,23 +6052,23 @@
         <v/>
       </c>
       <c r="G18" s="16">
-        <f>'Income Statement'!D8*'Assumptions'!C43</f>
+        <f>'Income Statement'!D8*'Assumptions'!C46</f>
         <v/>
       </c>
       <c r="H18" s="16">
-        <f>'Income Statement'!E8*'Assumptions'!C43</f>
+        <f>'Income Statement'!E8*'Assumptions'!C46</f>
         <v/>
       </c>
       <c r="I18" s="16">
-        <f>'Income Statement'!F8*'Assumptions'!C43</f>
+        <f>'Income Statement'!F8*'Assumptions'!C46</f>
         <v/>
       </c>
       <c r="J18" s="16">
-        <f>'Income Statement'!G8*'Assumptions'!C43</f>
+        <f>'Income Statement'!G8*'Assumptions'!C46</f>
         <v/>
       </c>
       <c r="K18" s="16">
-        <f>'Income Statement'!H8*'Assumptions'!C43</f>
+        <f>'Income Statement'!H8*'Assumptions'!C46</f>
         <v/>
       </c>
     </row>
@@ -5625,23 +6092,23 @@
         <v/>
       </c>
       <c r="G19" s="16">
-        <f>'Income Statement'!D8*'Assumptions'!C44</f>
+        <f>'Income Statement'!D8*'Assumptions'!C47</f>
         <v/>
       </c>
       <c r="H19" s="16">
-        <f>'Income Statement'!E8*'Assumptions'!C44</f>
+        <f>'Income Statement'!E8*'Assumptions'!C47</f>
         <v/>
       </c>
       <c r="I19" s="16">
-        <f>'Income Statement'!F8*'Assumptions'!C44</f>
+        <f>'Income Statement'!F8*'Assumptions'!C47</f>
         <v/>
       </c>
       <c r="J19" s="16">
-        <f>'Income Statement'!G8*'Assumptions'!C44</f>
+        <f>'Income Statement'!G8*'Assumptions'!C47</f>
         <v/>
       </c>
       <c r="K19" s="16">
-        <f>'Income Statement'!H8*'Assumptions'!C44</f>
+        <f>'Income Statement'!H8*'Assumptions'!C47</f>
         <v/>
       </c>
     </row>
@@ -5708,23 +6175,23 @@
         <v/>
       </c>
       <c r="G21" s="16">
-        <f>'Schedules'!D18</f>
+        <f>'Schedules'!D34</f>
         <v/>
       </c>
       <c r="H21" s="16">
-        <f>'Schedules'!E18</f>
+        <f>'Schedules'!E34</f>
         <v/>
       </c>
       <c r="I21" s="16">
-        <f>'Schedules'!F18</f>
+        <f>'Schedules'!F34</f>
         <v/>
       </c>
       <c r="J21" s="16">
-        <f>'Schedules'!G18</f>
+        <f>'Schedules'!G34</f>
         <v/>
       </c>
       <c r="K21" s="16">
-        <f>'Schedules'!H18</f>
+        <f>'Schedules'!H34</f>
         <v/>
       </c>
     </row>
@@ -5748,23 +6215,23 @@
         <v/>
       </c>
       <c r="G22" s="16">
-        <f>'Schedules'!D21</f>
+        <f>'Schedules'!D37</f>
         <v/>
       </c>
       <c r="H22" s="16">
-        <f>'Schedules'!E21</f>
+        <f>'Schedules'!E37</f>
         <v/>
       </c>
       <c r="I22" s="16">
-        <f>'Schedules'!F21</f>
+        <f>'Schedules'!F37</f>
         <v/>
       </c>
       <c r="J22" s="16">
-        <f>'Schedules'!G21</f>
+        <f>'Schedules'!G37</f>
         <v/>
       </c>
       <c r="K22" s="16">
-        <f>'Schedules'!H21</f>
+        <f>'Schedules'!H37</f>
         <v/>
       </c>
     </row>
@@ -5829,23 +6296,23 @@
         <v/>
       </c>
       <c r="G24" s="16">
-        <f>'Schedules'!D14</f>
+        <f>'Schedules'!D30</f>
         <v/>
       </c>
       <c r="H24" s="16">
-        <f>'Schedules'!E14</f>
+        <f>'Schedules'!E30</f>
         <v/>
       </c>
       <c r="I24" s="16">
-        <f>'Schedules'!F14</f>
+        <f>'Schedules'!F30</f>
         <v/>
       </c>
       <c r="J24" s="16">
-        <f>'Schedules'!G14</f>
+        <f>'Schedules'!G30</f>
         <v/>
       </c>
       <c r="K24" s="16">
-        <f>'Schedules'!H14</f>
+        <f>'Schedules'!H30</f>
         <v/>
       </c>
     </row>
@@ -5970,23 +6437,23 @@
         <v/>
       </c>
       <c r="G28" s="16">
-        <f>'Balance Sheet'!F28+'Cash Flow'!D8+'Assumptions'!D29</f>
+        <f>'Balance Sheet'!F28+'Cash Flow'!D8+'Assumptions'!D32</f>
         <v/>
       </c>
       <c r="H28" s="16">
-        <f>'Balance Sheet'!G28+'Cash Flow'!E8+'Assumptions'!E29</f>
+        <f>'Balance Sheet'!G28+'Cash Flow'!E8+'Assumptions'!E32</f>
         <v/>
       </c>
       <c r="I28" s="16">
-        <f>'Balance Sheet'!H28+'Cash Flow'!F8+'Assumptions'!F29</f>
+        <f>'Balance Sheet'!H28+'Cash Flow'!F8+'Assumptions'!F32</f>
         <v/>
       </c>
       <c r="J28" s="16">
-        <f>'Balance Sheet'!I28+'Cash Flow'!G8+'Assumptions'!G29</f>
+        <f>'Balance Sheet'!I28+'Cash Flow'!G8+'Assumptions'!G32</f>
         <v/>
       </c>
       <c r="K28" s="16">
-        <f>'Balance Sheet'!J28+'Cash Flow'!H8+'Assumptions'!H29</f>
+        <f>'Balance Sheet'!J28+'Cash Flow'!H8+'Assumptions'!H32</f>
         <v/>
       </c>
     </row>
@@ -6285,23 +6752,23 @@
         </is>
       </c>
       <c r="D6" s="16">
-        <f>'Schedules'!D6</f>
+        <f>'Schedules'!D22</f>
         <v/>
       </c>
       <c r="E6" s="16">
-        <f>'Schedules'!E6</f>
+        <f>'Schedules'!E22</f>
         <v/>
       </c>
       <c r="F6" s="16">
-        <f>'Schedules'!F6</f>
+        <f>'Schedules'!F22</f>
         <v/>
       </c>
       <c r="G6" s="16">
-        <f>'Schedules'!G6</f>
+        <f>'Schedules'!G22</f>
         <v/>
       </c>
       <c r="H6" s="16">
-        <f>'Schedules'!H6</f>
+        <f>'Schedules'!H22</f>
         <v/>
       </c>
     </row>
@@ -6312,23 +6779,23 @@
         </is>
       </c>
       <c r="D7" s="16">
-        <f>'Schedules'!D10</f>
+        <f>'Schedules'!D26</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>'Schedules'!E10</f>
+        <f>'Schedules'!E26</f>
         <v/>
       </c>
       <c r="F7" s="16">
-        <f>'Schedules'!F10</f>
+        <f>'Schedules'!F26</f>
         <v/>
       </c>
       <c r="G7" s="16">
-        <f>'Schedules'!G10</f>
+        <f>'Schedules'!G26</f>
         <v/>
       </c>
       <c r="H7" s="16">
-        <f>'Schedules'!H10</f>
+        <f>'Schedules'!H26</f>
         <v/>
       </c>
     </row>
@@ -6339,23 +6806,23 @@
         </is>
       </c>
       <c r="D8" s="16">
-        <f>'Assumptions'!D26*'Income Statement'!D8</f>
+        <f>'Assumptions'!D29*'Income Statement'!D8</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>'Assumptions'!E26*'Income Statement'!E8</f>
+        <f>'Assumptions'!E29*'Income Statement'!E8</f>
         <v/>
       </c>
       <c r="F8" s="16">
-        <f>'Assumptions'!F26*'Income Statement'!F8</f>
+        <f>'Assumptions'!F29*'Income Statement'!F8</f>
         <v/>
       </c>
       <c r="G8" s="16">
-        <f>'Assumptions'!G26*'Income Statement'!G8</f>
+        <f>'Assumptions'!G29*'Income Statement'!G8</f>
         <v/>
       </c>
       <c r="H8" s="16">
-        <f>'Assumptions'!H26*'Income Statement'!H8</f>
+        <f>'Assumptions'!H29*'Income Statement'!H8</f>
         <v/>
       </c>
     </row>
@@ -6366,23 +6833,23 @@
         </is>
       </c>
       <c r="D9" s="16">
-        <f>'Schedules'!D13</f>
+        <f>'Schedules'!D29</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>'Schedules'!E13</f>
+        <f>'Schedules'!E29</f>
         <v/>
       </c>
       <c r="F9" s="16">
-        <f>'Schedules'!F13</f>
+        <f>'Schedules'!F29</f>
         <v/>
       </c>
       <c r="G9" s="16">
-        <f>'Schedules'!G13</f>
+        <f>'Schedules'!G29</f>
         <v/>
       </c>
       <c r="H9" s="16">
-        <f>'Schedules'!H13</f>
+        <f>'Schedules'!H29</f>
         <v/>
       </c>
     </row>
@@ -6653,23 +7120,23 @@
         </is>
       </c>
       <c r="D20" s="16">
-        <f>-'Schedules'!D5</f>
+        <f>-'Schedules'!D21</f>
         <v/>
       </c>
       <c r="E20" s="16">
-        <f>-'Schedules'!E5</f>
+        <f>-'Schedules'!E21</f>
         <v/>
       </c>
       <c r="F20" s="16">
-        <f>-'Schedules'!F5</f>
+        <f>-'Schedules'!F21</f>
         <v/>
       </c>
       <c r="G20" s="16">
-        <f>-'Schedules'!G5</f>
+        <f>-'Schedules'!G21</f>
         <v/>
       </c>
       <c r="H20" s="16">
-        <f>-'Schedules'!H5</f>
+        <f>-'Schedules'!H21</f>
         <v/>
       </c>
     </row>
@@ -6724,23 +7191,23 @@
         </is>
       </c>
       <c r="D23" s="16">
-        <f>'Schedules'!D17</f>
+        <f>'Schedules'!D33</f>
         <v/>
       </c>
       <c r="E23" s="16">
-        <f>'Schedules'!E17</f>
+        <f>'Schedules'!E33</f>
         <v/>
       </c>
       <c r="F23" s="16">
-        <f>'Schedules'!F17</f>
+        <f>'Schedules'!F33</f>
         <v/>
       </c>
       <c r="G23" s="16">
-        <f>'Schedules'!G17</f>
+        <f>'Schedules'!G33</f>
         <v/>
       </c>
       <c r="H23" s="16">
-        <f>'Schedules'!H17</f>
+        <f>'Schedules'!H33</f>
         <v/>
       </c>
     </row>
@@ -6751,23 +7218,23 @@
         </is>
       </c>
       <c r="D24" s="16">
-        <f>'Schedules'!D20</f>
+        <f>'Schedules'!D36</f>
         <v/>
       </c>
       <c r="E24" s="16">
-        <f>'Schedules'!E20</f>
+        <f>'Schedules'!E36</f>
         <v/>
       </c>
       <c r="F24" s="16">
-        <f>'Schedules'!F20</f>
+        <f>'Schedules'!F36</f>
         <v/>
       </c>
       <c r="G24" s="16">
-        <f>'Schedules'!G20</f>
+        <f>'Schedules'!G36</f>
         <v/>
       </c>
       <c r="H24" s="16">
-        <f>'Schedules'!H20</f>
+        <f>'Schedules'!H36</f>
         <v/>
       </c>
     </row>
@@ -6778,23 +7245,23 @@
         </is>
       </c>
       <c r="D25" s="16">
-        <f>'Assumptions'!D29</f>
+        <f>'Assumptions'!D32</f>
         <v/>
       </c>
       <c r="E25" s="16">
-        <f>'Assumptions'!E29</f>
+        <f>'Assumptions'!E32</f>
         <v/>
       </c>
       <c r="F25" s="16">
-        <f>'Assumptions'!F29</f>
+        <f>'Assumptions'!F32</f>
         <v/>
       </c>
       <c r="G25" s="16">
-        <f>'Assumptions'!G29</f>
+        <f>'Assumptions'!G32</f>
         <v/>
       </c>
       <c r="H25" s="16">
-        <f>'Assumptions'!H29</f>
+        <f>'Assumptions'!H32</f>
         <v/>
       </c>
     </row>
